--- a/data/music.xlsx
+++ b/data/music.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lindanakasone/Documents/GitHub/sound-and-vision/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA77C79A-72A6-B145-A976-3E85B378FAB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7A3CCF2-9596-6A47-98FB-098D7461F449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17340" yWindow="8300" windowWidth="30500" windowHeight="18440" xr2:uid="{D9D4D37D-4BCE-774B-89FD-6B702A9EB150}"/>
+    <workbookView xWindow="12200" yWindow="4220" windowWidth="30500" windowHeight="18440" xr2:uid="{D9D4D37D-4BCE-774B-89FD-6B702A9EB150}"/>
   </bookViews>
   <sheets>
     <sheet name="750 songs" sheetId="5" r:id="rId1"/>
@@ -39,6 +39,24 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={D8D12FB0-34E4-7041-9281-9B060D9CC634}</author>
+  </authors>
+  <commentList>
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{D8D12FB0-34E4-7041-9281-9B060D9CC634}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Genre according to Apple Music</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
 <metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
@@ -62,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7141" uniqueCount="1526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7832" uniqueCount="1573">
   <si>
     <t>Song</t>
   </si>
@@ -4417,9 +4435,6 @@
     <t>England; Australia</t>
   </si>
   <si>
-    <t>England: Denmark</t>
-  </si>
-  <si>
     <t>US - Minnesota</t>
   </si>
   <si>
@@ -4480,9 +4495,6 @@
     <t>US - New York; Italy; US - Michigan</t>
   </si>
   <si>
-    <t>US - New York; US-Virginia</t>
-  </si>
-  <si>
     <t>US - Washington</t>
   </si>
   <si>
@@ -4495,9 +4507,6 @@
     <t>US - Oregon</t>
   </si>
   <si>
-    <t xml:space="preserve">England; US - California </t>
-  </si>
-  <si>
     <t>US - Wisconsin</t>
   </si>
   <si>
@@ -4576,9 +4585,6 @@
     <t>Russia</t>
   </si>
   <si>
-    <t>US - Michegan</t>
-  </si>
-  <si>
     <t>Canada; US - Illinois</t>
   </si>
   <si>
@@ -4640,6 +4646,159 @@
   </si>
   <si>
     <t>Troubleman</t>
+  </si>
+  <si>
+    <t>Indie Pop</t>
+  </si>
+  <si>
+    <t>Operatic Pop</t>
+  </si>
+  <si>
+    <t>Piano</t>
+  </si>
+  <si>
+    <t>Early Modern Classical</t>
+  </si>
+  <si>
+    <t>Electric Guitar</t>
+  </si>
+  <si>
+    <t>Piano; Guitar</t>
+  </si>
+  <si>
+    <t>Alt Metal</t>
+  </si>
+  <si>
+    <t>Bass</t>
+  </si>
+  <si>
+    <t>Drum Machine; Synth</t>
+  </si>
+  <si>
+    <t>Post Punk</t>
+  </si>
+  <si>
+    <t>Bass Guitar</t>
+  </si>
+  <si>
+    <t>Pop Rock</t>
+  </si>
+  <si>
+    <t>Classic Rock</t>
+  </si>
+  <si>
+    <t>Orchestral Rock</t>
+  </si>
+  <si>
+    <t>Alternative Rock</t>
+  </si>
+  <si>
+    <t>Synth Rock</t>
+  </si>
+  <si>
+    <t>Downtempo</t>
+  </si>
+  <si>
+    <t>Film Score; Free Jazz</t>
+  </si>
+  <si>
+    <t>Trip Hop</t>
+  </si>
+  <si>
+    <t>Latin</t>
+  </si>
+  <si>
+    <t>Neoclassical; Film Score</t>
+  </si>
+  <si>
+    <t>Neoclassical</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>Led Zeppelin</t>
+  </si>
+  <si>
+    <t>Nu Jazz</t>
+  </si>
+  <si>
+    <t>Psychedlic Rock</t>
+  </si>
+  <si>
+    <t>Guitar</t>
+  </si>
+  <si>
+    <t>Indie Electronic</t>
+  </si>
+  <si>
+    <t>Synth Pop</t>
+  </si>
+  <si>
+    <t>Orchestral Pop</t>
+  </si>
+  <si>
+    <t>Dream Pop</t>
+  </si>
+  <si>
+    <t>Swing Jazz</t>
+  </si>
+  <si>
+    <t>Indie Folk</t>
+  </si>
+  <si>
+    <t>Trumpet</t>
+  </si>
+  <si>
+    <t>Disco</t>
+  </si>
+  <si>
+    <t>Lounge Rock</t>
+  </si>
+  <si>
+    <t>Hip Hop</t>
+  </si>
+  <si>
+    <t>Cabaret Pop</t>
+  </si>
+  <si>
+    <t>Cabaret Jazz</t>
+  </si>
+  <si>
+    <t>Lounge Jazz</t>
+  </si>
+  <si>
+    <t>Synth Disco</t>
+  </si>
+  <si>
+    <t>Jazz Pop</t>
+  </si>
+  <si>
+    <t>Ambient Piano</t>
+  </si>
+  <si>
+    <t>Sanskrit</t>
+  </si>
+  <si>
+    <t>The Mamas &amp; the Papas</t>
+  </si>
+  <si>
+    <t>Billie Holiday</t>
+  </si>
+  <si>
+    <t>England; Denmark</t>
+  </si>
+  <si>
+    <t>England; US - California</t>
+  </si>
+  <si>
+    <t>US - New York; US - Virginia</t>
+  </si>
+  <si>
+    <t>Soul Pop</t>
+  </si>
+  <si>
+    <t>Alternative Dance</t>
   </si>
 </sst>
 </file>
@@ -4662,7 +4821,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4681,6 +4840,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.749992370372631"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -4694,7 +4859,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -4703,6 +4868,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4718,6 +4884,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Linda N" id="{3F9DA79B-C5C6-914E-9032-FA8F06D2E665}" userId="b88caa72ce5f0b6c" providerId="Windows Live"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5035,8 +5207,16 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="J1" dT="2026-03-28T19:16:16.93" personId="{3F9DA79B-C5C6-914E-9032-FA8F06D2E665}" id="{D8D12FB0-34E4-7041-9281-9B060D9CC634}">
+    <text>Genre according to Apple Music</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D73E79B3-672E-5F4C-A79E-CB748E362622}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D73E79B3-672E-5F4C-A79E-CB748E362622}">
   <dimension ref="A1:XEX751"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -5076,34 +5256,34 @@
         <v>1447</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>1506</v>
+        <v>1502</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="6" t="s">
         <v>1313</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>187</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>1507</v>
+        <v>1503</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>1508</v>
+        <v>1504</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>1509</v>
+        <v>1505</v>
       </c>
       <c r="P1" s="3" t="s">
         <v>127</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>1510</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.2">
@@ -5438,7 +5618,7 @@
         <v>38</v>
       </c>
       <c r="H14" t="s">
-        <v>1512</v>
+        <v>1508</v>
       </c>
       <c r="J14" t="s">
         <v>10</v>
@@ -5464,7 +5644,7 @@
         <v>38</v>
       </c>
       <c r="H15" t="s">
-        <v>1512</v>
+        <v>1508</v>
       </c>
       <c r="J15" t="s">
         <v>305</v>
@@ -5548,7 +5728,7 @@
         <v>2010</v>
       </c>
       <c r="G18" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H18" t="s">
         <v>9</v>
@@ -5606,7 +5786,7 @@
         <v>2009</v>
       </c>
       <c r="G20" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="H20" t="s">
         <v>9</v>
@@ -5693,7 +5873,7 @@
         <v>153</v>
       </c>
       <c r="H23" t="s">
-        <v>1512</v>
+        <v>1508</v>
       </c>
       <c r="J23" t="s">
         <v>264</v>
@@ -5719,7 +5899,7 @@
         <v>2009</v>
       </c>
       <c r="G24" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="H24" t="s">
         <v>9</v>
@@ -5748,7 +5928,7 @@
         <v>2009</v>
       </c>
       <c r="G25" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="H25" t="s">
         <v>9</v>
@@ -5771,10 +5951,10 @@
         <v>19</v>
       </c>
       <c r="F26">
-        <v>2001</v>
+        <v>2005</v>
       </c>
       <c r="G26" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="H26" t="s">
         <v>9</v>
@@ -5797,10 +5977,10 @@
         <v>19</v>
       </c>
       <c r="F27">
-        <v>2001</v>
+        <v>2005</v>
       </c>
       <c r="G27" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="H27" t="s">
         <v>9</v>
@@ -5956,7 +6136,7 @@
         <v>1968</v>
       </c>
       <c r="G33" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="H33" t="s">
         <v>9</v>
@@ -5985,7 +6165,7 @@
         <v>497</v>
       </c>
       <c r="H34" t="s">
-        <v>1513</v>
+        <v>1509</v>
       </c>
       <c r="J34" t="s">
         <v>550</v>
@@ -6164,7 +6344,7 @@
         <v>2003</v>
       </c>
       <c r="G41" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="H41" t="s">
         <v>9</v>
@@ -6193,7 +6373,7 @@
         <v>2006</v>
       </c>
       <c r="G42" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="H42" t="s">
         <v>9</v>
@@ -6219,7 +6399,7 @@
         <v>1987</v>
       </c>
       <c r="G43" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H43" t="s">
         <v>9</v>
@@ -6228,7 +6408,7 @@
         <v>282</v>
       </c>
       <c r="P43" t="s">
-        <v>1517</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.2">
@@ -6248,7 +6428,7 @@
         <v>1988</v>
       </c>
       <c r="G44" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H44" t="s">
         <v>9</v>
@@ -6780,7 +6960,7 @@
         <v>2017</v>
       </c>
       <c r="G64" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H64" t="s">
         <v>9</v>
@@ -6806,7 +6986,7 @@
         <v>2017</v>
       </c>
       <c r="G65" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H65" t="s">
         <v>9</v>
@@ -6832,7 +7012,7 @@
         <v>2015</v>
       </c>
       <c r="G66" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H66" t="s">
         <v>9</v>
@@ -6858,7 +7038,7 @@
         <v>2019</v>
       </c>
       <c r="G67" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H67" t="s">
         <v>9</v>
@@ -6884,7 +7064,7 @@
         <v>2019</v>
       </c>
       <c r="G68" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H68" t="s">
         <v>9</v>
@@ -6910,7 +7090,7 @@
         <v>2008</v>
       </c>
       <c r="G69" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H69" t="s">
         <v>9</v>
@@ -6936,7 +7116,7 @@
         <v>1998</v>
       </c>
       <c r="G70" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H70" t="s">
         <v>9</v>
@@ -6965,7 +7145,7 @@
         <v>2014</v>
       </c>
       <c r="G71" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="H71" t="s">
         <v>39</v>
@@ -6991,7 +7171,7 @@
         <v>2006</v>
       </c>
       <c r="G72" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="H72" t="s">
         <v>9</v>
@@ -7017,7 +7197,7 @@
         <v>2019</v>
       </c>
       <c r="G73" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H73" t="s">
         <v>9</v>
@@ -7043,7 +7223,7 @@
         <v>1977</v>
       </c>
       <c r="G74" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="H74" t="s">
         <v>9</v>
@@ -7072,7 +7252,7 @@
         <v>2014</v>
       </c>
       <c r="G75" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="H75" t="s">
         <v>9</v>
@@ -7098,7 +7278,7 @@
         <v>2008</v>
       </c>
       <c r="G76" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H76" t="s">
         <v>9</v>
@@ -7107,7 +7287,7 @@
         <v>10</v>
       </c>
       <c r="P76" t="s">
-        <v>1518</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.2">
@@ -7127,7 +7307,7 @@
         <v>2008</v>
       </c>
       <c r="G77" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H77" t="s">
         <v>9</v>
@@ -7182,7 +7362,7 @@
         <v>2004</v>
       </c>
       <c r="G79" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="H79" t="s">
         <v>9</v>
@@ -7211,7 +7391,7 @@
         <v>2004</v>
       </c>
       <c r="G80" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="H80" t="s">
         <v>9</v>
@@ -7292,7 +7472,7 @@
         <v>2005</v>
       </c>
       <c r="G83" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="H83" t="s">
         <v>9</v>
@@ -7318,7 +7498,7 @@
         <v>2009</v>
       </c>
       <c r="G84" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="H84" t="s">
         <v>9</v>
@@ -7344,7 +7524,7 @@
         <v>2014</v>
       </c>
       <c r="G85" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H85" t="s">
         <v>9</v>
@@ -7370,7 +7550,7 @@
         <v>2014</v>
       </c>
       <c r="G86" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H86" t="s">
         <v>9</v>
@@ -7396,7 +7576,7 @@
         <v>2014</v>
       </c>
       <c r="G87" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H87" t="s">
         <v>9</v>
@@ -7422,7 +7602,7 @@
         <v>2014</v>
       </c>
       <c r="G88" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H88" t="s">
         <v>9</v>
@@ -7448,7 +7628,7 @@
         <v>2014</v>
       </c>
       <c r="G89" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H89" t="s">
         <v>9</v>
@@ -7474,7 +7654,7 @@
         <v>2014</v>
       </c>
       <c r="G90" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H90" t="s">
         <v>9</v>
@@ -7500,7 +7680,7 @@
         <v>2014</v>
       </c>
       <c r="G91" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H91" t="s">
         <v>9</v>
@@ -7526,7 +7706,7 @@
         <v>2014</v>
       </c>
       <c r="G92" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H92" t="s">
         <v>9</v>
@@ -7552,7 +7732,7 @@
         <v>2014</v>
       </c>
       <c r="G93" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H93" t="s">
         <v>9</v>
@@ -7578,7 +7758,7 @@
         <v>2014</v>
       </c>
       <c r="G94" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H94" t="s">
         <v>9</v>
@@ -7604,7 +7784,7 @@
         <v>2009</v>
       </c>
       <c r="G95" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H95" t="s">
         <v>9</v>
@@ -7630,7 +7810,7 @@
         <v>2010</v>
       </c>
       <c r="G96" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H96" t="s">
         <v>9</v>
@@ -7656,7 +7836,7 @@
         <v>2010</v>
       </c>
       <c r="G97" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H97" t="s">
         <v>9</v>
@@ -7682,7 +7862,7 @@
         <v>2010</v>
       </c>
       <c r="G98" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H98" t="s">
         <v>9</v>
@@ -7708,7 +7888,7 @@
         <v>2010</v>
       </c>
       <c r="G99" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H99" t="s">
         <v>9</v>
@@ -7734,7 +7914,7 @@
         <v>2010</v>
       </c>
       <c r="G100" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H100" t="s">
         <v>9</v>
@@ -7760,7 +7940,7 @@
         <v>2010</v>
       </c>
       <c r="G101" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H101" t="s">
         <v>9</v>
@@ -7786,7 +7966,7 @@
         <v>2010</v>
       </c>
       <c r="G102" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H102" t="s">
         <v>9</v>
@@ -7812,7 +7992,7 @@
         <v>2010</v>
       </c>
       <c r="G103" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H103" t="s">
         <v>9</v>
@@ -7838,7 +8018,7 @@
         <v>2010</v>
       </c>
       <c r="G104" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H104" t="s">
         <v>9</v>
@@ -7864,7 +8044,7 @@
         <v>2010</v>
       </c>
       <c r="G105" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H105" t="s">
         <v>9</v>
@@ -7890,7 +8070,7 @@
         <v>2022</v>
       </c>
       <c r="G106" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H106" t="s">
         <v>9</v>
@@ -7916,7 +8096,7 @@
         <v>2022</v>
       </c>
       <c r="G107" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H107" t="s">
         <v>9</v>
@@ -7942,7 +8122,7 @@
         <v>2022</v>
       </c>
       <c r="G108" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H108" t="s">
         <v>9</v>
@@ -7968,7 +8148,7 @@
         <v>2022</v>
       </c>
       <c r="G109" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H109" t="s">
         <v>9</v>
@@ -7994,7 +8174,7 @@
         <v>2022</v>
       </c>
       <c r="G110" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H110" t="s">
         <v>9</v>
@@ -8020,7 +8200,7 @@
         <v>2022</v>
       </c>
       <c r="G111" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H111" t="s">
         <v>9</v>
@@ -8046,7 +8226,7 @@
         <v>2015</v>
       </c>
       <c r="G112" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H112" t="s">
         <v>9</v>
@@ -8072,7 +8252,7 @@
         <v>2018</v>
       </c>
       <c r="G113" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H113" t="s">
         <v>9</v>
@@ -8098,7 +8278,7 @@
         <v>2022</v>
       </c>
       <c r="G114" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H114" t="s">
         <v>9</v>
@@ -8150,7 +8330,7 @@
         <v>2022</v>
       </c>
       <c r="G116" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H116" t="s">
         <v>9</v>
@@ -8176,7 +8356,7 @@
         <v>1996</v>
       </c>
       <c r="G117" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H117" t="s">
         <v>9</v>
@@ -8202,7 +8382,7 @@
         <v>1996</v>
       </c>
       <c r="G118" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H118" t="s">
         <v>9</v>
@@ -8228,7 +8408,7 @@
         <v>1996</v>
       </c>
       <c r="G119" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H119" t="s">
         <v>9</v>
@@ -8254,7 +8434,7 @@
         <v>1996</v>
       </c>
       <c r="G120" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H120" t="s">
         <v>9</v>
@@ -8283,7 +8463,7 @@
         <v>1996</v>
       </c>
       <c r="G121" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H121" t="s">
         <v>9</v>
@@ -8309,7 +8489,7 @@
         <v>1994</v>
       </c>
       <c r="G122" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H122" t="s">
         <v>9</v>
@@ -8335,7 +8515,7 @@
         <v>1998</v>
       </c>
       <c r="G123" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="H123" t="s">
         <v>9</v>
@@ -8361,7 +8541,7 @@
         <v>1998</v>
       </c>
       <c r="G124" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="H124" t="s">
         <v>9</v>
@@ -8413,7 +8593,7 @@
         <v>2021</v>
       </c>
       <c r="G126" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="H126" t="s">
         <v>9</v>
@@ -8439,7 +8619,7 @@
         <v>2007</v>
       </c>
       <c r="G127" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H127" t="s">
         <v>9</v>
@@ -8459,13 +8639,13 @@
         <v>137</v>
       </c>
       <c r="E128" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="F128">
         <v>1990</v>
       </c>
       <c r="G128" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H128" t="s">
         <v>9</v>
@@ -8485,13 +8665,13 @@
         <v>137</v>
       </c>
       <c r="E129" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="F129">
         <v>1990</v>
       </c>
       <c r="G129" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H129" t="s">
         <v>9</v>
@@ -8511,13 +8691,13 @@
         <v>137</v>
       </c>
       <c r="E130" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="F130">
         <v>1990</v>
       </c>
       <c r="G130" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H130" t="s">
         <v>9</v>
@@ -8537,13 +8717,13 @@
         <v>137</v>
       </c>
       <c r="E131" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="F131">
         <v>1990</v>
       </c>
       <c r="G131" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H131" t="s">
         <v>9</v>
@@ -8563,13 +8743,13 @@
         <v>137</v>
       </c>
       <c r="E132" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="F132">
         <v>1990</v>
       </c>
       <c r="G132" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H132" t="s">
         <v>9</v>
@@ -8589,13 +8769,13 @@
         <v>137</v>
       </c>
       <c r="E133" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="F133">
         <v>1990</v>
       </c>
       <c r="G133" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H133" t="s">
         <v>9</v>
@@ -8615,13 +8795,13 @@
         <v>137</v>
       </c>
       <c r="E134" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="F134">
         <v>1990</v>
       </c>
       <c r="G134" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H134" t="s">
         <v>9</v>
@@ -8641,13 +8821,13 @@
         <v>137</v>
       </c>
       <c r="E135" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="F135">
         <v>1990</v>
       </c>
       <c r="G135" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H135" t="s">
         <v>9</v>
@@ -8667,13 +8847,13 @@
         <v>137</v>
       </c>
       <c r="E136" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="F136">
         <v>1990</v>
       </c>
       <c r="G136" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H136" t="s">
         <v>39</v>
@@ -8699,7 +8879,7 @@
         <v>1989</v>
       </c>
       <c r="G137" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H137" t="s">
         <v>9</v>
@@ -8725,7 +8905,7 @@
         <v>1989</v>
       </c>
       <c r="G138" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H138" t="s">
         <v>9</v>
@@ -8751,7 +8931,7 @@
         <v>1996</v>
       </c>
       <c r="G139" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H139" t="s">
         <v>9</v>
@@ -8777,7 +8957,7 @@
         <v>1996</v>
       </c>
       <c r="G140" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H140" t="s">
         <v>9</v>
@@ -8803,7 +8983,7 @@
         <v>1996</v>
       </c>
       <c r="G141" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H141" t="s">
         <v>9</v>
@@ -8829,7 +9009,7 @@
         <v>1996</v>
       </c>
       <c r="G142" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H142" t="s">
         <v>9</v>
@@ -8855,7 +9035,7 @@
         <v>1993</v>
       </c>
       <c r="G143" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H143" t="s">
         <v>9</v>
@@ -8881,7 +9061,7 @@
         <v>1996</v>
       </c>
       <c r="G144" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H144" t="s">
         <v>9</v>
@@ -8901,7 +9081,7 @@
         <v>151</v>
       </c>
       <c r="D145" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="E145" t="s">
         <v>152</v>
@@ -8910,7 +9090,7 @@
         <v>2016</v>
       </c>
       <c r="G145" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="H145" t="s">
         <v>9</v>
@@ -9641,7 +9821,7 @@
         <v>466</v>
       </c>
       <c r="H173" t="s">
-        <v>1512</v>
+        <v>1508</v>
       </c>
       <c r="J173" t="s">
         <v>10</v>
@@ -9719,7 +9899,7 @@
         <v>466</v>
       </c>
       <c r="H176" t="s">
-        <v>1512</v>
+        <v>1508</v>
       </c>
       <c r="J176" t="s">
         <v>10</v>
@@ -9745,7 +9925,7 @@
         <v>466</v>
       </c>
       <c r="H177" t="s">
-        <v>1514</v>
+        <v>1510</v>
       </c>
       <c r="J177" t="s">
         <v>10</v>
@@ -9771,7 +9951,7 @@
         <v>466</v>
       </c>
       <c r="H178" t="s">
-        <v>1512</v>
+        <v>1508</v>
       </c>
       <c r="J178" t="s">
         <v>10</v>
@@ -9797,7 +9977,7 @@
         <v>466</v>
       </c>
       <c r="H179" t="s">
-        <v>1512</v>
+        <v>1508</v>
       </c>
       <c r="J179" t="s">
         <v>10</v>
@@ -9849,7 +10029,7 @@
         <v>466</v>
       </c>
       <c r="H181" t="s">
-        <v>1512</v>
+        <v>1508</v>
       </c>
       <c r="J181" t="s">
         <v>10</v>
@@ -9875,7 +10055,7 @@
         <v>466</v>
       </c>
       <c r="H182" t="s">
-        <v>1512</v>
+        <v>1508</v>
       </c>
       <c r="J182" t="s">
         <v>10</v>
@@ -9901,7 +10081,7 @@
         <v>466</v>
       </c>
       <c r="H183" t="s">
-        <v>1512</v>
+        <v>1508</v>
       </c>
       <c r="J183" t="s">
         <v>627</v>
@@ -9927,7 +10107,7 @@
         <v>466</v>
       </c>
       <c r="H184" t="s">
-        <v>1512</v>
+        <v>1508</v>
       </c>
       <c r="J184" t="s">
         <v>10</v>
@@ -9982,7 +10162,7 @@
         <v>466</v>
       </c>
       <c r="H186" t="s">
-        <v>1512</v>
+        <v>1508</v>
       </c>
       <c r="J186" t="s">
         <v>10</v>
@@ -10008,7 +10188,7 @@
         <v>466</v>
       </c>
       <c r="H187" t="s">
-        <v>1512</v>
+        <v>1508</v>
       </c>
       <c r="J187" t="s">
         <v>10</v>
@@ -10034,7 +10214,7 @@
         <v>466</v>
       </c>
       <c r="H188" t="s">
-        <v>1512</v>
+        <v>1508</v>
       </c>
       <c r="J188" t="s">
         <v>10</v>
@@ -10060,7 +10240,7 @@
         <v>466</v>
       </c>
       <c r="H189" t="s">
-        <v>1512</v>
+        <v>1508</v>
       </c>
       <c r="J189" t="s">
         <v>629</v>
@@ -10086,7 +10266,7 @@
         <v>466</v>
       </c>
       <c r="H190" t="s">
-        <v>1512</v>
+        <v>1508</v>
       </c>
       <c r="J190" t="s">
         <v>629</v>
@@ -10112,7 +10292,7 @@
         <v>466</v>
       </c>
       <c r="H191" t="s">
-        <v>1512</v>
+        <v>1508</v>
       </c>
       <c r="J191" t="s">
         <v>629</v>
@@ -10141,7 +10321,7 @@
         <v>466</v>
       </c>
       <c r="H192" t="s">
-        <v>1512</v>
+        <v>1508</v>
       </c>
       <c r="J192" t="s">
         <v>305</v>
@@ -10193,7 +10373,7 @@
         <v>2010</v>
       </c>
       <c r="G194" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="H194" t="s">
         <v>9</v>
@@ -10479,10 +10659,10 @@
         <v>2011</v>
       </c>
       <c r="G205" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="H205" t="s">
-        <v>1512</v>
+        <v>1508</v>
       </c>
       <c r="J205" t="s">
         <v>131</v>
@@ -10508,7 +10688,7 @@
         <v>2011</v>
       </c>
       <c r="G206" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -10534,10 +10714,10 @@
         <v>2011</v>
       </c>
       <c r="G207" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="H207" t="s">
-        <v>1512</v>
+        <v>1508</v>
       </c>
       <c r="J207" t="s">
         <v>131</v>
@@ -10563,7 +10743,7 @@
         <v>2011</v>
       </c>
       <c r="G208" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -10589,10 +10769,10 @@
         <v>2011</v>
       </c>
       <c r="G209" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="H209" t="s">
-        <v>1512</v>
+        <v>1508</v>
       </c>
       <c r="J209" t="s">
         <v>131</v>
@@ -10615,10 +10795,10 @@
         <v>2011</v>
       </c>
       <c r="G210" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="H210" t="s">
-        <v>1512</v>
+        <v>1508</v>
       </c>
       <c r="J210" t="s">
         <v>131</v>
@@ -10644,7 +10824,7 @@
         <v>2011</v>
       </c>
       <c r="G211" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -10670,10 +10850,10 @@
         <v>2011</v>
       </c>
       <c r="G212" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="H212" t="s">
-        <v>1512</v>
+        <v>1508</v>
       </c>
       <c r="J212" t="s">
         <v>131</v>
@@ -10696,10 +10876,10 @@
         <v>2011</v>
       </c>
       <c r="G213" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="H213" t="s">
-        <v>1512</v>
+        <v>1508</v>
       </c>
       <c r="J213" t="s">
         <v>131</v>
@@ -10725,7 +10905,7 @@
         <v>2011</v>
       </c>
       <c r="G214" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="H214" t="s">
         <v>9</v>
@@ -10751,10 +10931,10 @@
         <v>2011</v>
       </c>
       <c r="G215" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="H215" t="s">
-        <v>1512</v>
+        <v>1508</v>
       </c>
       <c r="J215" t="s">
         <v>131</v>
@@ -10780,7 +10960,7 @@
         <v>2009</v>
       </c>
       <c r="G216" t="s">
-        <v>1472</v>
+        <v>1570</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -11069,7 +11249,7 @@
         <v>2008</v>
       </c>
       <c r="G227" t="s">
-        <v>1505</v>
+        <v>1501</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -11095,7 +11275,7 @@
         <v>2008</v>
       </c>
       <c r="G228" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -11121,7 +11301,7 @@
         <v>2005</v>
       </c>
       <c r="G229" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -11618,7 +11798,7 @@
         <v>1449</v>
       </c>
       <c r="H248" t="s">
-        <v>1512</v>
+        <v>1508</v>
       </c>
       <c r="J248" t="s">
         <v>282</v>
@@ -11878,7 +12058,7 @@
         <v>1449</v>
       </c>
       <c r="H258" t="s">
-        <v>1512</v>
+        <v>1508</v>
       </c>
       <c r="J258" t="s">
         <v>282</v>
@@ -11910,7 +12090,7 @@
         <v>282</v>
       </c>
       <c r="P259" t="s">
-        <v>1519</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="260" spans="1:16" x14ac:dyDescent="0.2">
@@ -11933,13 +12113,13 @@
         <v>1449</v>
       </c>
       <c r="H260" t="s">
-        <v>1512</v>
+        <v>1508</v>
       </c>
       <c r="J260" t="s">
         <v>282</v>
       </c>
       <c r="P260" t="s">
-        <v>1520</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="261" spans="1:16" x14ac:dyDescent="0.2">
@@ -12040,7 +12220,7 @@
         <v>1449</v>
       </c>
       <c r="H264" t="s">
-        <v>1512</v>
+        <v>1508</v>
       </c>
       <c r="J264" t="s">
         <v>282</v>
@@ -12378,7 +12558,7 @@
         <v>1449</v>
       </c>
       <c r="H277" t="s">
-        <v>1512</v>
+        <v>1508</v>
       </c>
       <c r="J277" t="s">
         <v>131</v>
@@ -12560,7 +12740,7 @@
         <v>1449</v>
       </c>
       <c r="H284" t="s">
-        <v>1512</v>
+        <v>1508</v>
       </c>
       <c r="J284" t="s">
         <v>676</v>
@@ -12586,7 +12766,7 @@
         <v>1449</v>
       </c>
       <c r="H285" t="s">
-        <v>1512</v>
+        <v>1508</v>
       </c>
       <c r="J285" t="s">
         <v>676</v>
@@ -12716,7 +12896,7 @@
         <v>1996</v>
       </c>
       <c r="G290" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -12742,10 +12922,10 @@
         <v>1996</v>
       </c>
       <c r="G291" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H291" t="s">
-        <v>1512</v>
+        <v>1508</v>
       </c>
       <c r="J291" t="s">
         <v>683</v>
@@ -12768,10 +12948,10 @@
         <v>1996</v>
       </c>
       <c r="G292" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H292" t="s">
-        <v>1512</v>
+        <v>1508</v>
       </c>
       <c r="J292" t="s">
         <v>683</v>
@@ -12846,7 +13026,7 @@
         <v>1985</v>
       </c>
       <c r="G295" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -12872,7 +13052,7 @@
         <v>1985</v>
       </c>
       <c r="G296" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -12952,6 +13132,9 @@
       <c r="G299" t="s">
         <v>1449</v>
       </c>
+      <c r="H299" t="s">
+        <v>9</v>
+      </c>
       <c r="J299" t="s">
         <v>676</v>
       </c>
@@ -12975,6 +13158,9 @@
       <c r="G300" t="s">
         <v>1449</v>
       </c>
+      <c r="H300" t="s">
+        <v>9</v>
+      </c>
       <c r="J300" t="s">
         <v>676</v>
       </c>
@@ -12998,6 +13184,9 @@
       <c r="G301" t="s">
         <v>1449</v>
       </c>
+      <c r="H301" t="s">
+        <v>1508</v>
+      </c>
       <c r="J301" t="s">
         <v>676</v>
       </c>
@@ -13021,6 +13210,9 @@
       <c r="G302" t="s">
         <v>1449</v>
       </c>
+      <c r="H302" t="s">
+        <v>9</v>
+      </c>
       <c r="J302" t="s">
         <v>676</v>
       </c>
@@ -13044,6 +13236,9 @@
       <c r="G303" t="s">
         <v>1449</v>
       </c>
+      <c r="H303" t="s">
+        <v>9</v>
+      </c>
       <c r="J303" t="s">
         <v>676</v>
       </c>
@@ -13067,6 +13262,9 @@
       <c r="G304" t="s">
         <v>1449</v>
       </c>
+      <c r="H304" t="s">
+        <v>9</v>
+      </c>
       <c r="J304" t="s">
         <v>676</v>
       </c>
@@ -13090,6 +13288,9 @@
       <c r="G305" t="s">
         <v>1449</v>
       </c>
+      <c r="H305" t="s">
+        <v>9</v>
+      </c>
       <c r="J305" t="s">
         <v>676</v>
       </c>
@@ -13113,6 +13314,9 @@
       <c r="G306" t="s">
         <v>1449</v>
       </c>
+      <c r="H306" t="s">
+        <v>9</v>
+      </c>
       <c r="J306" t="s">
         <v>676</v>
       </c>
@@ -13136,6 +13340,9 @@
       <c r="G307" t="s">
         <v>1449</v>
       </c>
+      <c r="H307" t="s">
+        <v>9</v>
+      </c>
       <c r="J307" t="s">
         <v>676</v>
       </c>
@@ -13159,6 +13366,9 @@
       <c r="G308" t="s">
         <v>1449</v>
       </c>
+      <c r="H308" t="s">
+        <v>9</v>
+      </c>
       <c r="J308" t="s">
         <v>282</v>
       </c>
@@ -13180,7 +13390,10 @@
         <v>2016</v>
       </c>
       <c r="G309" t="s">
-        <v>1475</v>
+        <v>1473</v>
+      </c>
+      <c r="H309" t="s">
+        <v>1508</v>
       </c>
       <c r="J309" t="s">
         <v>285</v>
@@ -13203,7 +13416,10 @@
         <v>2016</v>
       </c>
       <c r="G310" t="s">
-        <v>1475</v>
+        <v>1473</v>
+      </c>
+      <c r="H310" t="s">
+        <v>1508</v>
       </c>
       <c r="J310" t="s">
         <v>285</v>
@@ -13226,7 +13442,10 @@
         <v>2016</v>
       </c>
       <c r="G311" t="s">
-        <v>1475</v>
+        <v>1473</v>
+      </c>
+      <c r="H311" t="s">
+        <v>1508</v>
       </c>
       <c r="J311" t="s">
         <v>285</v>
@@ -13249,7 +13468,10 @@
         <v>2016</v>
       </c>
       <c r="G312" t="s">
-        <v>1475</v>
+        <v>1473</v>
+      </c>
+      <c r="H312" t="s">
+        <v>1508</v>
       </c>
       <c r="J312" t="s">
         <v>285</v>
@@ -13272,7 +13494,10 @@
         <v>2016</v>
       </c>
       <c r="G313" t="s">
-        <v>1475</v>
+        <v>1473</v>
+      </c>
+      <c r="H313" t="s">
+        <v>1508</v>
       </c>
       <c r="J313" t="s">
         <v>285</v>
@@ -13297,28 +13522,40 @@
       <c r="G314" t="s">
         <v>8</v>
       </c>
+      <c r="H314" t="s">
+        <v>1508</v>
+      </c>
+      <c r="I314" t="s">
+        <v>10</v>
+      </c>
       <c r="J314" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="315" spans="1:1018 1026:2042 2050:3066 3074:4090 4098:5114 5122:6138 6146:7162 7170:8186 8194:9210 9218:10234 10242:11258 11266:12282 12290:13306 13314:14330 14338:15354 15362:16378" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
-        <v>1522</v>
+        <v>1518</v>
       </c>
       <c r="B315" s="2">
         <v>0.12222222222222222</v>
       </c>
       <c r="C315" t="s">
-        <v>1523</v>
+        <v>1519</v>
       </c>
       <c r="E315" t="s">
-        <v>1524</v>
+        <v>1520</v>
       </c>
       <c r="F315">
         <v>2012</v>
       </c>
       <c r="G315" t="s">
-        <v>1453</v>
+        <v>1452</v>
+      </c>
+      <c r="H315" t="s">
+        <v>9</v>
+      </c>
+      <c r="I315" t="s">
+        <v>1522</v>
       </c>
       <c r="J315" t="s">
         <v>131</v>
@@ -15372,22 +15609,28 @@
     </row>
     <row r="316" spans="1:1018 1026:2042 2050:3066 3074:4090 4098:5114 5122:6138 6146:7162 7170:8186 8194:9210 9218:10234 10242:11258 11266:12282 12290:13306 13314:14330 14338:15354 15362:16378" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
-        <v>1525</v>
+        <v>1521</v>
       </c>
       <c r="B316" s="2">
         <v>0.36736111111111114</v>
       </c>
       <c r="C316" t="s">
-        <v>1523</v>
+        <v>1519</v>
       </c>
       <c r="E316" t="s">
-        <v>1524</v>
+        <v>1520</v>
       </c>
       <c r="F316">
         <v>2012</v>
       </c>
       <c r="G316" t="s">
-        <v>1453</v>
+        <v>1452</v>
+      </c>
+      <c r="H316" t="s">
+        <v>9</v>
+      </c>
+      <c r="I316" t="s">
+        <v>1522</v>
       </c>
       <c r="J316" t="s">
         <v>131</v>
@@ -17458,6 +17701,12 @@
       <c r="G317" t="s">
         <v>1449</v>
       </c>
+      <c r="H317" t="s">
+        <v>9</v>
+      </c>
+      <c r="I317" t="s">
+        <v>1550</v>
+      </c>
       <c r="J317" t="s">
         <v>285</v>
       </c>
@@ -17481,6 +17730,12 @@
       <c r="G318" t="s">
         <v>1449</v>
       </c>
+      <c r="H318" t="s">
+        <v>9</v>
+      </c>
+      <c r="I318" t="s">
+        <v>1550</v>
+      </c>
       <c r="J318" t="s">
         <v>285</v>
       </c>
@@ -17504,6 +17759,12 @@
       <c r="G319" t="s">
         <v>1449</v>
       </c>
+      <c r="H319" t="s">
+        <v>9</v>
+      </c>
+      <c r="I319" t="s">
+        <v>1550</v>
+      </c>
       <c r="J319" t="s">
         <v>285</v>
       </c>
@@ -17527,11 +17788,17 @@
       <c r="G320" t="s">
         <v>1449</v>
       </c>
+      <c r="H320" t="s">
+        <v>9</v>
+      </c>
+      <c r="I320" t="s">
+        <v>1550</v>
+      </c>
       <c r="J320" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="321" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
         <v>344</v>
       </c>
@@ -17548,13 +17815,19 @@
         <v>2011</v>
       </c>
       <c r="G321" t="s">
-        <v>1461</v>
+        <v>1460</v>
+      </c>
+      <c r="H321" t="s">
+        <v>9</v>
+      </c>
+      <c r="I321" t="s">
+        <v>1523</v>
       </c>
       <c r="J321" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="322" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
         <v>346</v>
       </c>
@@ -17571,13 +17844,22 @@
         <v>2000</v>
       </c>
       <c r="G322" t="s">
-        <v>1476</v>
+        <v>1474</v>
+      </c>
+      <c r="H322" t="s">
+        <v>1508</v>
+      </c>
+      <c r="I322" t="s">
+        <v>1522</v>
       </c>
       <c r="J322" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="323" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="M322" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="323" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
         <v>700</v>
       </c>
@@ -17591,16 +17873,25 @@
         <v>701</v>
       </c>
       <c r="F323">
-        <v>2012</v>
+        <v>1888</v>
       </c>
       <c r="G323" t="s">
         <v>38</v>
       </c>
+      <c r="H323" t="s">
+        <v>1508</v>
+      </c>
+      <c r="I323" t="s">
+        <v>1525</v>
+      </c>
       <c r="J323" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="324" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="M323" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="324" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
         <v>349</v>
       </c>
@@ -17619,11 +17910,20 @@
       <c r="G324" t="s">
         <v>470</v>
       </c>
+      <c r="H324" t="s">
+        <v>9</v>
+      </c>
+      <c r="I324" t="s">
+        <v>55</v>
+      </c>
       <c r="J324" t="s">
         <v>521</v>
       </c>
-    </row>
-    <row r="325" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="M324" t="s">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="325" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
         <v>702</v>
       </c>
@@ -17642,11 +17942,20 @@
       <c r="G325" t="s">
         <v>24</v>
       </c>
+      <c r="H325" t="s">
+        <v>9</v>
+      </c>
+      <c r="I325" t="s">
+        <v>1522</v>
+      </c>
       <c r="J325" t="s">
         <v>521</v>
       </c>
-    </row>
-    <row r="326" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="M325" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="326" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
         <v>354</v>
       </c>
@@ -17665,11 +17974,17 @@
       <c r="G326" t="s">
         <v>1449</v>
       </c>
+      <c r="H326" t="s">
+        <v>9</v>
+      </c>
+      <c r="I326" t="s">
+        <v>1550</v>
+      </c>
       <c r="J326" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="327" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
         <v>357</v>
       </c>
@@ -17688,11 +18003,17 @@
       <c r="G327" t="s">
         <v>1449</v>
       </c>
+      <c r="H327" t="s">
+        <v>9</v>
+      </c>
+      <c r="I327" t="s">
+        <v>1550</v>
+      </c>
       <c r="J327" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="328" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
         <v>471</v>
       </c>
@@ -17711,11 +18032,17 @@
       <c r="G328" t="s">
         <v>1449</v>
       </c>
+      <c r="H328" t="s">
+        <v>9</v>
+      </c>
+      <c r="I328" t="s">
+        <v>282</v>
+      </c>
       <c r="J328" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="329" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
         <v>705</v>
       </c>
@@ -17732,13 +18059,22 @@
         <v>1997</v>
       </c>
       <c r="G329" t="s">
-        <v>1453</v>
+        <v>1452</v>
+      </c>
+      <c r="H329" t="s">
+        <v>9</v>
+      </c>
+      <c r="I329" t="s">
+        <v>1528</v>
       </c>
       <c r="J329" t="s">
         <v>708</v>
       </c>
-    </row>
-    <row r="330" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="M329" t="s">
+        <v>1529</v>
+      </c>
+    </row>
+    <row r="330" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
         <v>359</v>
       </c>
@@ -17757,11 +18093,20 @@
       <c r="G330" t="s">
         <v>38</v>
       </c>
+      <c r="H330" t="s">
+        <v>9</v>
+      </c>
+      <c r="I330" t="s">
+        <v>1531</v>
+      </c>
       <c r="J330" t="s">
         <v>573</v>
       </c>
-    </row>
-    <row r="331" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="M330" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="331" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
         <v>312</v>
       </c>
@@ -17778,13 +18123,22 @@
         <v>2023</v>
       </c>
       <c r="G331" t="s">
-        <v>1453</v>
+        <v>1452</v>
+      </c>
+      <c r="H331" t="s">
+        <v>9</v>
+      </c>
+      <c r="I331" t="s">
+        <v>1531</v>
       </c>
       <c r="J331" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="332" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="M331" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="332" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
         <v>362</v>
       </c>
@@ -17803,11 +18157,20 @@
       <c r="G332" t="s">
         <v>24</v>
       </c>
+      <c r="H332" t="s">
+        <v>9</v>
+      </c>
+      <c r="I332" t="s">
+        <v>1522</v>
+      </c>
       <c r="J332" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="333" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="M332" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="333" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
         <v>365</v>
       </c>
@@ -17826,11 +18189,17 @@
       <c r="G333" t="s">
         <v>1449</v>
       </c>
+      <c r="H333" t="s">
+        <v>9</v>
+      </c>
+      <c r="I333" t="s">
+        <v>1533</v>
+      </c>
       <c r="J333" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="334" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
         <v>367</v>
       </c>
@@ -17849,11 +18218,17 @@
       <c r="G334" t="s">
         <v>1449</v>
       </c>
+      <c r="H334" t="s">
+        <v>9</v>
+      </c>
+      <c r="I334" t="s">
+        <v>1533</v>
+      </c>
       <c r="J334" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="335" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
         <v>292</v>
       </c>
@@ -17867,16 +18242,22 @@
         <v>49</v>
       </c>
       <c r="F335">
-        <v>1987</v>
+        <v>1977</v>
       </c>
       <c r="G335" t="s">
-        <v>1477</v>
+        <v>1569</v>
+      </c>
+      <c r="H335" t="s">
+        <v>9</v>
+      </c>
+      <c r="I335" t="s">
+        <v>1534</v>
       </c>
       <c r="J335" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="336" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
         <v>369</v>
       </c>
@@ -17895,11 +18276,17 @@
       <c r="G336" t="s">
         <v>8</v>
       </c>
+      <c r="H336" t="s">
+        <v>9</v>
+      </c>
+      <c r="I336" t="s">
+        <v>1522</v>
+      </c>
       <c r="J336" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="337" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
         <v>372</v>
       </c>
@@ -17918,11 +18305,20 @@
       <c r="G337" t="s">
         <v>38</v>
       </c>
+      <c r="H337" t="s">
+        <v>39</v>
+      </c>
+      <c r="I337" t="s">
+        <v>79</v>
+      </c>
       <c r="J337" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="338" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="M337" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="338" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
         <v>376</v>
       </c>
@@ -17941,11 +18337,17 @@
       <c r="G338" t="s">
         <v>466</v>
       </c>
+      <c r="H338" t="s">
+        <v>9</v>
+      </c>
+      <c r="I338" t="s">
+        <v>55</v>
+      </c>
       <c r="J338" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="339" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
         <v>710</v>
       </c>
@@ -17964,11 +18366,17 @@
       <c r="G339" t="s">
         <v>466</v>
       </c>
+      <c r="H339" t="s">
+        <v>9</v>
+      </c>
+      <c r="I339" t="s">
+        <v>55</v>
+      </c>
       <c r="J339" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="340" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
         <v>377</v>
       </c>
@@ -17987,11 +18395,17 @@
       <c r="G340" t="s">
         <v>466</v>
       </c>
+      <c r="H340" t="s">
+        <v>9</v>
+      </c>
+      <c r="I340" t="s">
+        <v>55</v>
+      </c>
       <c r="J340" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="341" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
         <v>378</v>
       </c>
@@ -18010,11 +18424,17 @@
       <c r="G341" t="s">
         <v>466</v>
       </c>
+      <c r="H341" t="s">
+        <v>9</v>
+      </c>
+      <c r="I341" t="s">
+        <v>55</v>
+      </c>
       <c r="J341" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="342" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
         <v>379</v>
       </c>
@@ -18033,11 +18453,17 @@
       <c r="G342" t="s">
         <v>466</v>
       </c>
+      <c r="H342" t="s">
+        <v>9</v>
+      </c>
+      <c r="I342" t="s">
+        <v>55</v>
+      </c>
       <c r="J342" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="343" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
         <v>380</v>
       </c>
@@ -18056,11 +18482,17 @@
       <c r="G343" t="s">
         <v>466</v>
       </c>
+      <c r="H343" t="s">
+        <v>9</v>
+      </c>
+      <c r="I343" t="s">
+        <v>55</v>
+      </c>
       <c r="J343" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="344" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
         <v>381</v>
       </c>
@@ -18079,11 +18511,17 @@
       <c r="G344" t="s">
         <v>466</v>
       </c>
+      <c r="H344" t="s">
+        <v>9</v>
+      </c>
+      <c r="I344" t="s">
+        <v>55</v>
+      </c>
       <c r="J344" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="345" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
         <v>382</v>
       </c>
@@ -18102,11 +18540,17 @@
       <c r="G345" t="s">
         <v>466</v>
       </c>
+      <c r="H345" t="s">
+        <v>9</v>
+      </c>
+      <c r="I345" t="s">
+        <v>55</v>
+      </c>
       <c r="J345" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="346" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
         <v>383</v>
       </c>
@@ -18125,11 +18569,17 @@
       <c r="G346" t="s">
         <v>466</v>
       </c>
+      <c r="H346" t="s">
+        <v>9</v>
+      </c>
+      <c r="I346" t="s">
+        <v>55</v>
+      </c>
       <c r="J346" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="347" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
         <v>390</v>
       </c>
@@ -18148,11 +18598,17 @@
       <c r="G347" t="s">
         <v>466</v>
       </c>
+      <c r="H347" t="s">
+        <v>9</v>
+      </c>
+      <c r="I347" t="s">
+        <v>55</v>
+      </c>
       <c r="J347" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="348" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
         <v>384</v>
       </c>
@@ -18171,11 +18627,17 @@
       <c r="G348" t="s">
         <v>466</v>
       </c>
+      <c r="H348" t="s">
+        <v>9</v>
+      </c>
+      <c r="I348" t="s">
+        <v>55</v>
+      </c>
       <c r="J348" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="349" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
         <v>386</v>
       </c>
@@ -18194,11 +18656,17 @@
       <c r="G349" t="s">
         <v>466</v>
       </c>
+      <c r="H349" t="s">
+        <v>9</v>
+      </c>
+      <c r="I349" t="s">
+        <v>55</v>
+      </c>
       <c r="J349" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="350" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
         <v>387</v>
       </c>
@@ -18217,11 +18685,17 @@
       <c r="G350" t="s">
         <v>466</v>
       </c>
+      <c r="H350" t="s">
+        <v>9</v>
+      </c>
+      <c r="I350" t="s">
+        <v>55</v>
+      </c>
       <c r="J350" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="351" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
         <v>388</v>
       </c>
@@ -18240,11 +18714,17 @@
       <c r="G351" t="s">
         <v>466</v>
       </c>
+      <c r="H351" t="s">
+        <v>9</v>
+      </c>
+      <c r="I351" t="s">
+        <v>55</v>
+      </c>
       <c r="J351" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="352" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
         <v>389</v>
       </c>
@@ -18263,11 +18743,17 @@
       <c r="G352" t="s">
         <v>466</v>
       </c>
+      <c r="H352" t="s">
+        <v>9</v>
+      </c>
+      <c r="I352" t="s">
+        <v>55</v>
+      </c>
       <c r="J352" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="353" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
         <v>391</v>
       </c>
@@ -18284,13 +18770,19 @@
         <v>1997</v>
       </c>
       <c r="G353" t="s">
-        <v>1475</v>
+        <v>1473</v>
+      </c>
+      <c r="H353" t="s">
+        <v>9</v>
+      </c>
+      <c r="I353" t="s">
+        <v>1522</v>
       </c>
       <c r="J353" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="354" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
         <v>393</v>
       </c>
@@ -18307,13 +18799,19 @@
         <v>1997</v>
       </c>
       <c r="G354" t="s">
-        <v>1475</v>
+        <v>1473</v>
+      </c>
+      <c r="H354" t="s">
+        <v>9</v>
+      </c>
+      <c r="I354" t="s">
+        <v>1522</v>
       </c>
       <c r="J354" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="355" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
         <v>394</v>
       </c>
@@ -18330,13 +18828,19 @@
         <v>1997</v>
       </c>
       <c r="G355" t="s">
-        <v>1475</v>
+        <v>1473</v>
+      </c>
+      <c r="H355" t="s">
+        <v>9</v>
+      </c>
+      <c r="I355" t="s">
+        <v>1522</v>
       </c>
       <c r="J355" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="356" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
         <v>395</v>
       </c>
@@ -18353,13 +18857,19 @@
         <v>1997</v>
       </c>
       <c r="G356" t="s">
-        <v>1475</v>
+        <v>1473</v>
+      </c>
+      <c r="H356" t="s">
+        <v>9</v>
+      </c>
+      <c r="I356" t="s">
+        <v>1522</v>
       </c>
       <c r="J356" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="357" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
         <v>396</v>
       </c>
@@ -18376,13 +18886,19 @@
         <v>1997</v>
       </c>
       <c r="G357" t="s">
-        <v>1475</v>
+        <v>1473</v>
+      </c>
+      <c r="H357" t="s">
+        <v>9</v>
+      </c>
+      <c r="I357" t="s">
+        <v>1522</v>
       </c>
       <c r="J357" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="358" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
         <v>712</v>
       </c>
@@ -18399,13 +18915,19 @@
         <v>1999</v>
       </c>
       <c r="G358" t="s">
-        <v>1478</v>
+        <v>1475</v>
+      </c>
+      <c r="H358" t="s">
+        <v>9</v>
+      </c>
+      <c r="I358" t="s">
+        <v>1535</v>
       </c>
       <c r="J358" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="359" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
         <v>478</v>
       </c>
@@ -18422,13 +18944,19 @@
         <v>1995</v>
       </c>
       <c r="G359" t="s">
-        <v>1478</v>
+        <v>1475</v>
+      </c>
+      <c r="H359" t="s">
+        <v>9</v>
+      </c>
+      <c r="I359" t="s">
+        <v>1536</v>
       </c>
       <c r="J359" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="360" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
         <v>479</v>
       </c>
@@ -18445,13 +18973,19 @@
         <v>1995</v>
       </c>
       <c r="G360" t="s">
-        <v>1478</v>
+        <v>1475</v>
+      </c>
+      <c r="H360" t="s">
+        <v>9</v>
+      </c>
+      <c r="I360" t="s">
+        <v>1536</v>
       </c>
       <c r="J360" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="361" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
         <v>480</v>
       </c>
@@ -18468,13 +19002,19 @@
         <v>1995</v>
       </c>
       <c r="G361" t="s">
-        <v>1478</v>
+        <v>1475</v>
+      </c>
+      <c r="H361" t="s">
+        <v>9</v>
+      </c>
+      <c r="I361" t="s">
+        <v>1536</v>
       </c>
       <c r="J361" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="362" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
         <v>481</v>
       </c>
@@ -18491,13 +19031,19 @@
         <v>1995</v>
       </c>
       <c r="G362" t="s">
-        <v>1478</v>
+        <v>1475</v>
+      </c>
+      <c r="H362" t="s">
+        <v>9</v>
+      </c>
+      <c r="I362" t="s">
+        <v>1536</v>
       </c>
       <c r="J362" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="363" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
         <v>482</v>
       </c>
@@ -18514,13 +19060,19 @@
         <v>1995</v>
       </c>
       <c r="G363" t="s">
-        <v>1478</v>
+        <v>1475</v>
+      </c>
+      <c r="H363" t="s">
+        <v>9</v>
+      </c>
+      <c r="I363" t="s">
+        <v>1536</v>
       </c>
       <c r="J363" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="364" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
         <v>483</v>
       </c>
@@ -18537,13 +19089,19 @@
         <v>1995</v>
       </c>
       <c r="G364" t="s">
-        <v>1478</v>
+        <v>1475</v>
+      </c>
+      <c r="H364" t="s">
+        <v>9</v>
+      </c>
+      <c r="I364" t="s">
+        <v>1536</v>
       </c>
       <c r="J364" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="365" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
         <v>1371</v>
       </c>
@@ -18563,13 +19121,19 @@
         <v>2021</v>
       </c>
       <c r="G365" t="s">
-        <v>1479</v>
+        <v>1476</v>
+      </c>
+      <c r="H365" t="s">
+        <v>9</v>
+      </c>
+      <c r="I365" t="s">
+        <v>1536</v>
       </c>
       <c r="J365" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="366" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
         <v>1373</v>
       </c>
@@ -18589,13 +19153,19 @@
         <v>2021</v>
       </c>
       <c r="G366" t="s">
-        <v>1480</v>
+        <v>1477</v>
+      </c>
+      <c r="H366" t="s">
+        <v>9</v>
+      </c>
+      <c r="I366" t="s">
+        <v>1536</v>
       </c>
       <c r="J366" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="367" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
         <v>1374</v>
       </c>
@@ -18615,13 +19185,22 @@
         <v>2018</v>
       </c>
       <c r="G367" t="s">
-        <v>1480</v>
+        <v>1477</v>
+      </c>
+      <c r="H367" t="s">
+        <v>9</v>
+      </c>
+      <c r="I367" t="s">
+        <v>1536</v>
       </c>
       <c r="J367" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="368" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="M367" t="s">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="368" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
         <v>484</v>
       </c>
@@ -18638,7 +19217,13 @@
         <v>1998</v>
       </c>
       <c r="G368" t="s">
-        <v>1478</v>
+        <v>1475</v>
+      </c>
+      <c r="H368" t="s">
+        <v>9</v>
+      </c>
+      <c r="I368" t="s">
+        <v>1536</v>
       </c>
       <c r="J368" t="s">
         <v>285</v>
@@ -18661,7 +19246,13 @@
         <v>1998</v>
       </c>
       <c r="G369" t="s">
-        <v>1478</v>
+        <v>1475</v>
+      </c>
+      <c r="H369" t="s">
+        <v>9</v>
+      </c>
+      <c r="I369" t="s">
+        <v>1536</v>
       </c>
       <c r="J369" t="s">
         <v>285</v>
@@ -18684,7 +19275,13 @@
         <v>1998</v>
       </c>
       <c r="G370" t="s">
-        <v>1478</v>
+        <v>1475</v>
+      </c>
+      <c r="H370" t="s">
+        <v>9</v>
+      </c>
+      <c r="I370" t="s">
+        <v>1536</v>
       </c>
       <c r="J370" t="s">
         <v>285</v>
@@ -18707,7 +19304,13 @@
         <v>1998</v>
       </c>
       <c r="G371" t="s">
-        <v>1478</v>
+        <v>1475</v>
+      </c>
+      <c r="H371" t="s">
+        <v>9</v>
+      </c>
+      <c r="I371" t="s">
+        <v>1536</v>
       </c>
       <c r="J371" t="s">
         <v>285</v>
@@ -18730,7 +19333,13 @@
         <v>1998</v>
       </c>
       <c r="G372" t="s">
-        <v>1478</v>
+        <v>1475</v>
+      </c>
+      <c r="H372" t="s">
+        <v>9</v>
+      </c>
+      <c r="I372" t="s">
+        <v>1536</v>
       </c>
       <c r="J372" t="s">
         <v>285</v>
@@ -18753,7 +19362,13 @@
         <v>2023</v>
       </c>
       <c r="G373" t="s">
-        <v>1478</v>
+        <v>1475</v>
+      </c>
+      <c r="H373" t="s">
+        <v>9</v>
+      </c>
+      <c r="I373" t="s">
+        <v>1536</v>
       </c>
       <c r="J373" t="s">
         <v>285</v>
@@ -18782,7 +19397,13 @@
         <v>2021</v>
       </c>
       <c r="G374" t="s">
-        <v>1478</v>
+        <v>1475</v>
+      </c>
+      <c r="H374" t="s">
+        <v>9</v>
+      </c>
+      <c r="I374" t="s">
+        <v>1536</v>
       </c>
       <c r="J374" t="s">
         <v>285</v>
@@ -18808,7 +19429,13 @@
         <v>2005</v>
       </c>
       <c r="G375" t="s">
-        <v>1457</v>
+        <v>1456</v>
+      </c>
+      <c r="H375" t="s">
+        <v>9</v>
+      </c>
+      <c r="I375" t="s">
+        <v>1536</v>
       </c>
       <c r="J375" t="s">
         <v>131</v>
@@ -18831,7 +19458,13 @@
         <v>1981</v>
       </c>
       <c r="G376" t="s">
-        <v>1453</v>
+        <v>1452</v>
+      </c>
+      <c r="H376" t="s">
+        <v>9</v>
+      </c>
+      <c r="I376" t="s">
+        <v>1533</v>
       </c>
       <c r="J376" t="s">
         <v>282</v>
@@ -18859,6 +19492,12 @@
       <c r="G377" t="s">
         <v>1449</v>
       </c>
+      <c r="H377" t="s">
+        <v>9</v>
+      </c>
+      <c r="I377" t="s">
+        <v>1537</v>
+      </c>
       <c r="J377" t="s">
         <v>131</v>
       </c>
@@ -18882,6 +19521,12 @@
       <c r="G378" t="s">
         <v>1449</v>
       </c>
+      <c r="H378" t="s">
+        <v>9</v>
+      </c>
+      <c r="I378" t="s">
+        <v>10</v>
+      </c>
       <c r="J378" t="s">
         <v>131</v>
       </c>
@@ -18903,7 +19548,13 @@
         <v>2009</v>
       </c>
       <c r="G379" t="s">
-        <v>1453</v>
+        <v>1452</v>
+      </c>
+      <c r="H379" t="s">
+        <v>9</v>
+      </c>
+      <c r="I379" t="s">
+        <v>1522</v>
       </c>
       <c r="J379" t="s">
         <v>131</v>
@@ -18928,6 +19579,12 @@
       <c r="G380" t="s">
         <v>80</v>
       </c>
+      <c r="H380" t="s">
+        <v>9</v>
+      </c>
+      <c r="I380" t="s">
+        <v>1540</v>
+      </c>
       <c r="J380" t="s">
         <v>285</v>
       </c>
@@ -18951,6 +19608,12 @@
       <c r="G381" t="s">
         <v>80</v>
       </c>
+      <c r="H381" t="s">
+        <v>9</v>
+      </c>
+      <c r="I381" t="s">
+        <v>1540</v>
+      </c>
       <c r="J381" t="s">
         <v>131</v>
       </c>
@@ -18974,6 +19637,12 @@
       <c r="G382" t="s">
         <v>80</v>
       </c>
+      <c r="H382" t="s">
+        <v>9</v>
+      </c>
+      <c r="I382" t="s">
+        <v>1540</v>
+      </c>
       <c r="J382" t="s">
         <v>131</v>
       </c>
@@ -18997,6 +19666,12 @@
       <c r="G383" t="s">
         <v>80</v>
       </c>
+      <c r="H383" t="s">
+        <v>9</v>
+      </c>
+      <c r="I383" t="s">
+        <v>1540</v>
+      </c>
       <c r="J383" t="s">
         <v>282</v>
       </c>
@@ -19018,7 +19693,13 @@
         <v>2014</v>
       </c>
       <c r="G384" t="s">
-        <v>1461</v>
+        <v>1460</v>
+      </c>
+      <c r="H384" t="s">
+        <v>9</v>
+      </c>
+      <c r="I384" t="s">
+        <v>1540</v>
       </c>
       <c r="J384" t="s">
         <v>131</v>
@@ -19041,7 +19722,13 @@
         <v>1991</v>
       </c>
       <c r="G385" t="s">
-        <v>1481</v>
+        <v>1478</v>
+      </c>
+      <c r="H385" t="s">
+        <v>1508</v>
+      </c>
+      <c r="I385" t="s">
+        <v>1539</v>
       </c>
       <c r="J385" t="s">
         <v>568</v>
@@ -19064,7 +19751,13 @@
         <v>1991</v>
       </c>
       <c r="G386" t="s">
-        <v>1481</v>
+        <v>1478</v>
+      </c>
+      <c r="H386" t="s">
+        <v>1508</v>
+      </c>
+      <c r="I386" t="s">
+        <v>1539</v>
       </c>
       <c r="J386" t="s">
         <v>568</v>
@@ -19087,7 +19780,13 @@
         <v>1991</v>
       </c>
       <c r="G387" t="s">
-        <v>1481</v>
+        <v>1478</v>
+      </c>
+      <c r="H387" t="s">
+        <v>1508</v>
+      </c>
+      <c r="I387" t="s">
+        <v>1539</v>
       </c>
       <c r="J387" t="s">
         <v>568</v>
@@ -19110,7 +19809,13 @@
         <v>1991</v>
       </c>
       <c r="G388" t="s">
-        <v>1481</v>
+        <v>1478</v>
+      </c>
+      <c r="H388" t="s">
+        <v>1508</v>
+      </c>
+      <c r="I388" t="s">
+        <v>1539</v>
       </c>
       <c r="J388" t="s">
         <v>568</v>
@@ -19133,7 +19838,13 @@
         <v>1991</v>
       </c>
       <c r="G389" t="s">
-        <v>1481</v>
+        <v>1478</v>
+      </c>
+      <c r="H389" t="s">
+        <v>1508</v>
+      </c>
+      <c r="I389" t="s">
+        <v>1539</v>
       </c>
       <c r="J389" t="s">
         <v>568</v>
@@ -19156,7 +19867,13 @@
         <v>1991</v>
       </c>
       <c r="G390" t="s">
-        <v>1481</v>
+        <v>1478</v>
+      </c>
+      <c r="H390" t="s">
+        <v>1508</v>
+      </c>
+      <c r="I390" t="s">
+        <v>1539</v>
       </c>
       <c r="J390" t="s">
         <v>568</v>
@@ -19170,7 +19887,7 @@
         <v>0.12291666666666666</v>
       </c>
       <c r="C391" t="s">
-        <v>1482</v>
+        <v>1479</v>
       </c>
       <c r="E391" t="s">
         <v>730</v>
@@ -19179,7 +19896,13 @@
         <v>2010</v>
       </c>
       <c r="G391" t="s">
-        <v>1483</v>
+        <v>1480</v>
+      </c>
+      <c r="H391" t="s">
+        <v>9</v>
+      </c>
+      <c r="I391" t="s">
+        <v>55</v>
       </c>
       <c r="J391" t="s">
         <v>731</v>
@@ -19204,8 +19927,17 @@
       <c r="G392" t="s">
         <v>470</v>
       </c>
+      <c r="H392" t="s">
+        <v>9</v>
+      </c>
+      <c r="I392" t="s">
+        <v>55</v>
+      </c>
       <c r="J392" t="s">
         <v>131</v>
+      </c>
+      <c r="M392" t="s">
+        <v>1526</v>
       </c>
     </row>
     <row r="393" spans="1:16" x14ac:dyDescent="0.2">
@@ -19227,6 +19959,12 @@
       <c r="G393" t="s">
         <v>132</v>
       </c>
+      <c r="H393" t="s">
+        <v>9</v>
+      </c>
+      <c r="I393" t="s">
+        <v>1522</v>
+      </c>
       <c r="J393" t="s">
         <v>131</v>
       </c>
@@ -19248,7 +19986,13 @@
         <v>1997</v>
       </c>
       <c r="G394" t="s">
-        <v>1461</v>
+        <v>1460</v>
+      </c>
+      <c r="H394" t="s">
+        <v>9</v>
+      </c>
+      <c r="I394" t="s">
+        <v>1522</v>
       </c>
       <c r="J394" t="s">
         <v>55</v>
@@ -19271,7 +20015,13 @@
         <v>1997</v>
       </c>
       <c r="G395" t="s">
-        <v>1461</v>
+        <v>1460</v>
+      </c>
+      <c r="H395" t="s">
+        <v>9</v>
+      </c>
+      <c r="I395" t="s">
+        <v>1522</v>
       </c>
       <c r="J395" t="s">
         <v>55</v>
@@ -19294,13 +20044,19 @@
         <v>2002</v>
       </c>
       <c r="G396" t="s">
-        <v>1461</v>
+        <v>1460</v>
+      </c>
+      <c r="H396" t="s">
+        <v>9</v>
+      </c>
+      <c r="I396" t="s">
+        <v>1522</v>
       </c>
       <c r="J396" t="s">
         <v>131</v>
       </c>
       <c r="P396" t="s">
-        <v>1515</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="397" spans="1:16" x14ac:dyDescent="0.2">
@@ -19320,13 +20076,19 @@
         <v>2000</v>
       </c>
       <c r="G397" t="s">
-        <v>1461</v>
+        <v>1460</v>
+      </c>
+      <c r="H397" t="s">
+        <v>9</v>
+      </c>
+      <c r="I397" t="s">
+        <v>1522</v>
       </c>
       <c r="J397" t="s">
         <v>131</v>
       </c>
       <c r="P397" t="s">
-        <v>1516</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="398" spans="1:16" x14ac:dyDescent="0.2">
@@ -19346,7 +20108,13 @@
         <v>2015</v>
       </c>
       <c r="G398" t="s">
-        <v>1453</v>
+        <v>1452</v>
+      </c>
+      <c r="H398" t="s">
+        <v>9</v>
+      </c>
+      <c r="I398" t="s">
+        <v>55</v>
       </c>
       <c r="J398" t="s">
         <v>131</v>
@@ -19369,7 +20137,13 @@
         <v>2016</v>
       </c>
       <c r="G399" t="s">
-        <v>1453</v>
+        <v>1452</v>
+      </c>
+      <c r="H399" t="s">
+        <v>9</v>
+      </c>
+      <c r="I399" t="s">
+        <v>55</v>
       </c>
       <c r="J399" t="s">
         <v>131</v>
@@ -19392,7 +20166,13 @@
         <v>2011</v>
       </c>
       <c r="G400" t="s">
-        <v>1453</v>
+        <v>1452</v>
+      </c>
+      <c r="H400" t="s">
+        <v>9</v>
+      </c>
+      <c r="I400" t="s">
+        <v>1536</v>
       </c>
       <c r="J400" t="s">
         <v>131</v>
@@ -19418,7 +20198,13 @@
         <v>2023</v>
       </c>
       <c r="G401" t="s">
-        <v>1484</v>
+        <v>1481</v>
+      </c>
+      <c r="H401" t="s">
+        <v>9</v>
+      </c>
+      <c r="I401" t="s">
+        <v>1536</v>
       </c>
       <c r="J401" t="s">
         <v>131</v>
@@ -19441,7 +20227,13 @@
         <v>2004</v>
       </c>
       <c r="G402" t="s">
-        <v>1485</v>
+        <v>1482</v>
+      </c>
+      <c r="H402" t="s">
+        <v>9</v>
+      </c>
+      <c r="I402" t="s">
+        <v>1540</v>
       </c>
       <c r="J402" t="s">
         <v>282</v>
@@ -19464,7 +20256,13 @@
         <v>2004</v>
       </c>
       <c r="G403" t="s">
-        <v>1485</v>
+        <v>1482</v>
+      </c>
+      <c r="H403" t="s">
+        <v>9</v>
+      </c>
+      <c r="I403" t="s">
+        <v>1540</v>
       </c>
       <c r="J403" t="s">
         <v>282</v>
@@ -19487,7 +20285,13 @@
         <v>2004</v>
       </c>
       <c r="G404" t="s">
-        <v>1485</v>
+        <v>1482</v>
+      </c>
+      <c r="H404" t="s">
+        <v>9</v>
+      </c>
+      <c r="I404" t="s">
+        <v>1540</v>
       </c>
       <c r="J404" t="s">
         <v>282</v>
@@ -19513,7 +20317,13 @@
         <v>2021</v>
       </c>
       <c r="G405" t="s">
-        <v>1484</v>
+        <v>1481</v>
+      </c>
+      <c r="H405" t="s">
+        <v>9</v>
+      </c>
+      <c r="I405" t="s">
+        <v>1522</v>
       </c>
       <c r="J405" t="s">
         <v>131</v>
@@ -19541,6 +20351,12 @@
       <c r="G406" t="s">
         <v>466</v>
       </c>
+      <c r="H406" t="s">
+        <v>39</v>
+      </c>
+      <c r="I406" t="s">
+        <v>79</v>
+      </c>
       <c r="J406" t="s">
         <v>282</v>
       </c>
@@ -19567,6 +20383,12 @@
       <c r="G407" t="s">
         <v>1449</v>
       </c>
+      <c r="H407" t="s">
+        <v>9</v>
+      </c>
+      <c r="I407" t="s">
+        <v>676</v>
+      </c>
       <c r="J407" t="s">
         <v>282</v>
       </c>
@@ -19590,6 +20412,12 @@
       <c r="G408" t="s">
         <v>1449</v>
       </c>
+      <c r="H408" t="s">
+        <v>9</v>
+      </c>
+      <c r="I408" t="s">
+        <v>676</v>
+      </c>
       <c r="J408" t="s">
         <v>282</v>
       </c>
@@ -19613,6 +20441,12 @@
       <c r="G409" t="s">
         <v>89</v>
       </c>
+      <c r="H409" t="s">
+        <v>1508</v>
+      </c>
+      <c r="I409" t="s">
+        <v>1542</v>
+      </c>
       <c r="J409" t="s">
         <v>14</v>
       </c>
@@ -19636,6 +20470,12 @@
       <c r="G410" t="s">
         <v>89</v>
       </c>
+      <c r="H410" t="s">
+        <v>1508</v>
+      </c>
+      <c r="I410" t="s">
+        <v>1542</v>
+      </c>
       <c r="J410" t="s">
         <v>14</v>
       </c>
@@ -19659,6 +20499,12 @@
       <c r="G411" t="s">
         <v>89</v>
       </c>
+      <c r="H411" t="s">
+        <v>1508</v>
+      </c>
+      <c r="I411" t="s">
+        <v>1542</v>
+      </c>
       <c r="J411" t="s">
         <v>14</v>
       </c>
@@ -19682,6 +20528,12 @@
       <c r="G412" t="s">
         <v>89</v>
       </c>
+      <c r="H412" t="s">
+        <v>1508</v>
+      </c>
+      <c r="I412" t="s">
+        <v>1542</v>
+      </c>
       <c r="J412" t="s">
         <v>14</v>
       </c>
@@ -19705,6 +20557,12 @@
       <c r="G413" t="s">
         <v>89</v>
       </c>
+      <c r="H413" t="s">
+        <v>1508</v>
+      </c>
+      <c r="I413" t="s">
+        <v>1542</v>
+      </c>
       <c r="J413" t="s">
         <v>14</v>
       </c>
@@ -19728,6 +20586,12 @@
       <c r="G414" t="s">
         <v>89</v>
       </c>
+      <c r="H414" t="s">
+        <v>1508</v>
+      </c>
+      <c r="I414" t="s">
+        <v>1542</v>
+      </c>
       <c r="J414" t="s">
         <v>14</v>
       </c>
@@ -19751,6 +20615,12 @@
       <c r="G415" t="s">
         <v>89</v>
       </c>
+      <c r="H415" t="s">
+        <v>1508</v>
+      </c>
+      <c r="I415" t="s">
+        <v>1542</v>
+      </c>
       <c r="J415" t="s">
         <v>14</v>
       </c>
@@ -19774,6 +20644,12 @@
       <c r="G416" t="s">
         <v>89</v>
       </c>
+      <c r="H416" t="s">
+        <v>1508</v>
+      </c>
+      <c r="I416" t="s">
+        <v>1542</v>
+      </c>
       <c r="J416" t="s">
         <v>14</v>
       </c>
@@ -19797,6 +20673,12 @@
       <c r="G417" t="s">
         <v>89</v>
       </c>
+      <c r="H417" t="s">
+        <v>1508</v>
+      </c>
+      <c r="I417" t="s">
+        <v>1542</v>
+      </c>
       <c r="J417" t="s">
         <v>14</v>
       </c>
@@ -19820,6 +20702,12 @@
       <c r="G418" t="s">
         <v>89</v>
       </c>
+      <c r="H418" t="s">
+        <v>1508</v>
+      </c>
+      <c r="I418" t="s">
+        <v>1542</v>
+      </c>
       <c r="J418" t="s">
         <v>14</v>
       </c>
@@ -19843,6 +20731,12 @@
       <c r="G419" t="s">
         <v>89</v>
       </c>
+      <c r="H419" t="s">
+        <v>1508</v>
+      </c>
+      <c r="I419" t="s">
+        <v>1542</v>
+      </c>
       <c r="J419" t="s">
         <v>14</v>
       </c>
@@ -19866,6 +20760,12 @@
       <c r="G420" t="s">
         <v>89</v>
       </c>
+      <c r="H420" t="s">
+        <v>1508</v>
+      </c>
+      <c r="I420" t="s">
+        <v>1542</v>
+      </c>
       <c r="J420" t="s">
         <v>14</v>
       </c>
@@ -19889,6 +20789,12 @@
       <c r="G421" t="s">
         <v>89</v>
       </c>
+      <c r="H421" t="s">
+        <v>1508</v>
+      </c>
+      <c r="I421" t="s">
+        <v>1542</v>
+      </c>
       <c r="J421" t="s">
         <v>14</v>
       </c>
@@ -19912,6 +20818,12 @@
       <c r="G422" t="s">
         <v>89</v>
       </c>
+      <c r="H422" t="s">
+        <v>1508</v>
+      </c>
+      <c r="I422" t="s">
+        <v>1542</v>
+      </c>
       <c r="J422" t="s">
         <v>14</v>
       </c>
@@ -19935,6 +20847,12 @@
       <c r="G423" t="s">
         <v>89</v>
       </c>
+      <c r="H423" t="s">
+        <v>1541</v>
+      </c>
+      <c r="I423" t="s">
+        <v>1543</v>
+      </c>
       <c r="J423" t="s">
         <v>627</v>
       </c>
@@ -19958,6 +20876,12 @@
       <c r="G424" t="s">
         <v>89</v>
       </c>
+      <c r="H424" t="s">
+        <v>1508</v>
+      </c>
+      <c r="I424" t="s">
+        <v>1543</v>
+      </c>
       <c r="J424" t="s">
         <v>629</v>
       </c>
@@ -19981,6 +20905,12 @@
       <c r="G425" t="s">
         <v>1449</v>
       </c>
+      <c r="H425" t="s">
+        <v>9</v>
+      </c>
+      <c r="I425" t="s">
+        <v>55</v>
+      </c>
       <c r="J425" t="s">
         <v>131</v>
       </c>
@@ -20004,6 +20934,12 @@
       <c r="G426" t="s">
         <v>1449</v>
       </c>
+      <c r="H426" t="s">
+        <v>9</v>
+      </c>
+      <c r="I426" t="s">
+        <v>55</v>
+      </c>
       <c r="J426" t="s">
         <v>131</v>
       </c>
@@ -20027,6 +20963,12 @@
       <c r="G427" t="s">
         <v>1449</v>
       </c>
+      <c r="H427" t="s">
+        <v>9</v>
+      </c>
+      <c r="I427" t="s">
+        <v>55</v>
+      </c>
       <c r="J427" t="s">
         <v>131</v>
       </c>
@@ -20048,10 +20990,19 @@
         <v>2007</v>
       </c>
       <c r="G428" t="s">
-        <v>1486</v>
+        <v>1483</v>
+      </c>
+      <c r="H428" t="s">
+        <v>9</v>
+      </c>
+      <c r="I428" t="s">
+        <v>1546</v>
       </c>
       <c r="J428" t="s">
         <v>568</v>
+      </c>
+      <c r="L428" t="s">
+        <v>1544</v>
       </c>
     </row>
     <row r="429" spans="1:12" x14ac:dyDescent="0.2">
@@ -20074,13 +21025,19 @@
         <v>2018</v>
       </c>
       <c r="G429" t="s">
-        <v>1463</v>
+        <v>1462</v>
+      </c>
+      <c r="H429" t="s">
+        <v>9</v>
+      </c>
+      <c r="I429" t="s">
+        <v>55</v>
       </c>
       <c r="J429" t="s">
         <v>131</v>
       </c>
       <c r="L429" t="s">
-        <v>1511</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="430" spans="1:12" x14ac:dyDescent="0.2">
@@ -20100,7 +21057,13 @@
         <v>2018</v>
       </c>
       <c r="G430" t="s">
-        <v>1461</v>
+        <v>1460</v>
+      </c>
+      <c r="H430" t="s">
+        <v>9</v>
+      </c>
+      <c r="I430" t="s">
+        <v>55</v>
       </c>
       <c r="J430" t="s">
         <v>131</v>
@@ -20123,7 +21086,13 @@
         <v>2019</v>
       </c>
       <c r="G431" t="s">
-        <v>1461</v>
+        <v>1460</v>
+      </c>
+      <c r="H431" t="s">
+        <v>9</v>
+      </c>
+      <c r="I431" t="s">
+        <v>55</v>
       </c>
       <c r="J431" t="s">
         <v>131</v>
@@ -20146,13 +21115,19 @@
         <v>2019</v>
       </c>
       <c r="G432" t="s">
-        <v>1461</v>
+        <v>1460</v>
+      </c>
+      <c r="H432" t="s">
+        <v>9</v>
+      </c>
+      <c r="I432" t="s">
+        <v>55</v>
       </c>
       <c r="J432" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="433" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
         <v>758</v>
       </c>
@@ -20169,13 +21144,19 @@
         <v>2019</v>
       </c>
       <c r="G433" t="s">
-        <v>1461</v>
+        <v>1460</v>
+      </c>
+      <c r="H433" t="s">
+        <v>9</v>
+      </c>
+      <c r="I433" t="s">
+        <v>55</v>
       </c>
       <c r="J433" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="434" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A434" t="s">
         <v>759</v>
       </c>
@@ -20192,13 +21173,19 @@
         <v>2019</v>
       </c>
       <c r="G434" t="s">
-        <v>1461</v>
+        <v>1460</v>
+      </c>
+      <c r="H434" t="s">
+        <v>9</v>
+      </c>
+      <c r="I434" t="s">
+        <v>55</v>
       </c>
       <c r="J434" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="435" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A435" t="s">
         <v>760</v>
       </c>
@@ -20215,13 +21202,19 @@
         <v>2019</v>
       </c>
       <c r="G435" t="s">
-        <v>1461</v>
+        <v>1460</v>
+      </c>
+      <c r="H435" t="s">
+        <v>9</v>
+      </c>
+      <c r="I435" t="s">
+        <v>55</v>
       </c>
       <c r="J435" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="436" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A436" t="s">
         <v>761</v>
       </c>
@@ -20238,13 +21231,19 @@
         <v>2019</v>
       </c>
       <c r="G436" t="s">
-        <v>1461</v>
+        <v>1460</v>
+      </c>
+      <c r="H436" t="s">
+        <v>9</v>
+      </c>
+      <c r="I436" t="s">
+        <v>55</v>
       </c>
       <c r="J436" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="437" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A437" t="s">
         <v>762</v>
       </c>
@@ -20261,13 +21260,19 @@
         <v>2019</v>
       </c>
       <c r="G437" t="s">
-        <v>1461</v>
+        <v>1460</v>
+      </c>
+      <c r="H437" t="s">
+        <v>9</v>
+      </c>
+      <c r="I437" t="s">
+        <v>55</v>
       </c>
       <c r="J437" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="438" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A438" t="s">
         <v>763</v>
       </c>
@@ -20284,13 +21289,19 @@
         <v>2019</v>
       </c>
       <c r="G438" t="s">
-        <v>1461</v>
+        <v>1460</v>
+      </c>
+      <c r="H438" t="s">
+        <v>9</v>
+      </c>
+      <c r="I438" t="s">
+        <v>55</v>
       </c>
       <c r="J438" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="439" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A439" t="s">
         <v>764</v>
       </c>
@@ -20307,13 +21318,22 @@
         <v>2011</v>
       </c>
       <c r="G439" t="s">
-        <v>1487</v>
+        <v>1484</v>
+      </c>
+      <c r="H439" t="s">
+        <v>9</v>
+      </c>
+      <c r="I439" t="s">
+        <v>55</v>
       </c>
       <c r="J439" t="s">
         <v>568</v>
       </c>
-    </row>
-    <row r="440" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="P439" t="s">
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="440" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A440" t="s">
         <v>767</v>
       </c>
@@ -20330,13 +21350,19 @@
         <v>2016</v>
       </c>
       <c r="G440" t="s">
-        <v>1488</v>
+        <v>1485</v>
+      </c>
+      <c r="H440" t="s">
+        <v>9</v>
+      </c>
+      <c r="I440" t="s">
+        <v>55</v>
       </c>
       <c r="J440" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="441" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
         <v>770</v>
       </c>
@@ -20353,13 +21379,19 @@
         <v>2016</v>
       </c>
       <c r="G441" t="s">
-        <v>1488</v>
+        <v>1485</v>
+      </c>
+      <c r="H441" t="s">
+        <v>9</v>
+      </c>
+      <c r="I441" t="s">
+        <v>55</v>
       </c>
       <c r="J441" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="442" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
         <v>771</v>
       </c>
@@ -20376,13 +21408,19 @@
         <v>2016</v>
       </c>
       <c r="G442" t="s">
-        <v>1488</v>
+        <v>1485</v>
+      </c>
+      <c r="H442" t="s">
+        <v>9</v>
+      </c>
+      <c r="I442" t="s">
+        <v>55</v>
       </c>
       <c r="J442" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="443" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
         <v>772</v>
       </c>
@@ -20399,13 +21437,19 @@
         <v>2011</v>
       </c>
       <c r="G443" t="s">
-        <v>1488</v>
+        <v>1485</v>
+      </c>
+      <c r="H443" t="s">
+        <v>9</v>
+      </c>
+      <c r="I443" t="s">
+        <v>55</v>
       </c>
       <c r="J443" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="444" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A444" t="s">
         <v>774</v>
       </c>
@@ -20422,13 +21466,19 @@
         <v>2011</v>
       </c>
       <c r="G444" t="s">
-        <v>1488</v>
+        <v>1485</v>
+      </c>
+      <c r="H444" t="s">
+        <v>9</v>
+      </c>
+      <c r="I444" t="s">
+        <v>55</v>
       </c>
       <c r="J444" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="445" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
         <v>775</v>
       </c>
@@ -20445,13 +21495,19 @@
         <v>2011</v>
       </c>
       <c r="G445" t="s">
-        <v>1488</v>
+        <v>1485</v>
+      </c>
+      <c r="H445" t="s">
+        <v>9</v>
+      </c>
+      <c r="I445" t="s">
+        <v>55</v>
       </c>
       <c r="J445" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="446" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
         <v>776</v>
       </c>
@@ -20468,13 +21524,19 @@
         <v>2011</v>
       </c>
       <c r="G446" t="s">
-        <v>1488</v>
+        <v>1485</v>
+      </c>
+      <c r="H446" t="s">
+        <v>9</v>
+      </c>
+      <c r="I446" t="s">
+        <v>55</v>
       </c>
       <c r="J446" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="447" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A447" t="s">
         <v>777</v>
       </c>
@@ -20491,13 +21553,19 @@
         <v>2008</v>
       </c>
       <c r="G447" t="s">
-        <v>1488</v>
+        <v>1485</v>
+      </c>
+      <c r="H447" t="s">
+        <v>9</v>
+      </c>
+      <c r="I447" t="s">
+        <v>55</v>
       </c>
       <c r="J447" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="448" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
         <v>779</v>
       </c>
@@ -20514,13 +21582,19 @@
         <v>2008</v>
       </c>
       <c r="G448" t="s">
-        <v>1488</v>
+        <v>1485</v>
+      </c>
+      <c r="H448" t="s">
+        <v>9</v>
+      </c>
+      <c r="I448" t="s">
+        <v>55</v>
       </c>
       <c r="J448" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="449" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
         <v>780</v>
       </c>
@@ -20540,13 +21614,19 @@
         <v>2006</v>
       </c>
       <c r="G449" t="s">
-        <v>1489</v>
+        <v>1486</v>
+      </c>
+      <c r="H449" t="s">
+        <v>9</v>
+      </c>
+      <c r="I449" t="s">
+        <v>1546</v>
       </c>
       <c r="J449" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="450" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
         <v>783</v>
       </c>
@@ -20566,13 +21646,19 @@
         <v>2006</v>
       </c>
       <c r="G450" t="s">
-        <v>1489</v>
+        <v>1486</v>
+      </c>
+      <c r="H450" t="s">
+        <v>9</v>
+      </c>
+      <c r="I450" t="s">
+        <v>1546</v>
       </c>
       <c r="J450" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="451" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
         <v>784</v>
       </c>
@@ -20591,11 +21677,17 @@
       <c r="G451" t="s">
         <v>38</v>
       </c>
+      <c r="H451" t="s">
+        <v>39</v>
+      </c>
+      <c r="I451" t="s">
+        <v>1547</v>
+      </c>
       <c r="J451" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="452" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
         <v>787</v>
       </c>
@@ -20614,11 +21706,17 @@
       <c r="G452" t="s">
         <v>38</v>
       </c>
+      <c r="H452" t="s">
+        <v>39</v>
+      </c>
+      <c r="I452" t="s">
+        <v>1522</v>
+      </c>
       <c r="J452" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="453" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A453" t="s">
         <v>788</v>
       </c>
@@ -20637,11 +21735,20 @@
       <c r="G453" t="s">
         <v>38</v>
       </c>
+      <c r="H453" t="s">
+        <v>39</v>
+      </c>
+      <c r="I453" t="s">
+        <v>1547</v>
+      </c>
       <c r="J453" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="454" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="M453" t="s">
+        <v>1548</v>
+      </c>
+    </row>
+    <row r="454" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
         <v>789</v>
       </c>
@@ -20660,11 +21767,17 @@
       <c r="G454" t="s">
         <v>1449</v>
       </c>
+      <c r="H454" t="s">
+        <v>9</v>
+      </c>
+      <c r="I454" t="s">
+        <v>1540</v>
+      </c>
       <c r="J454" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="455" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A455" t="s">
         <v>791</v>
       </c>
@@ -20681,13 +21794,19 @@
         <v>2013</v>
       </c>
       <c r="G455" t="s">
-        <v>1461</v>
+        <v>1460</v>
+      </c>
+      <c r="H455" t="s">
+        <v>9</v>
+      </c>
+      <c r="I455" t="s">
+        <v>568</v>
       </c>
       <c r="J455" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="456" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A456" t="s">
         <v>794</v>
       </c>
@@ -20706,11 +21825,17 @@
       <c r="G456" t="s">
         <v>1449</v>
       </c>
+      <c r="H456" t="s">
+        <v>9</v>
+      </c>
+      <c r="I456" t="s">
+        <v>1535</v>
+      </c>
       <c r="J456" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="457" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A457" t="s">
         <v>940</v>
       </c>
@@ -20732,11 +21857,20 @@
       <c r="G457" t="s">
         <v>8</v>
       </c>
+      <c r="H457" t="s">
+        <v>9</v>
+      </c>
+      <c r="I457" t="s">
+        <v>1549</v>
+      </c>
       <c r="J457" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="458" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="M457" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="458" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A458" t="s">
         <v>800</v>
       </c>
@@ -20755,11 +21889,17 @@
       <c r="G458" t="s">
         <v>1449</v>
       </c>
+      <c r="H458" t="s">
+        <v>9</v>
+      </c>
+      <c r="I458" t="s">
+        <v>1550</v>
+      </c>
       <c r="J458" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="459" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A459" t="s">
         <v>803</v>
       </c>
@@ -20776,13 +21916,19 @@
         <v>1972</v>
       </c>
       <c r="G459" t="s">
-        <v>1461</v>
+        <v>1460</v>
+      </c>
+      <c r="H459" t="s">
+        <v>9</v>
+      </c>
+      <c r="I459" t="s">
+        <v>1551</v>
       </c>
       <c r="J459" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="460" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A460" t="s">
         <v>806</v>
       </c>
@@ -20801,11 +21947,17 @@
       <c r="G460" t="s">
         <v>1449</v>
       </c>
+      <c r="H460" t="s">
+        <v>9</v>
+      </c>
+      <c r="I460" t="s">
+        <v>1552</v>
+      </c>
       <c r="J460" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="461" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A461" t="s">
         <v>1380</v>
       </c>
@@ -20825,13 +21977,19 @@
         <v>2013</v>
       </c>
       <c r="G461" t="s">
-        <v>1490</v>
+        <v>1487</v>
+      </c>
+      <c r="H461" t="s">
+        <v>9</v>
+      </c>
+      <c r="I461" t="s">
+        <v>1552</v>
       </c>
       <c r="J461" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="462" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A462" t="s">
         <v>812</v>
       </c>
@@ -20850,11 +22008,17 @@
       <c r="G462" t="s">
         <v>1449</v>
       </c>
+      <c r="H462" t="s">
+        <v>9</v>
+      </c>
+      <c r="I462" t="s">
+        <v>1522</v>
+      </c>
       <c r="J462" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="463" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A463" t="s">
         <v>815</v>
       </c>
@@ -20873,11 +22037,17 @@
       <c r="G463" t="s">
         <v>1449</v>
       </c>
+      <c r="H463" t="s">
+        <v>9</v>
+      </c>
+      <c r="I463" t="s">
+        <v>1536</v>
+      </c>
       <c r="J463" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="464" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A464" t="s">
         <v>818</v>
       </c>
@@ -20896,11 +22066,17 @@
       <c r="G464" t="s">
         <v>1449</v>
       </c>
+      <c r="H464" t="s">
+        <v>9</v>
+      </c>
+      <c r="I464" t="s">
+        <v>1536</v>
+      </c>
       <c r="J464" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="465" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A465" t="s">
         <v>821</v>
       </c>
@@ -20917,13 +22093,22 @@
         <v>1964</v>
       </c>
       <c r="G465" t="s">
-        <v>1491</v>
+        <v>1488</v>
+      </c>
+      <c r="H465" t="s">
+        <v>1508</v>
+      </c>
+      <c r="I465" t="s">
+        <v>1553</v>
       </c>
       <c r="J465" t="s">
         <v>824</v>
       </c>
-    </row>
-    <row r="466" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="M465" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="466" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A466" t="s">
         <v>1381</v>
       </c>
@@ -20942,11 +22127,17 @@
       <c r="G466" t="s">
         <v>1449</v>
       </c>
+      <c r="H466" t="s">
+        <v>9</v>
+      </c>
+      <c r="I466" t="s">
+        <v>1540</v>
+      </c>
       <c r="J466" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="467" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A467" t="s">
         <v>828</v>
       </c>
@@ -20965,11 +22156,17 @@
       <c r="G467" t="s">
         <v>38</v>
       </c>
+      <c r="H467" t="s">
+        <v>9</v>
+      </c>
+      <c r="I467" t="s">
+        <v>1552</v>
+      </c>
       <c r="J467" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="468" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A468" t="s">
         <v>831</v>
       </c>
@@ -20988,11 +22185,17 @@
       <c r="G468" t="s">
         <v>1449</v>
       </c>
+      <c r="H468" t="s">
+        <v>9</v>
+      </c>
+      <c r="I468" t="s">
+        <v>1550</v>
+      </c>
       <c r="J468" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="469" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A469" t="s">
         <v>836</v>
       </c>
@@ -21012,13 +22215,19 @@
         <v>2020</v>
       </c>
       <c r="G469" t="s">
-        <v>1453</v>
+        <v>1452</v>
+      </c>
+      <c r="H469" t="s">
+        <v>9</v>
+      </c>
+      <c r="I469" t="s">
+        <v>1554</v>
       </c>
       <c r="J469" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="470" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A470" t="s">
         <v>1383</v>
       </c>
@@ -21035,13 +22244,22 @@
         <v>1967</v>
       </c>
       <c r="G470" t="s">
-        <v>1455</v>
+        <v>1454</v>
+      </c>
+      <c r="H470" t="s">
+        <v>1508</v>
+      </c>
+      <c r="I470" t="s">
+        <v>264</v>
       </c>
       <c r="J470" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="471" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="M470" t="s">
+        <v>1555</v>
+      </c>
+    </row>
+    <row r="471" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A471" t="s">
         <v>840</v>
       </c>
@@ -21058,13 +22276,19 @@
         <v>2021</v>
       </c>
       <c r="G471" t="s">
-        <v>1473</v>
+        <v>1471</v>
+      </c>
+      <c r="H471" t="s">
+        <v>9</v>
+      </c>
+      <c r="I471" t="s">
+        <v>1552</v>
       </c>
       <c r="J471" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="472" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A472" t="s">
         <v>843</v>
       </c>
@@ -21081,13 +22305,19 @@
         <v>2023</v>
       </c>
       <c r="G472" t="s">
-        <v>1473</v>
+        <v>1471</v>
+      </c>
+      <c r="H472" t="s">
+        <v>9</v>
+      </c>
+      <c r="I472" t="s">
+        <v>1552</v>
       </c>
       <c r="J472" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="473" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A473" t="s">
         <v>844</v>
       </c>
@@ -21104,13 +22334,19 @@
         <v>1996</v>
       </c>
       <c r="G473" t="s">
-        <v>1461</v>
+        <v>1460</v>
+      </c>
+      <c r="H473" t="s">
+        <v>9</v>
+      </c>
+      <c r="I473" t="s">
+        <v>1540</v>
       </c>
       <c r="J473" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="474" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A474" t="s">
         <v>116</v>
       </c>
@@ -21127,13 +22363,19 @@
         <v>1995</v>
       </c>
       <c r="G474" t="s">
-        <v>1461</v>
+        <v>1460</v>
+      </c>
+      <c r="H474" t="s">
+        <v>9</v>
+      </c>
+      <c r="I474" t="s">
+        <v>1538</v>
       </c>
       <c r="J474" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="475" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A475" t="s">
         <v>1385</v>
       </c>
@@ -21153,13 +22395,19 @@
         <v>2013</v>
       </c>
       <c r="G475" t="s">
-        <v>1461</v>
+        <v>1460</v>
+      </c>
+      <c r="H475" t="s">
+        <v>9</v>
+      </c>
+      <c r="I475" t="s">
+        <v>1538</v>
       </c>
       <c r="J475" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="476" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A476" t="s">
         <v>1387</v>
       </c>
@@ -21179,13 +22427,19 @@
         <v>2013</v>
       </c>
       <c r="G476" t="s">
-        <v>1492</v>
+        <v>1489</v>
+      </c>
+      <c r="H476" t="s">
+        <v>9</v>
+      </c>
+      <c r="I476" t="s">
+        <v>1538</v>
       </c>
       <c r="J476" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="477" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
         <v>851</v>
       </c>
@@ -21202,13 +22456,19 @@
         <v>2014</v>
       </c>
       <c r="G477" t="s">
-        <v>1465</v>
+        <v>1464</v>
+      </c>
+      <c r="H477" t="s">
+        <v>9</v>
+      </c>
+      <c r="I477" t="s">
+        <v>1550</v>
       </c>
       <c r="J477" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="478" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A478" t="s">
         <v>854</v>
       </c>
@@ -21227,11 +22487,17 @@
       <c r="G478" t="s">
         <v>1449</v>
       </c>
+      <c r="H478" t="s">
+        <v>9</v>
+      </c>
+      <c r="I478" t="s">
+        <v>1540</v>
+      </c>
       <c r="J478" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="479" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A479" t="s">
         <v>857</v>
       </c>
@@ -21250,11 +22516,17 @@
       <c r="G479" t="s">
         <v>1449</v>
       </c>
+      <c r="H479" t="s">
+        <v>9</v>
+      </c>
+      <c r="I479" t="s">
+        <v>1556</v>
+      </c>
       <c r="J479" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="480" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A480" t="s">
         <v>859</v>
       </c>
@@ -21273,11 +22545,17 @@
       <c r="G480" t="s">
         <v>1449</v>
       </c>
+      <c r="H480" t="s">
+        <v>9</v>
+      </c>
+      <c r="I480" t="s">
+        <v>1550</v>
+      </c>
       <c r="J480" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="481" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A481" t="s">
         <v>862</v>
       </c>
@@ -21296,11 +22574,17 @@
       <c r="G481" t="s">
         <v>1449</v>
       </c>
+      <c r="H481" t="s">
+        <v>9</v>
+      </c>
+      <c r="I481" t="s">
+        <v>1550</v>
+      </c>
       <c r="J481" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="482" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A482" t="s">
         <v>863</v>
       </c>
@@ -21319,11 +22603,17 @@
       <c r="G482" t="s">
         <v>1449</v>
       </c>
+      <c r="H482" t="s">
+        <v>9</v>
+      </c>
+      <c r="I482" t="s">
+        <v>1550</v>
+      </c>
       <c r="J482" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="483" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A483" t="s">
         <v>864</v>
       </c>
@@ -21342,11 +22632,17 @@
       <c r="G483" t="s">
         <v>1449</v>
       </c>
+      <c r="H483" t="s">
+        <v>9</v>
+      </c>
+      <c r="I483" t="s">
+        <v>1550</v>
+      </c>
       <c r="J483" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="484" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
         <v>865</v>
       </c>
@@ -21365,11 +22661,17 @@
       <c r="G484" t="s">
         <v>1449</v>
       </c>
+      <c r="H484" t="s">
+        <v>9</v>
+      </c>
+      <c r="I484" t="s">
+        <v>1540</v>
+      </c>
       <c r="J484" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="485" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A485" t="s">
         <v>868</v>
       </c>
@@ -21388,11 +22690,17 @@
       <c r="G485" t="s">
         <v>1449</v>
       </c>
+      <c r="H485" t="s">
+        <v>9</v>
+      </c>
+      <c r="I485" t="s">
+        <v>1540</v>
+      </c>
       <c r="J485" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="486" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A486" t="s">
         <v>869</v>
       </c>
@@ -21409,13 +22717,19 @@
         <v>1969</v>
       </c>
       <c r="G486" t="s">
-        <v>1461</v>
+        <v>1460</v>
+      </c>
+      <c r="H486" t="s">
+        <v>1508</v>
+      </c>
+      <c r="I486" t="s">
+        <v>264</v>
       </c>
       <c r="J486" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="487" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A487" t="s">
         <v>871</v>
       </c>
@@ -21432,13 +22746,19 @@
         <v>2003</v>
       </c>
       <c r="G487" t="s">
-        <v>1453</v>
+        <v>1452</v>
+      </c>
+      <c r="H487" t="s">
+        <v>9</v>
+      </c>
+      <c r="I487" t="s">
+        <v>55</v>
       </c>
       <c r="J487" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="488" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A488" t="s">
         <v>874</v>
       </c>
@@ -21455,13 +22775,19 @@
         <v>1999</v>
       </c>
       <c r="G488" t="s">
-        <v>1453</v>
+        <v>1452</v>
+      </c>
+      <c r="H488" t="s">
+        <v>9</v>
+      </c>
+      <c r="I488" t="s">
+        <v>1557</v>
       </c>
       <c r="J488" t="s">
         <v>708</v>
       </c>
     </row>
-    <row r="489" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A489" t="s">
         <v>877</v>
       </c>
@@ -21480,11 +22806,20 @@
       <c r="G489" t="s">
         <v>1449</v>
       </c>
+      <c r="H489" t="s">
+        <v>9</v>
+      </c>
+      <c r="I489" t="s">
+        <v>1536</v>
+      </c>
       <c r="J489" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="490" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="P489" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="490" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A490" t="s">
         <v>880</v>
       </c>
@@ -21501,13 +22836,19 @@
         <v>2011</v>
       </c>
       <c r="G490" t="s">
-        <v>1493</v>
+        <v>1490</v>
+      </c>
+      <c r="H490" t="s">
+        <v>9</v>
+      </c>
+      <c r="I490" t="s">
+        <v>1536</v>
       </c>
       <c r="J490" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="491" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A491" t="s">
         <v>883</v>
       </c>
@@ -21524,13 +22865,19 @@
         <v>2010</v>
       </c>
       <c r="G491" t="s">
-        <v>1461</v>
+        <v>1460</v>
+      </c>
+      <c r="H491" t="s">
+        <v>9</v>
+      </c>
+      <c r="I491" t="s">
+        <v>55</v>
       </c>
       <c r="J491" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="492" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A492" t="s">
         <v>886</v>
       </c>
@@ -21544,16 +22891,22 @@
         <v>888</v>
       </c>
       <c r="F492">
-        <v>1980</v>
+        <v>2003</v>
       </c>
       <c r="G492" t="s">
-        <v>1461</v>
+        <v>1460</v>
+      </c>
+      <c r="H492" t="s">
+        <v>9</v>
+      </c>
+      <c r="I492" t="s">
+        <v>1560</v>
       </c>
       <c r="J492" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="493" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A493" t="s">
         <v>889</v>
       </c>
@@ -21567,16 +22920,22 @@
         <v>888</v>
       </c>
       <c r="F493">
-        <v>1980</v>
+        <v>2003</v>
       </c>
       <c r="G493" t="s">
-        <v>1461</v>
+        <v>1460</v>
+      </c>
+      <c r="H493" t="s">
+        <v>9</v>
+      </c>
+      <c r="I493" t="s">
+        <v>1560</v>
       </c>
       <c r="J493" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="494" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A494" t="s">
         <v>890</v>
       </c>
@@ -21590,16 +22949,22 @@
         <v>888</v>
       </c>
       <c r="F494">
-        <v>1980</v>
+        <v>2003</v>
       </c>
       <c r="G494" t="s">
-        <v>1461</v>
+        <v>1460</v>
+      </c>
+      <c r="H494" t="s">
+        <v>9</v>
+      </c>
+      <c r="I494" t="s">
+        <v>1558</v>
       </c>
       <c r="J494" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="495" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A495" t="s">
         <v>891</v>
       </c>
@@ -21613,16 +22978,22 @@
         <v>888</v>
       </c>
       <c r="F495">
-        <v>1980</v>
+        <v>2003</v>
       </c>
       <c r="G495" t="s">
-        <v>1461</v>
+        <v>1460</v>
+      </c>
+      <c r="H495" t="s">
+        <v>9</v>
+      </c>
+      <c r="I495" t="s">
+        <v>1559</v>
       </c>
       <c r="J495" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="496" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A496" t="s">
         <v>892</v>
       </c>
@@ -21636,10 +23007,16 @@
         <v>888</v>
       </c>
       <c r="F496">
-        <v>1980</v>
+        <v>2003</v>
       </c>
       <c r="G496" t="s">
-        <v>1461</v>
+        <v>1460</v>
+      </c>
+      <c r="H496" t="s">
+        <v>9</v>
+      </c>
+      <c r="I496" t="s">
+        <v>1561</v>
       </c>
       <c r="J496" t="s">
         <v>282</v>
@@ -21659,10 +23036,16 @@
         <v>888</v>
       </c>
       <c r="F497">
-        <v>1980</v>
+        <v>2003</v>
       </c>
       <c r="G497" t="s">
-        <v>1461</v>
+        <v>1460</v>
+      </c>
+      <c r="H497" t="s">
+        <v>9</v>
+      </c>
+      <c r="I497" t="s">
+        <v>1559</v>
       </c>
       <c r="J497" t="s">
         <v>282</v>
@@ -21682,10 +23065,16 @@
         <v>888</v>
       </c>
       <c r="F498">
-        <v>1980</v>
+        <v>2003</v>
       </c>
       <c r="G498" t="s">
-        <v>1461</v>
+        <v>1460</v>
+      </c>
+      <c r="H498" t="s">
+        <v>9</v>
+      </c>
+      <c r="I498" t="s">
+        <v>1562</v>
       </c>
       <c r="J498" t="s">
         <v>282</v>
@@ -21705,10 +23094,16 @@
         <v>888</v>
       </c>
       <c r="F499">
-        <v>1980</v>
+        <v>2003</v>
       </c>
       <c r="G499" t="s">
-        <v>1461</v>
+        <v>1460</v>
+      </c>
+      <c r="H499" t="s">
+        <v>9</v>
+      </c>
+      <c r="I499" t="s">
+        <v>1558</v>
       </c>
       <c r="J499" t="s">
         <v>282</v>
@@ -21728,10 +23123,16 @@
         <v>888</v>
       </c>
       <c r="F500">
-        <v>1980</v>
+        <v>2003</v>
       </c>
       <c r="G500" t="s">
-        <v>1461</v>
+        <v>1460</v>
+      </c>
+      <c r="H500" t="s">
+        <v>9</v>
+      </c>
+      <c r="I500" t="s">
+        <v>1558</v>
       </c>
       <c r="J500" t="s">
         <v>282</v>
@@ -21751,10 +23152,16 @@
         <v>888</v>
       </c>
       <c r="F501">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="G501" t="s">
-        <v>1461</v>
+        <v>1460</v>
+      </c>
+      <c r="H501" t="s">
+        <v>9</v>
+      </c>
+      <c r="I501" t="s">
+        <v>1558</v>
       </c>
       <c r="J501" t="s">
         <v>282</v>
@@ -21774,10 +23181,16 @@
         <v>888</v>
       </c>
       <c r="F502">
-        <v>1980</v>
+        <v>2003</v>
       </c>
       <c r="G502" t="s">
-        <v>1461</v>
+        <v>1460</v>
+      </c>
+      <c r="H502" t="s">
+        <v>9</v>
+      </c>
+      <c r="I502" t="s">
+        <v>1563</v>
       </c>
       <c r="J502" t="s">
         <v>282</v>
@@ -21797,10 +23210,16 @@
         <v>888</v>
       </c>
       <c r="F503">
-        <v>1980</v>
+        <v>2003</v>
       </c>
       <c r="G503" t="s">
-        <v>1461</v>
+        <v>1460</v>
+      </c>
+      <c r="H503" t="s">
+        <v>9</v>
+      </c>
+      <c r="I503" t="s">
+        <v>1558</v>
       </c>
       <c r="J503" t="s">
         <v>282</v>
@@ -21820,10 +23239,16 @@
         <v>888</v>
       </c>
       <c r="F504">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="G504" t="s">
-        <v>1461</v>
+        <v>1460</v>
+      </c>
+      <c r="H504" t="s">
+        <v>9</v>
+      </c>
+      <c r="I504" t="s">
+        <v>1559</v>
       </c>
       <c r="J504" t="s">
         <v>282</v>
@@ -21846,7 +23271,13 @@
         <v>2005</v>
       </c>
       <c r="G505" t="s">
-        <v>1461</v>
+        <v>1460</v>
+      </c>
+      <c r="H505" t="s">
+        <v>9</v>
+      </c>
+      <c r="I505" t="s">
+        <v>1571</v>
       </c>
       <c r="J505" t="s">
         <v>282</v>
@@ -21869,7 +23300,13 @@
         <v>2005</v>
       </c>
       <c r="G506" t="s">
-        <v>1461</v>
+        <v>1460</v>
+      </c>
+      <c r="H506" t="s">
+        <v>9</v>
+      </c>
+      <c r="I506" t="s">
+        <v>1559</v>
       </c>
       <c r="J506" t="s">
         <v>282</v>
@@ -21892,7 +23329,13 @@
         <v>2005</v>
       </c>
       <c r="G507" t="s">
-        <v>1461</v>
+        <v>1460</v>
+      </c>
+      <c r="H507" t="s">
+        <v>9</v>
+      </c>
+      <c r="I507" t="s">
+        <v>1559</v>
       </c>
       <c r="J507" t="s">
         <v>282</v>
@@ -21915,7 +23358,13 @@
         <v>2005</v>
       </c>
       <c r="G508" t="s">
-        <v>1461</v>
+        <v>1460</v>
+      </c>
+      <c r="H508" t="s">
+        <v>9</v>
+      </c>
+      <c r="I508" t="s">
+        <v>1559</v>
       </c>
       <c r="J508" t="s">
         <v>282</v>
@@ -21940,6 +23389,12 @@
       <c r="G509" t="s">
         <v>1449</v>
       </c>
+      <c r="H509" t="s">
+        <v>9</v>
+      </c>
+      <c r="I509" t="s">
+        <v>1572</v>
+      </c>
       <c r="J509" t="s">
         <v>282</v>
       </c>
@@ -21963,6 +23418,12 @@
       <c r="G510" t="s">
         <v>1449</v>
       </c>
+      <c r="H510" t="s">
+        <v>9</v>
+      </c>
+      <c r="I510" t="s">
+        <v>1533</v>
+      </c>
       <c r="J510" t="s">
         <v>285</v>
       </c>
@@ -21986,6 +23447,12 @@
       <c r="G511" t="s">
         <v>1449</v>
       </c>
+      <c r="H511" t="s">
+        <v>1508</v>
+      </c>
+      <c r="I511" t="s">
+        <v>676</v>
+      </c>
       <c r="J511" t="s">
         <v>285</v>
       </c>
@@ -22009,6 +23476,12 @@
       <c r="G512" t="s">
         <v>1449</v>
       </c>
+      <c r="H512" t="s">
+        <v>9</v>
+      </c>
+      <c r="I512" t="s">
+        <v>676</v>
+      </c>
       <c r="J512" t="s">
         <v>285</v>
       </c>
@@ -22027,10 +23500,16 @@
         <v>1433</v>
       </c>
       <c r="F513">
-        <v>2023</v>
+        <v>1987</v>
       </c>
       <c r="G513" t="s">
         <v>1449</v>
+      </c>
+      <c r="H513" t="s">
+        <v>9</v>
+      </c>
+      <c r="I513" t="s">
+        <v>676</v>
       </c>
       <c r="J513" t="s">
         <v>282</v>
@@ -22055,6 +23534,12 @@
       <c r="G514" t="s">
         <v>1449</v>
       </c>
+      <c r="H514" t="s">
+        <v>9</v>
+      </c>
+      <c r="I514" t="s">
+        <v>676</v>
+      </c>
       <c r="J514" t="s">
         <v>282</v>
       </c>
@@ -22078,6 +23563,12 @@
       <c r="G515" t="s">
         <v>1449</v>
       </c>
+      <c r="H515" t="s">
+        <v>9</v>
+      </c>
+      <c r="I515" t="s">
+        <v>676</v>
+      </c>
       <c r="J515" t="s">
         <v>285</v>
       </c>
@@ -22101,6 +23592,12 @@
       <c r="G516" t="s">
         <v>1449</v>
       </c>
+      <c r="H516" t="s">
+        <v>9</v>
+      </c>
+      <c r="I516" t="s">
+        <v>676</v>
+      </c>
       <c r="J516" t="s">
         <v>285</v>
       </c>
@@ -22124,6 +23621,12 @@
       <c r="G517" t="s">
         <v>1449</v>
       </c>
+      <c r="H517" t="s">
+        <v>9</v>
+      </c>
+      <c r="I517" t="s">
+        <v>676</v>
+      </c>
       <c r="J517" t="s">
         <v>282</v>
       </c>
@@ -22147,6 +23650,12 @@
       <c r="G518" t="s">
         <v>1449</v>
       </c>
+      <c r="H518" t="s">
+        <v>9</v>
+      </c>
+      <c r="I518" t="s">
+        <v>676</v>
+      </c>
       <c r="J518" t="s">
         <v>282</v>
       </c>
@@ -22170,6 +23679,12 @@
       <c r="G519" t="s">
         <v>1449</v>
       </c>
+      <c r="H519" t="s">
+        <v>9</v>
+      </c>
+      <c r="I519" t="s">
+        <v>676</v>
+      </c>
       <c r="J519" t="s">
         <v>282</v>
       </c>
@@ -22193,6 +23708,12 @@
       <c r="G520" t="s">
         <v>1449</v>
       </c>
+      <c r="H520" t="s">
+        <v>9</v>
+      </c>
+      <c r="I520" t="s">
+        <v>676</v>
+      </c>
       <c r="J520" t="s">
         <v>285</v>
       </c>
@@ -22216,6 +23737,12 @@
       <c r="G521" t="s">
         <v>1449</v>
       </c>
+      <c r="H521" t="s">
+        <v>9</v>
+      </c>
+      <c r="I521" t="s">
+        <v>676</v>
+      </c>
       <c r="J521" t="s">
         <v>285</v>
       </c>
@@ -22239,6 +23766,12 @@
       <c r="G522" t="s">
         <v>1449</v>
       </c>
+      <c r="H522" t="s">
+        <v>9</v>
+      </c>
+      <c r="I522" t="s">
+        <v>676</v>
+      </c>
       <c r="J522" t="s">
         <v>285</v>
       </c>
@@ -22260,7 +23793,13 @@
         <v>1965</v>
       </c>
       <c r="G523" t="s">
-        <v>1494</v>
+        <v>1491</v>
+      </c>
+      <c r="H523" t="s">
+        <v>9</v>
+      </c>
+      <c r="I523" t="s">
+        <v>264</v>
       </c>
       <c r="J523" t="s">
         <v>264</v>
@@ -22283,7 +23822,13 @@
         <v>1951</v>
       </c>
       <c r="G524" t="s">
-        <v>1494</v>
+        <v>1491</v>
+      </c>
+      <c r="H524" t="s">
+        <v>39</v>
+      </c>
+      <c r="I524" t="s">
+        <v>264</v>
       </c>
       <c r="J524" t="s">
         <v>264</v>
@@ -22306,7 +23851,13 @@
         <v>1951</v>
       </c>
       <c r="G525" t="s">
-        <v>1494</v>
+        <v>1491</v>
+      </c>
+      <c r="H525" t="s">
+        <v>9</v>
+      </c>
+      <c r="I525" t="s">
+        <v>264</v>
       </c>
       <c r="J525" t="s">
         <v>264</v>
@@ -22329,7 +23880,13 @@
         <v>1965</v>
       </c>
       <c r="G526" t="s">
-        <v>1494</v>
+        <v>1491</v>
+      </c>
+      <c r="H526" t="s">
+        <v>9</v>
+      </c>
+      <c r="I526" t="s">
+        <v>264</v>
       </c>
       <c r="J526" t="s">
         <v>264</v>
@@ -22352,7 +23909,13 @@
         <v>1965</v>
       </c>
       <c r="G527" t="s">
-        <v>1494</v>
+        <v>1491</v>
+      </c>
+      <c r="H527" t="s">
+        <v>9</v>
+      </c>
+      <c r="I527" t="s">
+        <v>264</v>
       </c>
       <c r="J527" t="s">
         <v>264</v>
@@ -22375,13 +23938,16 @@
         <v>2017</v>
       </c>
       <c r="G528" t="s">
-        <v>1495</v>
+        <v>1492</v>
+      </c>
+      <c r="H528" t="s">
+        <v>9</v>
       </c>
       <c r="J528" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="529" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A529" t="s">
         <v>936</v>
       </c>
@@ -22398,13 +23964,16 @@
         <v>1992</v>
       </c>
       <c r="G529" t="s">
-        <v>1495</v>
+        <v>1492</v>
+      </c>
+      <c r="H529" t="s">
+        <v>9</v>
       </c>
       <c r="J529" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="530" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A530" t="s">
         <v>938</v>
       </c>
@@ -22421,13 +23990,16 @@
         <v>1994</v>
       </c>
       <c r="G530" t="s">
-        <v>1495</v>
+        <v>1492</v>
+      </c>
+      <c r="H530" t="s">
+        <v>9</v>
       </c>
       <c r="J530" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="531" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A531" t="s">
         <v>940</v>
       </c>
@@ -22444,13 +24016,16 @@
         <v>1994</v>
       </c>
       <c r="G531" t="s">
-        <v>1495</v>
+        <v>1492</v>
+      </c>
+      <c r="H531" t="s">
+        <v>9</v>
       </c>
       <c r="J531" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="532" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A532" t="s">
         <v>941</v>
       </c>
@@ -22467,13 +24042,16 @@
         <v>1994</v>
       </c>
       <c r="G532" t="s">
-        <v>1495</v>
+        <v>1492</v>
+      </c>
+      <c r="H532" t="s">
+        <v>9</v>
       </c>
       <c r="J532" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="533" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A533" t="s">
         <v>942</v>
       </c>
@@ -22490,13 +24068,16 @@
         <v>1994</v>
       </c>
       <c r="G533" t="s">
-        <v>1495</v>
+        <v>1492</v>
+      </c>
+      <c r="H533" t="s">
+        <v>9</v>
       </c>
       <c r="J533" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="534" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A534" t="s">
         <v>943</v>
       </c>
@@ -22513,13 +24094,22 @@
         <v>1999</v>
       </c>
       <c r="G534" t="s">
-        <v>1495</v>
+        <v>1492</v>
+      </c>
+      <c r="H534" t="s">
+        <v>1508</v>
+      </c>
+      <c r="I534" t="s">
+        <v>1564</v>
       </c>
       <c r="J534" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="535" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="M534" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="535" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A535" t="s">
         <v>945</v>
       </c>
@@ -22536,13 +24126,19 @@
         <v>1997</v>
       </c>
       <c r="G535" t="s">
-        <v>1495</v>
+        <v>1492</v>
+      </c>
+      <c r="H535" t="s">
+        <v>9</v>
+      </c>
+      <c r="I535" t="s">
+        <v>1536</v>
       </c>
       <c r="J535" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="536" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A536" t="s">
         <v>947</v>
       </c>
@@ -22559,13 +24155,16 @@
         <v>1989</v>
       </c>
       <c r="G536" t="s">
-        <v>1495</v>
+        <v>1492</v>
+      </c>
+      <c r="H536" t="s">
+        <v>9</v>
       </c>
       <c r="J536" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="537" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A537" t="s">
         <v>949</v>
       </c>
@@ -22582,13 +24181,16 @@
         <v>1989</v>
       </c>
       <c r="G537" t="s">
-        <v>1495</v>
+        <v>1492</v>
+      </c>
+      <c r="H537" t="s">
+        <v>9</v>
       </c>
       <c r="J537" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="538" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A538" t="s">
         <v>950</v>
       </c>
@@ -22605,13 +24207,16 @@
         <v>1989</v>
       </c>
       <c r="G538" t="s">
-        <v>1495</v>
+        <v>1492</v>
+      </c>
+      <c r="H538" t="s">
+        <v>9</v>
       </c>
       <c r="J538" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="539" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A539" t="s">
         <v>951</v>
       </c>
@@ -22628,13 +24233,16 @@
         <v>2005</v>
       </c>
       <c r="G539" t="s">
-        <v>1495</v>
+        <v>1492</v>
+      </c>
+      <c r="H539" t="s">
+        <v>9</v>
       </c>
       <c r="J539" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="540" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A540" t="s">
         <v>953</v>
       </c>
@@ -22651,13 +24259,16 @@
         <v>2005</v>
       </c>
       <c r="G540" t="s">
-        <v>1495</v>
+        <v>1492</v>
+      </c>
+      <c r="H540" t="s">
+        <v>9</v>
       </c>
       <c r="J540" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="541" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A541" t="s">
         <v>954</v>
       </c>
@@ -22674,13 +24285,16 @@
         <v>2005</v>
       </c>
       <c r="G541" t="s">
-        <v>1495</v>
+        <v>1492</v>
+      </c>
+      <c r="H541" t="s">
+        <v>9</v>
       </c>
       <c r="J541" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="542" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A542" t="s">
         <v>955</v>
       </c>
@@ -22697,13 +24311,16 @@
         <v>2005</v>
       </c>
       <c r="G542" t="s">
-        <v>1495</v>
+        <v>1492</v>
+      </c>
+      <c r="H542" t="s">
+        <v>9</v>
       </c>
       <c r="J542" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="543" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A543" t="s">
         <v>956</v>
       </c>
@@ -22720,13 +24337,16 @@
         <v>2005</v>
       </c>
       <c r="G543" t="s">
-        <v>1495</v>
+        <v>1492</v>
+      </c>
+      <c r="H543" t="s">
+        <v>9</v>
       </c>
       <c r="J543" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="544" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A544" t="s">
         <v>957</v>
       </c>
@@ -22743,7 +24363,10 @@
         <v>1998</v>
       </c>
       <c r="G544" t="s">
-        <v>1453</v>
+        <v>1452</v>
+      </c>
+      <c r="H544" t="s">
+        <v>9</v>
       </c>
       <c r="J544" t="s">
         <v>285</v>
@@ -22768,6 +24391,9 @@
       <c r="G545" t="s">
         <v>1449</v>
       </c>
+      <c r="H545" t="s">
+        <v>9</v>
+      </c>
       <c r="J545" t="s">
         <v>10</v>
       </c>
@@ -22791,6 +24417,9 @@
       <c r="G546" t="s">
         <v>1449</v>
       </c>
+      <c r="H546" t="s">
+        <v>9</v>
+      </c>
       <c r="J546" t="s">
         <v>285</v>
       </c>
@@ -22812,7 +24441,10 @@
         <v>1991</v>
       </c>
       <c r="G547" t="s">
-        <v>1473</v>
+        <v>1471</v>
+      </c>
+      <c r="H547" t="s">
+        <v>9</v>
       </c>
       <c r="J547" t="s">
         <v>131</v>
@@ -22835,7 +24467,10 @@
         <v>1993</v>
       </c>
       <c r="G548" t="s">
-        <v>1473</v>
+        <v>1471</v>
+      </c>
+      <c r="H548" t="s">
+        <v>9</v>
       </c>
       <c r="J548" t="s">
         <v>131</v>
@@ -22858,7 +24493,10 @@
         <v>2013</v>
       </c>
       <c r="G549" t="s">
-        <v>1496</v>
+        <v>1493</v>
+      </c>
+      <c r="H549" t="s">
+        <v>1508</v>
       </c>
       <c r="J549" t="s">
         <v>10</v>
@@ -22883,6 +24521,9 @@
       <c r="G550" t="s">
         <v>1449</v>
       </c>
+      <c r="H550" t="s">
+        <v>9</v>
+      </c>
       <c r="J550" t="s">
         <v>282</v>
       </c>
@@ -22906,11 +24547,14 @@
       <c r="G551" t="s">
         <v>1449</v>
       </c>
+      <c r="H551" t="s">
+        <v>9</v>
+      </c>
       <c r="J551" t="s">
         <v>282</v>
       </c>
       <c r="P551" t="s">
-        <v>1521</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="552" spans="1:16" x14ac:dyDescent="0.2">
@@ -22932,6 +24576,9 @@
       <c r="G552" t="s">
         <v>1449</v>
       </c>
+      <c r="H552" t="s">
+        <v>9</v>
+      </c>
       <c r="J552" t="s">
         <v>282</v>
       </c>
@@ -22955,6 +24602,9 @@
       <c r="G553" t="s">
         <v>1449</v>
       </c>
+      <c r="H553" t="s">
+        <v>9</v>
+      </c>
       <c r="J553" t="s">
         <v>282</v>
       </c>
@@ -22978,6 +24628,9 @@
       <c r="G554" t="s">
         <v>1449</v>
       </c>
+      <c r="H554" t="s">
+        <v>9</v>
+      </c>
       <c r="J554" t="s">
         <v>282</v>
       </c>
@@ -23001,6 +24654,9 @@
       <c r="G555" t="s">
         <v>1449</v>
       </c>
+      <c r="H555" t="s">
+        <v>9</v>
+      </c>
       <c r="J555" t="s">
         <v>131</v>
       </c>
@@ -23024,6 +24680,9 @@
       <c r="G556" t="s">
         <v>1449</v>
       </c>
+      <c r="H556" t="s">
+        <v>9</v>
+      </c>
       <c r="J556" t="s">
         <v>131</v>
       </c>
@@ -23047,6 +24706,9 @@
       <c r="G557" t="s">
         <v>1449</v>
       </c>
+      <c r="H557" t="s">
+        <v>9</v>
+      </c>
       <c r="J557" t="s">
         <v>131</v>
       </c>
@@ -23070,6 +24732,9 @@
       <c r="G558" t="s">
         <v>1449</v>
       </c>
+      <c r="H558" t="s">
+        <v>9</v>
+      </c>
       <c r="J558" t="s">
         <v>131</v>
       </c>
@@ -23093,6 +24758,9 @@
       <c r="G559" t="s">
         <v>1449</v>
       </c>
+      <c r="H559" t="s">
+        <v>9</v>
+      </c>
       <c r="J559" t="s">
         <v>131</v>
       </c>
@@ -23116,6 +24784,9 @@
       <c r="G560" t="s">
         <v>1449</v>
       </c>
+      <c r="H560" t="s">
+        <v>9</v>
+      </c>
       <c r="J560" t="s">
         <v>131</v>
       </c>
@@ -23139,6 +24810,9 @@
       <c r="G561" t="s">
         <v>1449</v>
       </c>
+      <c r="H561" t="s">
+        <v>9</v>
+      </c>
       <c r="J561" t="s">
         <v>131</v>
       </c>
@@ -23162,6 +24836,9 @@
       <c r="G562" t="s">
         <v>1449</v>
       </c>
+      <c r="H562" t="s">
+        <v>9</v>
+      </c>
       <c r="J562" t="s">
         <v>131</v>
       </c>
@@ -23185,6 +24862,9 @@
       <c r="G563" t="s">
         <v>1449</v>
       </c>
+      <c r="H563" t="s">
+        <v>9</v>
+      </c>
       <c r="J563" t="s">
         <v>131</v>
       </c>
@@ -23208,6 +24888,9 @@
       <c r="G564" t="s">
         <v>1449</v>
       </c>
+      <c r="H564" t="s">
+        <v>9</v>
+      </c>
       <c r="J564" t="s">
         <v>131</v>
       </c>
@@ -23232,7 +24915,10 @@
         <v>2012</v>
       </c>
       <c r="G565" t="s">
-        <v>1497</v>
+        <v>1494</v>
+      </c>
+      <c r="H565" t="s">
+        <v>1565</v>
       </c>
       <c r="J565" t="s">
         <v>568</v>
@@ -23257,6 +24943,9 @@
       <c r="G566" t="s">
         <v>38</v>
       </c>
+      <c r="H566" t="s">
+        <v>9</v>
+      </c>
       <c r="J566" t="s">
         <v>131</v>
       </c>
@@ -23280,6 +24969,9 @@
       <c r="G567" t="s">
         <v>38</v>
       </c>
+      <c r="H567" t="s">
+        <v>9</v>
+      </c>
       <c r="J567" t="s">
         <v>131</v>
       </c>
@@ -23303,6 +24995,9 @@
       <c r="G568" t="s">
         <v>38</v>
       </c>
+      <c r="H568" t="s">
+        <v>9</v>
+      </c>
       <c r="J568" t="s">
         <v>285</v>
       </c>
@@ -23326,6 +25021,9 @@
       <c r="G569" t="s">
         <v>38</v>
       </c>
+      <c r="H569" t="s">
+        <v>9</v>
+      </c>
       <c r="J569" t="s">
         <v>285</v>
       </c>
@@ -23349,6 +25047,9 @@
       <c r="G570" t="s">
         <v>1449</v>
       </c>
+      <c r="H570" t="s">
+        <v>9</v>
+      </c>
       <c r="J570" t="s">
         <v>285</v>
       </c>
@@ -23372,6 +25073,9 @@
       <c r="G571" t="s">
         <v>1449</v>
       </c>
+      <c r="H571" t="s">
+        <v>9</v>
+      </c>
       <c r="J571" t="s">
         <v>285</v>
       </c>
@@ -23395,6 +25099,9 @@
       <c r="G572" t="s">
         <v>1449</v>
       </c>
+      <c r="H572" t="s">
+        <v>9</v>
+      </c>
       <c r="J572" t="s">
         <v>285</v>
       </c>
@@ -23418,6 +25125,9 @@
       <c r="G573" t="s">
         <v>1449</v>
       </c>
+      <c r="H573" t="s">
+        <v>9</v>
+      </c>
       <c r="J573" t="s">
         <v>285</v>
       </c>
@@ -23441,6 +25151,9 @@
       <c r="G574" t="s">
         <v>1449</v>
       </c>
+      <c r="H574" t="s">
+        <v>9</v>
+      </c>
       <c r="J574" t="s">
         <v>285</v>
       </c>
@@ -23464,6 +25177,9 @@
       <c r="G575" t="s">
         <v>1449</v>
       </c>
+      <c r="H575" t="s">
+        <v>9</v>
+      </c>
       <c r="J575" t="s">
         <v>285</v>
       </c>
@@ -23487,6 +25203,9 @@
       <c r="G576" t="s">
         <v>1449</v>
       </c>
+      <c r="H576" t="s">
+        <v>9</v>
+      </c>
       <c r="J576" t="s">
         <v>285</v>
       </c>
@@ -23510,6 +25229,9 @@
       <c r="G577" t="s">
         <v>1449</v>
       </c>
+      <c r="H577" t="s">
+        <v>9</v>
+      </c>
       <c r="J577" t="s">
         <v>10</v>
       </c>
@@ -23533,6 +25255,9 @@
       <c r="G578" t="s">
         <v>1449</v>
       </c>
+      <c r="H578" t="s">
+        <v>9</v>
+      </c>
       <c r="J578" t="s">
         <v>10</v>
       </c>
@@ -23556,6 +25281,9 @@
       <c r="G579" t="s">
         <v>1449</v>
       </c>
+      <c r="H579" t="s">
+        <v>9</v>
+      </c>
       <c r="J579" t="s">
         <v>10</v>
       </c>
@@ -23579,6 +25307,9 @@
       <c r="G580" t="s">
         <v>1449</v>
       </c>
+      <c r="H580" t="s">
+        <v>9</v>
+      </c>
       <c r="J580" t="s">
         <v>10</v>
       </c>
@@ -23602,6 +25333,9 @@
       <c r="G581" t="s">
         <v>1449</v>
       </c>
+      <c r="H581" t="s">
+        <v>9</v>
+      </c>
       <c r="J581" t="s">
         <v>10</v>
       </c>
@@ -23625,6 +25359,9 @@
       <c r="G582" t="s">
         <v>1449</v>
       </c>
+      <c r="H582" t="s">
+        <v>9</v>
+      </c>
       <c r="J582" t="s">
         <v>10</v>
       </c>
@@ -23648,6 +25385,9 @@
       <c r="G583" t="s">
         <v>1449</v>
       </c>
+      <c r="H583" t="s">
+        <v>9</v>
+      </c>
       <c r="J583" t="s">
         <v>10</v>
       </c>
@@ -23671,6 +25411,9 @@
       <c r="G584" t="s">
         <v>1449</v>
       </c>
+      <c r="H584" t="s">
+        <v>9</v>
+      </c>
       <c r="J584" t="s">
         <v>10</v>
       </c>
@@ -23694,6 +25437,9 @@
       <c r="G585" t="s">
         <v>1449</v>
       </c>
+      <c r="H585" t="s">
+        <v>9</v>
+      </c>
       <c r="J585" t="s">
         <v>10</v>
       </c>
@@ -23717,6 +25463,9 @@
       <c r="G586" t="s">
         <v>1449</v>
       </c>
+      <c r="H586" t="s">
+        <v>9</v>
+      </c>
       <c r="J586" t="s">
         <v>10</v>
       </c>
@@ -23740,6 +25489,9 @@
       <c r="G587" t="s">
         <v>1449</v>
       </c>
+      <c r="H587" t="s">
+        <v>9</v>
+      </c>
       <c r="J587" t="s">
         <v>10</v>
       </c>
@@ -23763,6 +25515,9 @@
       <c r="G588" t="s">
         <v>1449</v>
       </c>
+      <c r="H588" t="s">
+        <v>9</v>
+      </c>
       <c r="J588" t="s">
         <v>10</v>
       </c>
@@ -23786,6 +25541,9 @@
       <c r="G589" t="s">
         <v>1449</v>
       </c>
+      <c r="H589" t="s">
+        <v>9</v>
+      </c>
       <c r="J589" t="s">
         <v>10</v>
       </c>
@@ -23809,6 +25567,9 @@
       <c r="G590" t="s">
         <v>1449</v>
       </c>
+      <c r="H590" t="s">
+        <v>9</v>
+      </c>
       <c r="J590" t="s">
         <v>10</v>
       </c>
@@ -23832,6 +25593,9 @@
       <c r="G591" t="s">
         <v>1449</v>
       </c>
+      <c r="H591" t="s">
+        <v>9</v>
+      </c>
       <c r="J591" t="s">
         <v>131</v>
       </c>
@@ -23855,6 +25619,9 @@
       <c r="G592" t="s">
         <v>1449</v>
       </c>
+      <c r="H592" t="s">
+        <v>9</v>
+      </c>
       <c r="J592" t="s">
         <v>131</v>
       </c>
@@ -23878,6 +25645,9 @@
       <c r="G593" t="s">
         <v>1449</v>
       </c>
+      <c r="H593" t="s">
+        <v>9</v>
+      </c>
       <c r="J593" t="s">
         <v>131</v>
       </c>
@@ -23901,6 +25671,9 @@
       <c r="G594" t="s">
         <v>1449</v>
       </c>
+      <c r="H594" t="s">
+        <v>9</v>
+      </c>
       <c r="J594" t="s">
         <v>285</v>
       </c>
@@ -23924,6 +25697,9 @@
       <c r="G595" t="s">
         <v>1449</v>
       </c>
+      <c r="H595" t="s">
+        <v>9</v>
+      </c>
       <c r="J595" t="s">
         <v>285</v>
       </c>
@@ -23947,6 +25723,9 @@
       <c r="G596" t="s">
         <v>1449</v>
       </c>
+      <c r="H596" t="s">
+        <v>9</v>
+      </c>
       <c r="J596" t="s">
         <v>285</v>
       </c>
@@ -23970,6 +25749,9 @@
       <c r="G597" t="s">
         <v>1449</v>
       </c>
+      <c r="H597" t="s">
+        <v>9</v>
+      </c>
       <c r="J597" t="s">
         <v>131</v>
       </c>
@@ -23991,7 +25773,10 @@
         <v>1981</v>
       </c>
       <c r="G598" t="s">
-        <v>1457</v>
+        <v>1456</v>
+      </c>
+      <c r="H598" t="s">
+        <v>9</v>
       </c>
       <c r="J598" t="s">
         <v>285</v>
@@ -24014,7 +25799,10 @@
         <v>1983</v>
       </c>
       <c r="G599" t="s">
-        <v>1457</v>
+        <v>1456</v>
+      </c>
+      <c r="H599" t="s">
+        <v>9</v>
       </c>
       <c r="J599" t="s">
         <v>285</v>
@@ -24037,7 +25825,10 @@
         <v>1984</v>
       </c>
       <c r="G600" t="s">
-        <v>1457</v>
+        <v>1456</v>
+      </c>
+      <c r="H600" t="s">
+        <v>9</v>
       </c>
       <c r="J600" t="s">
         <v>285</v>
@@ -24060,7 +25851,10 @@
         <v>1985</v>
       </c>
       <c r="G601" t="s">
-        <v>1457</v>
+        <v>1456</v>
+      </c>
+      <c r="H601" t="s">
+        <v>9</v>
       </c>
       <c r="J601" t="s">
         <v>285</v>
@@ -24083,7 +25877,10 @@
         <v>1986</v>
       </c>
       <c r="G602" t="s">
-        <v>1457</v>
+        <v>1456</v>
+      </c>
+      <c r="H602" t="s">
+        <v>9</v>
       </c>
       <c r="J602" t="s">
         <v>285</v>
@@ -24106,7 +25903,10 @@
         <v>1987</v>
       </c>
       <c r="G603" t="s">
-        <v>1457</v>
+        <v>1456</v>
+      </c>
+      <c r="H603" t="s">
+        <v>9</v>
       </c>
       <c r="J603" t="s">
         <v>285</v>
@@ -24129,7 +25929,10 @@
         <v>1988</v>
       </c>
       <c r="G604" t="s">
-        <v>1457</v>
+        <v>1456</v>
+      </c>
+      <c r="H604" t="s">
+        <v>9</v>
       </c>
       <c r="J604" t="s">
         <v>285</v>
@@ -24152,7 +25955,10 @@
         <v>1983</v>
       </c>
       <c r="G605" t="s">
-        <v>1457</v>
+        <v>1456</v>
+      </c>
+      <c r="H605" t="s">
+        <v>9</v>
       </c>
       <c r="J605" t="s">
         <v>282</v>
@@ -24175,7 +25981,10 @@
         <v>1983</v>
       </c>
       <c r="G606" t="s">
-        <v>1457</v>
+        <v>1456</v>
+      </c>
+      <c r="H606" t="s">
+        <v>9</v>
       </c>
       <c r="J606" t="s">
         <v>282</v>
@@ -24198,7 +26007,10 @@
         <v>1983</v>
       </c>
       <c r="G607" t="s">
-        <v>1457</v>
+        <v>1456</v>
+      </c>
+      <c r="H607" t="s">
+        <v>9</v>
       </c>
       <c r="J607" t="s">
         <v>282</v>
@@ -24221,7 +26033,10 @@
         <v>1991</v>
       </c>
       <c r="G608" t="s">
-        <v>1457</v>
+        <v>1456</v>
+      </c>
+      <c r="H608" t="s">
+        <v>9</v>
       </c>
       <c r="J608" t="s">
         <v>131</v>
@@ -24244,7 +26059,10 @@
         <v>2008</v>
       </c>
       <c r="G609" t="s">
-        <v>1498</v>
+        <v>1495</v>
+      </c>
+      <c r="H609" t="s">
+        <v>9</v>
       </c>
       <c r="J609" t="s">
         <v>282</v>
@@ -24267,7 +26085,10 @@
         <v>2008</v>
       </c>
       <c r="G610" t="s">
-        <v>1498</v>
+        <v>1495</v>
+      </c>
+      <c r="H610" t="s">
+        <v>9</v>
       </c>
       <c r="J610" t="s">
         <v>282</v>
@@ -24290,7 +26111,10 @@
         <v>2008</v>
       </c>
       <c r="G611" t="s">
-        <v>1498</v>
+        <v>1495</v>
+      </c>
+      <c r="H611" t="s">
+        <v>9</v>
       </c>
       <c r="J611" t="s">
         <v>282</v>
@@ -24313,7 +26137,10 @@
         <v>1987</v>
       </c>
       <c r="G612" t="s">
-        <v>1452</v>
+        <v>1451</v>
+      </c>
+      <c r="H612" t="s">
+        <v>9</v>
       </c>
       <c r="J612" t="s">
         <v>285</v>
@@ -24338,6 +26165,9 @@
       <c r="G613" t="s">
         <v>1449</v>
       </c>
+      <c r="H613" t="s">
+        <v>9</v>
+      </c>
       <c r="J613" t="s">
         <v>282</v>
       </c>
@@ -24361,6 +26191,9 @@
       <c r="G614" t="s">
         <v>1449</v>
       </c>
+      <c r="H614" t="s">
+        <v>9</v>
+      </c>
       <c r="J614" t="s">
         <v>131</v>
       </c>
@@ -24382,7 +26215,10 @@
         <v>2004</v>
       </c>
       <c r="G615" t="s">
-        <v>1453</v>
+        <v>1452</v>
+      </c>
+      <c r="H615" t="s">
+        <v>9</v>
       </c>
       <c r="J615" t="s">
         <v>131</v>
@@ -24405,7 +26241,10 @@
         <v>2004</v>
       </c>
       <c r="G616" t="s">
-        <v>1453</v>
+        <v>1452</v>
+      </c>
+      <c r="H616" t="s">
+        <v>9</v>
       </c>
       <c r="J616" t="s">
         <v>131</v>
@@ -24428,7 +26267,10 @@
         <v>1973</v>
       </c>
       <c r="G617" t="s">
-        <v>1494</v>
+        <v>1491</v>
+      </c>
+      <c r="H617" t="s">
+        <v>9</v>
       </c>
       <c r="J617" t="s">
         <v>282</v>
@@ -24448,10 +26290,16 @@
         <v>1080</v>
       </c>
       <c r="F618">
-        <v>2006</v>
+        <v>1982</v>
       </c>
       <c r="G618" t="s">
-        <v>1499</v>
+        <v>1496</v>
+      </c>
+      <c r="H618" t="s">
+        <v>9</v>
+      </c>
+      <c r="I618" t="s">
+        <v>1531</v>
       </c>
       <c r="J618" t="s">
         <v>282</v>
@@ -24476,6 +26324,9 @@
       <c r="G619" t="s">
         <v>8</v>
       </c>
+      <c r="H619" t="s">
+        <v>9</v>
+      </c>
       <c r="J619" t="s">
         <v>10</v>
       </c>
@@ -24499,6 +26350,9 @@
       <c r="G620" t="s">
         <v>8</v>
       </c>
+      <c r="H620" t="s">
+        <v>9</v>
+      </c>
       <c r="J620" t="s">
         <v>10</v>
       </c>
@@ -24522,6 +26376,9 @@
       <c r="G621" t="s">
         <v>8</v>
       </c>
+      <c r="H621" t="s">
+        <v>9</v>
+      </c>
       <c r="J621" t="s">
         <v>31</v>
       </c>
@@ -24548,6 +26405,9 @@
       <c r="G622" t="s">
         <v>8</v>
       </c>
+      <c r="H622" t="s">
+        <v>9</v>
+      </c>
       <c r="J622" t="s">
         <v>10</v>
       </c>
@@ -24574,6 +26434,9 @@
       <c r="G623" t="s">
         <v>8</v>
       </c>
+      <c r="H623" t="s">
+        <v>9</v>
+      </c>
       <c r="J623" t="s">
         <v>10</v>
       </c>
@@ -24597,6 +26460,9 @@
       <c r="G624" t="s">
         <v>8</v>
       </c>
+      <c r="H624" t="s">
+        <v>9</v>
+      </c>
       <c r="J624" t="s">
         <v>282</v>
       </c>
@@ -24621,7 +26487,10 @@
         <v>2013</v>
       </c>
       <c r="G625" t="s">
-        <v>1500</v>
+        <v>1497</v>
+      </c>
+      <c r="H625" t="s">
+        <v>9</v>
       </c>
       <c r="J625" t="s">
         <v>10</v>
@@ -24646,6 +26515,9 @@
       <c r="G626" t="s">
         <v>8</v>
       </c>
+      <c r="H626" t="s">
+        <v>9</v>
+      </c>
       <c r="J626" t="s">
         <v>31</v>
       </c>
@@ -24669,6 +26541,9 @@
       <c r="G627" t="s">
         <v>8</v>
       </c>
+      <c r="H627" t="s">
+        <v>9</v>
+      </c>
       <c r="J627" t="s">
         <v>31</v>
       </c>
@@ -24692,6 +26567,9 @@
       <c r="G628" t="s">
         <v>8</v>
       </c>
+      <c r="H628" t="s">
+        <v>9</v>
+      </c>
       <c r="J628" t="s">
         <v>31</v>
       </c>
@@ -24715,6 +26593,9 @@
       <c r="G629" t="s">
         <v>1449</v>
       </c>
+      <c r="H629" t="s">
+        <v>9</v>
+      </c>
       <c r="J629" t="s">
         <v>282</v>
       </c>
@@ -24738,6 +26619,9 @@
       <c r="G630" t="s">
         <v>1449</v>
       </c>
+      <c r="H630" t="s">
+        <v>9</v>
+      </c>
       <c r="J630" t="s">
         <v>282</v>
       </c>
@@ -24761,6 +26645,9 @@
       <c r="G631" t="s">
         <v>1449</v>
       </c>
+      <c r="H631" t="s">
+        <v>9</v>
+      </c>
       <c r="J631" t="s">
         <v>282</v>
       </c>
@@ -24784,6 +26671,9 @@
       <c r="G632" t="s">
         <v>1449</v>
       </c>
+      <c r="H632" t="s">
+        <v>9</v>
+      </c>
       <c r="J632" t="s">
         <v>282</v>
       </c>
@@ -24807,6 +26697,9 @@
       <c r="G633" t="s">
         <v>1449</v>
       </c>
+      <c r="H633" t="s">
+        <v>9</v>
+      </c>
       <c r="J633" t="s">
         <v>282</v>
       </c>
@@ -24830,6 +26723,9 @@
       <c r="G634" t="s">
         <v>1449</v>
       </c>
+      <c r="H634" t="s">
+        <v>9</v>
+      </c>
       <c r="J634" t="s">
         <v>282</v>
       </c>
@@ -24853,6 +26749,9 @@
       <c r="G635" t="s">
         <v>1449</v>
       </c>
+      <c r="H635" t="s">
+        <v>9</v>
+      </c>
       <c r="J635" t="s">
         <v>282</v>
       </c>
@@ -24876,6 +26775,9 @@
       <c r="G636" t="s">
         <v>1449</v>
       </c>
+      <c r="H636" t="s">
+        <v>9</v>
+      </c>
       <c r="J636" t="s">
         <v>10</v>
       </c>
@@ -24899,6 +26801,9 @@
       <c r="G637" t="s">
         <v>132</v>
       </c>
+      <c r="H637" t="s">
+        <v>9</v>
+      </c>
       <c r="J637" t="s">
         <v>282</v>
       </c>
@@ -24920,7 +26825,10 @@
         <v>2001</v>
       </c>
       <c r="G638" t="s">
-        <v>1501</v>
+        <v>1498</v>
+      </c>
+      <c r="H638" t="s">
+        <v>9</v>
       </c>
       <c r="J638" t="s">
         <v>285</v>
@@ -24943,7 +26851,10 @@
         <v>2012</v>
       </c>
       <c r="G639" t="s">
-        <v>1501</v>
+        <v>1498</v>
+      </c>
+      <c r="H639" t="s">
+        <v>9</v>
       </c>
       <c r="J639" t="s">
         <v>131</v>
@@ -24968,11 +26879,14 @@
       <c r="G640" t="s">
         <v>132</v>
       </c>
+      <c r="H640" t="s">
+        <v>9</v>
+      </c>
       <c r="J640" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="641" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A641" t="s">
         <v>1124</v>
       </c>
@@ -24991,11 +26905,14 @@
       <c r="G641" t="s">
         <v>132</v>
       </c>
+      <c r="H641" t="s">
+        <v>9</v>
+      </c>
       <c r="J641" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="642" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A642" t="s">
         <v>1125</v>
       </c>
@@ -25014,11 +26931,14 @@
       <c r="G642" t="s">
         <v>132</v>
       </c>
+      <c r="H642" t="s">
+        <v>9</v>
+      </c>
       <c r="J642" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="643" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A643" t="s">
         <v>1022</v>
       </c>
@@ -25037,11 +26957,14 @@
       <c r="G643" t="s">
         <v>132</v>
       </c>
+      <c r="H643" t="s">
+        <v>9</v>
+      </c>
       <c r="J643" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="644" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A644" t="s">
         <v>1126</v>
       </c>
@@ -25060,11 +26983,14 @@
       <c r="G644" t="s">
         <v>132</v>
       </c>
+      <c r="H644" t="s">
+        <v>9</v>
+      </c>
       <c r="J644" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="645" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A645" t="s">
         <v>1127</v>
       </c>
@@ -25083,11 +27009,17 @@
       <c r="G645" t="s">
         <v>132</v>
       </c>
+      <c r="H645" t="s">
+        <v>9</v>
+      </c>
       <c r="J645" t="s">
         <v>568</v>
       </c>
-    </row>
-    <row r="646" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="P645" t="s">
+        <v>1566</v>
+      </c>
+    </row>
+    <row r="646" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A646" t="s">
         <v>1129</v>
       </c>
@@ -25106,11 +27038,14 @@
       <c r="G646" t="s">
         <v>132</v>
       </c>
+      <c r="H646" t="s">
+        <v>9</v>
+      </c>
       <c r="J646" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="647" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A647" t="s">
         <v>1131</v>
       </c>
@@ -25129,11 +27064,14 @@
       <c r="G647" t="s">
         <v>132</v>
       </c>
+      <c r="H647" t="s">
+        <v>9</v>
+      </c>
       <c r="J647" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="648" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A648" t="s">
         <v>1132</v>
       </c>
@@ -25152,11 +27090,14 @@
       <c r="G648" t="s">
         <v>132</v>
       </c>
+      <c r="H648" t="s">
+        <v>9</v>
+      </c>
       <c r="J648" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="649" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A649" t="s">
         <v>1134</v>
       </c>
@@ -25175,11 +27116,14 @@
       <c r="G649" t="s">
         <v>132</v>
       </c>
+      <c r="H649" t="s">
+        <v>9</v>
+      </c>
       <c r="J649" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="650" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A650" t="s">
         <v>1401</v>
       </c>
@@ -25198,11 +27142,14 @@
       <c r="G650" t="s">
         <v>1449</v>
       </c>
+      <c r="H650" t="s">
+        <v>9</v>
+      </c>
       <c r="J650" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="651" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A651" t="s">
         <v>1138</v>
       </c>
@@ -25221,11 +27168,14 @@
       <c r="G651" t="s">
         <v>1449</v>
       </c>
+      <c r="H651" t="s">
+        <v>9</v>
+      </c>
       <c r="J651" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="652" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A652" t="s">
         <v>1141</v>
       </c>
@@ -25244,11 +27194,14 @@
       <c r="G652" t="s">
         <v>1449</v>
       </c>
+      <c r="H652" t="s">
+        <v>9</v>
+      </c>
       <c r="J652" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="653" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A653" t="s">
         <v>1143</v>
       </c>
@@ -25267,11 +27220,14 @@
       <c r="G653" t="s">
         <v>1449</v>
       </c>
+      <c r="H653" t="s">
+        <v>9</v>
+      </c>
       <c r="J653" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="654" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A654" t="s">
         <v>1144</v>
       </c>
@@ -25290,11 +27246,14 @@
       <c r="G654" t="s">
         <v>1449</v>
       </c>
+      <c r="H654" t="s">
+        <v>9</v>
+      </c>
       <c r="J654" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="655" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A655" t="s">
         <v>930</v>
       </c>
@@ -25313,11 +27272,17 @@
       <c r="G655" t="s">
         <v>1449</v>
       </c>
+      <c r="H655" t="s">
+        <v>9</v>
+      </c>
       <c r="J655" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="656" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="P655" t="s">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="656" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A656" t="s">
         <v>1146</v>
       </c>
@@ -25335,6 +27300,9 @@
       </c>
       <c r="G656" t="s">
         <v>1449</v>
+      </c>
+      <c r="H656" t="s">
+        <v>9</v>
       </c>
       <c r="J656" t="s">
         <v>285</v>
@@ -25359,6 +27327,9 @@
       <c r="G657" t="s">
         <v>1449</v>
       </c>
+      <c r="H657" t="s">
+        <v>9</v>
+      </c>
       <c r="J657" t="s">
         <v>285</v>
       </c>
@@ -25382,6 +27353,9 @@
       <c r="G658" t="s">
         <v>1449</v>
       </c>
+      <c r="H658" t="s">
+        <v>9</v>
+      </c>
       <c r="J658" t="s">
         <v>285</v>
       </c>
@@ -25405,6 +27379,9 @@
       <c r="G659" t="s">
         <v>1449</v>
       </c>
+      <c r="H659" t="s">
+        <v>9</v>
+      </c>
       <c r="J659" t="s">
         <v>285</v>
       </c>
@@ -25428,6 +27405,9 @@
       <c r="G660" t="s">
         <v>1449</v>
       </c>
+      <c r="H660" t="s">
+        <v>9</v>
+      </c>
       <c r="J660" t="s">
         <v>285</v>
       </c>
@@ -25451,6 +27431,9 @@
       <c r="G661" t="s">
         <v>1449</v>
       </c>
+      <c r="H661" t="s">
+        <v>9</v>
+      </c>
       <c r="J661" t="s">
         <v>285</v>
       </c>
@@ -25474,6 +27457,9 @@
       <c r="G662" t="s">
         <v>1449</v>
       </c>
+      <c r="H662" t="s">
+        <v>9</v>
+      </c>
       <c r="J662" t="s">
         <v>285</v>
       </c>
@@ -25497,6 +27483,9 @@
       <c r="G663" t="s">
         <v>1449</v>
       </c>
+      <c r="H663" t="s">
+        <v>9</v>
+      </c>
       <c r="J663" t="s">
         <v>285</v>
       </c>
@@ -25520,6 +27509,9 @@
       <c r="G664" t="s">
         <v>1449</v>
       </c>
+      <c r="H664" t="s">
+        <v>9</v>
+      </c>
       <c r="J664" t="s">
         <v>285</v>
       </c>
@@ -25543,6 +27535,9 @@
       <c r="G665" t="s">
         <v>1449</v>
       </c>
+      <c r="H665" t="s">
+        <v>9</v>
+      </c>
       <c r="J665" t="s">
         <v>285</v>
       </c>
@@ -25566,6 +27561,9 @@
       <c r="G666" t="s">
         <v>1449</v>
       </c>
+      <c r="H666" t="s">
+        <v>9</v>
+      </c>
       <c r="J666" t="s">
         <v>285</v>
       </c>
@@ -25589,6 +27587,9 @@
       <c r="G667" t="s">
         <v>1449</v>
       </c>
+      <c r="H667" t="s">
+        <v>9</v>
+      </c>
       <c r="J667" t="s">
         <v>285</v>
       </c>
@@ -25612,6 +27613,9 @@
       <c r="G668" t="s">
         <v>1449</v>
       </c>
+      <c r="H668" t="s">
+        <v>9</v>
+      </c>
       <c r="J668" t="s">
         <v>285</v>
       </c>
@@ -25635,6 +27639,9 @@
       <c r="G669" t="s">
         <v>1449</v>
       </c>
+      <c r="H669" t="s">
+        <v>9</v>
+      </c>
       <c r="J669" t="s">
         <v>282</v>
       </c>
@@ -25658,6 +27665,9 @@
       <c r="G670" t="s">
         <v>1449</v>
       </c>
+      <c r="H670" t="s">
+        <v>9</v>
+      </c>
       <c r="J670" t="s">
         <v>282</v>
       </c>
@@ -25681,6 +27691,9 @@
       <c r="G671" t="s">
         <v>1449</v>
       </c>
+      <c r="H671" t="s">
+        <v>9</v>
+      </c>
       <c r="J671" t="s">
         <v>282</v>
       </c>
@@ -25704,6 +27717,9 @@
       <c r="G672" t="s">
         <v>1449</v>
       </c>
+      <c r="H672" t="s">
+        <v>9</v>
+      </c>
       <c r="J672" t="s">
         <v>282</v>
       </c>
@@ -25727,6 +27743,9 @@
       <c r="G673" t="s">
         <v>1449</v>
       </c>
+      <c r="H673" t="s">
+        <v>9</v>
+      </c>
       <c r="J673" t="s">
         <v>282</v>
       </c>
@@ -25748,7 +27767,10 @@
         <v>1990</v>
       </c>
       <c r="G674" t="s">
-        <v>1453</v>
+        <v>1452</v>
+      </c>
+      <c r="H674" t="s">
+        <v>9</v>
       </c>
       <c r="J674" t="s">
         <v>285</v>
@@ -25771,7 +27793,10 @@
         <v>1989</v>
       </c>
       <c r="G675" t="s">
-        <v>1453</v>
+        <v>1452</v>
+      </c>
+      <c r="H675" t="s">
+        <v>9</v>
       </c>
       <c r="J675" t="s">
         <v>285</v>
@@ -25794,7 +27819,10 @@
         <v>1990</v>
       </c>
       <c r="G676" t="s">
-        <v>1453</v>
+        <v>1452</v>
+      </c>
+      <c r="H676" t="s">
+        <v>9</v>
       </c>
       <c r="J676" t="s">
         <v>285</v>
@@ -25819,6 +27847,9 @@
       <c r="G677" t="s">
         <v>1449</v>
       </c>
+      <c r="H677" t="s">
+        <v>9</v>
+      </c>
       <c r="J677" t="s">
         <v>282</v>
       </c>
@@ -25842,6 +27873,9 @@
       <c r="G678" t="s">
         <v>1449</v>
       </c>
+      <c r="H678" t="s">
+        <v>9</v>
+      </c>
       <c r="J678" t="s">
         <v>282</v>
       </c>
@@ -25863,7 +27897,10 @@
         <v>2015</v>
       </c>
       <c r="G679" t="s">
-        <v>1453</v>
+        <v>1452</v>
+      </c>
+      <c r="H679" t="s">
+        <v>9</v>
       </c>
       <c r="J679" t="s">
         <v>131</v>
@@ -25888,6 +27925,9 @@
       <c r="G680" t="s">
         <v>80</v>
       </c>
+      <c r="H680" t="s">
+        <v>9</v>
+      </c>
       <c r="J680" t="s">
         <v>568</v>
       </c>
@@ -25914,6 +27954,9 @@
       <c r="G681" t="s">
         <v>80</v>
       </c>
+      <c r="H681" t="s">
+        <v>9</v>
+      </c>
       <c r="J681" t="s">
         <v>568</v>
       </c>
@@ -25937,6 +27980,9 @@
       <c r="G682" t="s">
         <v>1449</v>
       </c>
+      <c r="H682" t="s">
+        <v>9</v>
+      </c>
       <c r="J682" t="s">
         <v>131</v>
       </c>
@@ -25960,6 +28006,9 @@
       <c r="G683" t="s">
         <v>1449</v>
       </c>
+      <c r="H683" t="s">
+        <v>9</v>
+      </c>
       <c r="J683" t="s">
         <v>131</v>
       </c>
@@ -25983,6 +28032,9 @@
       <c r="G684" t="s">
         <v>1449</v>
       </c>
+      <c r="H684" t="s">
+        <v>9</v>
+      </c>
       <c r="J684" t="s">
         <v>131</v>
       </c>
@@ -26006,6 +28058,9 @@
       <c r="G685" t="s">
         <v>1449</v>
       </c>
+      <c r="H685" t="s">
+        <v>9</v>
+      </c>
       <c r="J685" t="s">
         <v>131</v>
       </c>
@@ -26029,6 +28084,9 @@
       <c r="G686" t="s">
         <v>1449</v>
       </c>
+      <c r="H686" t="s">
+        <v>9</v>
+      </c>
       <c r="J686" t="s">
         <v>131</v>
       </c>
@@ -26052,6 +28110,9 @@
       <c r="G687" t="s">
         <v>1449</v>
       </c>
+      <c r="H687" t="s">
+        <v>9</v>
+      </c>
       <c r="J687" t="s">
         <v>131</v>
       </c>
@@ -26075,6 +28136,9 @@
       <c r="G688" t="s">
         <v>1449</v>
       </c>
+      <c r="H688" t="s">
+        <v>9</v>
+      </c>
       <c r="J688" t="s">
         <v>131</v>
       </c>
@@ -26098,6 +28162,9 @@
       <c r="G689" t="s">
         <v>1449</v>
       </c>
+      <c r="H689" t="s">
+        <v>9</v>
+      </c>
       <c r="J689" t="s">
         <v>131</v>
       </c>
@@ -26121,6 +28188,9 @@
       <c r="G690" t="s">
         <v>1449</v>
       </c>
+      <c r="H690" t="s">
+        <v>9</v>
+      </c>
       <c r="J690" t="s">
         <v>131</v>
       </c>
@@ -26144,6 +28214,9 @@
       <c r="G691" t="s">
         <v>1449</v>
       </c>
+      <c r="H691" t="s">
+        <v>9</v>
+      </c>
       <c r="J691" t="s">
         <v>131</v>
       </c>
@@ -26165,7 +28238,10 @@
         <v>1996</v>
       </c>
       <c r="G692" t="s">
-        <v>1453</v>
+        <v>1452</v>
+      </c>
+      <c r="H692" t="s">
+        <v>9</v>
       </c>
       <c r="J692" t="s">
         <v>708</v>
@@ -26190,6 +28266,9 @@
       <c r="G693" t="s">
         <v>89</v>
       </c>
+      <c r="H693" t="s">
+        <v>9</v>
+      </c>
       <c r="J693" t="s">
         <v>285</v>
       </c>
@@ -26211,7 +28290,10 @@
         <v>2000</v>
       </c>
       <c r="G694" t="s">
-        <v>1453</v>
+        <v>1452</v>
+      </c>
+      <c r="H694" t="s">
+        <v>9</v>
       </c>
       <c r="J694" t="s">
         <v>285</v>
@@ -26234,7 +28316,10 @@
         <v>1986</v>
       </c>
       <c r="G695" t="s">
-        <v>1461</v>
+        <v>1460</v>
+      </c>
+      <c r="H695" t="s">
+        <v>9</v>
       </c>
       <c r="J695" t="s">
         <v>285</v>
@@ -26259,6 +28344,9 @@
       <c r="G696" t="s">
         <v>80</v>
       </c>
+      <c r="H696" t="s">
+        <v>9</v>
+      </c>
       <c r="J696" t="s">
         <v>131</v>
       </c>
@@ -26282,6 +28370,9 @@
       <c r="G697" t="s">
         <v>80</v>
       </c>
+      <c r="H697" t="s">
+        <v>9</v>
+      </c>
       <c r="J697" t="s">
         <v>282</v>
       </c>
@@ -26303,7 +28394,10 @@
         <v>1987</v>
       </c>
       <c r="G698" t="s">
-        <v>1458</v>
+        <v>1457</v>
+      </c>
+      <c r="H698" t="s">
+        <v>9</v>
       </c>
       <c r="J698" t="s">
         <v>10</v>
@@ -26328,6 +28422,9 @@
       <c r="G699" t="s">
         <v>1449</v>
       </c>
+      <c r="H699" t="s">
+        <v>9</v>
+      </c>
       <c r="J699" t="s">
         <v>285</v>
       </c>
@@ -26351,6 +28448,9 @@
       <c r="G700" t="s">
         <v>1449</v>
       </c>
+      <c r="H700" t="s">
+        <v>9</v>
+      </c>
       <c r="J700" t="s">
         <v>285</v>
       </c>
@@ -26374,6 +28474,9 @@
       <c r="G701" t="s">
         <v>1449</v>
       </c>
+      <c r="H701" t="s">
+        <v>9</v>
+      </c>
       <c r="J701" t="s">
         <v>285</v>
       </c>
@@ -26397,6 +28500,9 @@
       <c r="G702" t="s">
         <v>1449</v>
       </c>
+      <c r="H702" t="s">
+        <v>9</v>
+      </c>
       <c r="J702" t="s">
         <v>285</v>
       </c>
@@ -26420,6 +28526,9 @@
       <c r="G703" t="s">
         <v>1449</v>
       </c>
+      <c r="H703" t="s">
+        <v>9</v>
+      </c>
       <c r="J703" t="s">
         <v>285</v>
       </c>
@@ -26443,6 +28552,9 @@
       <c r="G704" t="s">
         <v>1449</v>
       </c>
+      <c r="H704" t="s">
+        <v>9</v>
+      </c>
       <c r="J704" t="s">
         <v>282</v>
       </c>
@@ -26466,6 +28578,9 @@
       <c r="G705" t="s">
         <v>1449</v>
       </c>
+      <c r="H705" t="s">
+        <v>9</v>
+      </c>
       <c r="J705" t="s">
         <v>282</v>
       </c>
@@ -26489,6 +28604,9 @@
       <c r="G706" t="s">
         <v>1449</v>
       </c>
+      <c r="H706" t="s">
+        <v>9</v>
+      </c>
       <c r="J706" t="s">
         <v>285</v>
       </c>
@@ -26510,7 +28628,10 @@
         <v>2007</v>
       </c>
       <c r="G707" t="s">
-        <v>1461</v>
+        <v>1460</v>
+      </c>
+      <c r="H707" t="s">
+        <v>9</v>
       </c>
       <c r="J707" t="s">
         <v>131</v>
@@ -26533,7 +28654,10 @@
         <v>2007</v>
       </c>
       <c r="G708" t="s">
-        <v>1461</v>
+        <v>1460</v>
+      </c>
+      <c r="H708" t="s">
+        <v>9</v>
       </c>
       <c r="J708" t="s">
         <v>131</v>
@@ -26556,7 +28680,10 @@
         <v>2007</v>
       </c>
       <c r="G709" t="s">
-        <v>1461</v>
+        <v>1460</v>
+      </c>
+      <c r="H709" t="s">
+        <v>9</v>
       </c>
       <c r="J709" t="s">
         <v>131</v>
@@ -26579,7 +28706,10 @@
         <v>1990</v>
       </c>
       <c r="G710" t="s">
-        <v>1461</v>
+        <v>1460</v>
+      </c>
+      <c r="H710" t="s">
+        <v>9</v>
       </c>
       <c r="J710" t="s">
         <v>131</v>
@@ -26605,7 +28735,10 @@
         <v>2014</v>
       </c>
       <c r="G711" t="s">
-        <v>1502</v>
+        <v>1499</v>
+      </c>
+      <c r="H711" t="s">
+        <v>9</v>
       </c>
       <c r="J711" t="s">
         <v>10</v>
@@ -26630,6 +28763,9 @@
       <c r="G712" t="s">
         <v>1449</v>
       </c>
+      <c r="H712" t="s">
+        <v>9</v>
+      </c>
       <c r="J712" t="s">
         <v>282</v>
       </c>
@@ -26653,6 +28789,9 @@
       <c r="G713" t="s">
         <v>1449</v>
       </c>
+      <c r="H713" t="s">
+        <v>9</v>
+      </c>
       <c r="J713" t="s">
         <v>282</v>
       </c>
@@ -26676,6 +28815,9 @@
       <c r="G714" t="s">
         <v>1449</v>
       </c>
+      <c r="H714" t="s">
+        <v>9</v>
+      </c>
       <c r="J714" t="s">
         <v>285</v>
       </c>
@@ -26699,6 +28841,9 @@
       <c r="G715" t="s">
         <v>1449</v>
       </c>
+      <c r="H715" t="s">
+        <v>9</v>
+      </c>
       <c r="J715" t="s">
         <v>31</v>
       </c>
@@ -26722,6 +28867,9 @@
       <c r="G716" t="s">
         <v>1449</v>
       </c>
+      <c r="H716" t="s">
+        <v>9</v>
+      </c>
       <c r="J716" t="s">
         <v>10</v>
       </c>
@@ -26745,6 +28893,9 @@
       <c r="G717" t="s">
         <v>1449</v>
       </c>
+      <c r="H717" t="s">
+        <v>9</v>
+      </c>
       <c r="J717" t="s">
         <v>10</v>
       </c>
@@ -26768,6 +28919,9 @@
       <c r="G718" t="s">
         <v>1449</v>
       </c>
+      <c r="H718" t="s">
+        <v>9</v>
+      </c>
       <c r="J718" t="s">
         <v>10</v>
       </c>
@@ -26791,6 +28945,9 @@
       <c r="G719" t="s">
         <v>1449</v>
       </c>
+      <c r="H719" t="s">
+        <v>9</v>
+      </c>
       <c r="J719" t="s">
         <v>10</v>
       </c>
@@ -26814,6 +28971,9 @@
       <c r="G720" t="s">
         <v>1449</v>
       </c>
+      <c r="H720" t="s">
+        <v>9</v>
+      </c>
       <c r="J720" t="s">
         <v>10</v>
       </c>
@@ -26837,6 +28997,9 @@
       <c r="G721" t="s">
         <v>1449</v>
       </c>
+      <c r="H721" t="s">
+        <v>9</v>
+      </c>
       <c r="J721" t="s">
         <v>31</v>
       </c>
@@ -26863,6 +29026,9 @@
       <c r="G722" t="s">
         <v>1449</v>
       </c>
+      <c r="H722" t="s">
+        <v>9</v>
+      </c>
       <c r="J722" t="s">
         <v>285</v>
       </c>
@@ -26884,7 +29050,10 @@
         <v>2024</v>
       </c>
       <c r="G723" t="s">
-        <v>1461</v>
+        <v>1460</v>
+      </c>
+      <c r="H723" t="s">
+        <v>9</v>
       </c>
       <c r="J723" t="s">
         <v>131</v>
@@ -26909,6 +29078,9 @@
       <c r="G724" t="s">
         <v>1449</v>
       </c>
+      <c r="H724" t="s">
+        <v>9</v>
+      </c>
       <c r="J724" t="s">
         <v>285</v>
       </c>
@@ -26930,7 +29102,10 @@
         <v>1964</v>
       </c>
       <c r="G725" t="s">
-        <v>1503</v>
+        <v>1500</v>
+      </c>
+      <c r="H725" t="s">
+        <v>1508</v>
       </c>
       <c r="J725" t="s">
         <v>629</v>
@@ -26953,7 +29128,10 @@
         <v>2003</v>
       </c>
       <c r="G726" t="s">
-        <v>1504</v>
+        <v>1455</v>
+      </c>
+      <c r="H726" t="s">
+        <v>9</v>
       </c>
       <c r="J726" t="s">
         <v>285</v>
@@ -26978,6 +29156,9 @@
       <c r="G727" t="s">
         <v>38</v>
       </c>
+      <c r="H727" t="s">
+        <v>9</v>
+      </c>
       <c r="J727" t="s">
         <v>131</v>
       </c>
@@ -27001,6 +29182,9 @@
       <c r="G728" t="s">
         <v>38</v>
       </c>
+      <c r="H728" t="s">
+        <v>9</v>
+      </c>
       <c r="J728" t="s">
         <v>131</v>
       </c>
@@ -27024,6 +29208,9 @@
       <c r="G729" t="s">
         <v>1449</v>
       </c>
+      <c r="H729" t="s">
+        <v>9</v>
+      </c>
       <c r="J729" t="s">
         <v>131</v>
       </c>
@@ -27047,6 +29234,9 @@
       <c r="G730" t="s">
         <v>1449</v>
       </c>
+      <c r="H730" t="s">
+        <v>9</v>
+      </c>
       <c r="J730" t="s">
         <v>131</v>
       </c>
@@ -27070,6 +29260,9 @@
       <c r="G731" t="s">
         <v>1449</v>
       </c>
+      <c r="H731" t="s">
+        <v>9</v>
+      </c>
       <c r="J731" t="s">
         <v>131</v>
       </c>
@@ -27096,6 +29289,9 @@
       <c r="G732" t="s">
         <v>1448</v>
       </c>
+      <c r="H732" t="s">
+        <v>9</v>
+      </c>
       <c r="J732" t="s">
         <v>824</v>
       </c>
@@ -27119,6 +29315,9 @@
       <c r="G733" t="s">
         <v>1449</v>
       </c>
+      <c r="H733" t="s">
+        <v>9</v>
+      </c>
       <c r="J733" t="s">
         <v>10</v>
       </c>
@@ -27145,6 +29344,9 @@
       <c r="G734" t="s">
         <v>1449</v>
       </c>
+      <c r="H734" t="s">
+        <v>9</v>
+      </c>
       <c r="J734" t="s">
         <v>282</v>
       </c>
@@ -27171,6 +29373,9 @@
       <c r="G735" t="s">
         <v>1449</v>
       </c>
+      <c r="H735" t="s">
+        <v>9</v>
+      </c>
       <c r="J735" t="s">
         <v>282</v>
       </c>
@@ -27197,6 +29402,9 @@
       <c r="G736" t="s">
         <v>1449</v>
       </c>
+      <c r="H736" t="s">
+        <v>9</v>
+      </c>
       <c r="J736" t="s">
         <v>282</v>
       </c>
@@ -27223,6 +29431,9 @@
       <c r="G737" t="s">
         <v>1450</v>
       </c>
+      <c r="H737" t="s">
+        <v>9</v>
+      </c>
       <c r="J737" t="s">
         <v>282</v>
       </c>
@@ -27249,6 +29460,9 @@
       <c r="G738" t="s">
         <v>1450</v>
       </c>
+      <c r="H738" t="s">
+        <v>9</v>
+      </c>
       <c r="J738" t="s">
         <v>282</v>
       </c>
@@ -27275,6 +29489,9 @@
       <c r="G739" t="s">
         <v>1450</v>
       </c>
+      <c r="H739" t="s">
+        <v>9</v>
+      </c>
       <c r="J739" t="s">
         <v>282</v>
       </c>
@@ -27301,6 +29518,9 @@
       <c r="G740" t="s">
         <v>1450</v>
       </c>
+      <c r="H740" t="s">
+        <v>9</v>
+      </c>
       <c r="J740" t="s">
         <v>282</v>
       </c>
@@ -27327,6 +29547,9 @@
       <c r="G741" t="s">
         <v>1450</v>
       </c>
+      <c r="H741" t="s">
+        <v>9</v>
+      </c>
       <c r="J741" t="s">
         <v>282</v>
       </c>
@@ -27353,6 +29576,9 @@
       <c r="G742" t="s">
         <v>1450</v>
       </c>
+      <c r="H742" t="s">
+        <v>9</v>
+      </c>
       <c r="J742" t="s">
         <v>282</v>
       </c>
@@ -27379,6 +29605,9 @@
       <c r="G743" t="s">
         <v>1450</v>
       </c>
+      <c r="H743" t="s">
+        <v>9</v>
+      </c>
       <c r="J743" t="s">
         <v>10</v>
       </c>
@@ -27405,6 +29634,9 @@
       <c r="G744" t="s">
         <v>1450</v>
       </c>
+      <c r="H744" t="s">
+        <v>9</v>
+      </c>
       <c r="J744" t="s">
         <v>10</v>
       </c>
@@ -27431,6 +29663,9 @@
       <c r="G745" t="s">
         <v>1450</v>
       </c>
+      <c r="H745" t="s">
+        <v>9</v>
+      </c>
       <c r="J745" t="s">
         <v>10</v>
       </c>
@@ -27457,6 +29692,9 @@
       <c r="G746" t="s">
         <v>1449</v>
       </c>
+      <c r="H746" t="s">
+        <v>9</v>
+      </c>
       <c r="J746" t="s">
         <v>10</v>
       </c>
@@ -27483,6 +29721,9 @@
       <c r="G747" t="s">
         <v>1449</v>
       </c>
+      <c r="H747" t="s">
+        <v>9</v>
+      </c>
       <c r="J747" t="s">
         <v>10</v>
       </c>
@@ -27507,7 +29748,10 @@
         <v>2004</v>
       </c>
       <c r="G748" t="s">
-        <v>1451</v>
+        <v>1568</v>
+      </c>
+      <c r="H748" t="s">
+        <v>9</v>
       </c>
       <c r="J748" t="s">
         <v>10</v>
@@ -27533,7 +29777,10 @@
         <v>2004</v>
       </c>
       <c r="G749" t="s">
-        <v>1451</v>
+        <v>1568</v>
+      </c>
+      <c r="H749" t="s">
+        <v>9</v>
       </c>
       <c r="J749" t="s">
         <v>10</v>
@@ -27561,6 +29808,9 @@
       <c r="G750" t="s">
         <v>1449</v>
       </c>
+      <c r="H750" t="s">
+        <v>9</v>
+      </c>
       <c r="J750" t="s">
         <v>10</v>
       </c>
@@ -27582,7 +29832,10 @@
         <v>1998</v>
       </c>
       <c r="G751" t="s">
-        <v>1452</v>
+        <v>1451</v>
+      </c>
+      <c r="H751" t="s">
+        <v>9</v>
       </c>
       <c r="J751" t="s">
         <v>131</v>
@@ -27592,6 +29845,7 @@
   <autoFilter ref="A1:Q751" xr:uid="{D73E79B3-672E-5F4C-A79E-CB748E362622}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -35483,16 +37737,16 @@
     </row>
     <row r="314" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
-        <v>1522</v>
+        <v>1518</v>
       </c>
       <c r="B314" s="2">
         <v>0.12222222222222222</v>
       </c>
       <c r="C314" t="s">
-        <v>1523</v>
+        <v>1519</v>
       </c>
       <c r="D314" t="s">
-        <v>1524</v>
+        <v>1520</v>
       </c>
       <c r="E314" t="s">
         <v>131</v>
@@ -35506,16 +37760,16 @@
     </row>
     <row r="315" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
-        <v>1525</v>
+        <v>1521</v>
       </c>
       <c r="B315" s="2">
         <v>0.36736111111111114</v>
       </c>
       <c r="C315" t="s">
-        <v>1523</v>
+        <v>1519</v>
       </c>
       <c r="D315" t="s">
-        <v>1524</v>
+        <v>1520</v>
       </c>
       <c r="E315" t="s">
         <v>131</v>

--- a/data/music.xlsx
+++ b/data/music.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lindanakasone/Documents/GitHub/sound-and-vision/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BAB6B3B-15E7-4442-AC88-019EDAFD26BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02E651C2-EABE-C44F-ACF3-2A4F12AB3D4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8760" yWindow="2940" windowWidth="33440" windowHeight="19800" xr2:uid="{D9D4D37D-4BCE-774B-89FD-6B702A9EB150}"/>
+    <workbookView xWindow="1380" yWindow="5640" windowWidth="33440" windowHeight="19800" xr2:uid="{D9D4D37D-4BCE-774B-89FD-6B702A9EB150}"/>
   </bookViews>
   <sheets>
     <sheet name="750 songs" sheetId="5" r:id="rId1"/>
@@ -4046,9 +4046,6 @@
     <t>–</t>
   </si>
   <si>
-    <t>Portugese</t>
-  </si>
-  <si>
     <t>German; English</t>
   </si>
   <si>
@@ -4386,6 +4383,9 @@
   </si>
   <si>
     <t>Italy; Australia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portuguese </t>
   </si>
 </sst>
 </file>
@@ -5042,7 +5042,7 @@
         <v>9</v>
       </c>
       <c r="I7" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="J7" t="s">
         <v>277</v>
@@ -5071,7 +5071,7 @@
         <v>1328</v>
       </c>
       <c r="I8" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J8" t="s">
         <v>10</v>
@@ -5100,7 +5100,7 @@
         <v>1328</v>
       </c>
       <c r="I9" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J9" t="s">
         <v>299</v>
@@ -5132,7 +5132,7 @@
         <v>9</v>
       </c>
       <c r="I10" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J10" t="s">
         <v>10</v>
@@ -5164,7 +5164,7 @@
         <v>9</v>
       </c>
       <c r="I11" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J11" t="s">
         <v>10</v>
@@ -5347,7 +5347,7 @@
         <v>2009</v>
       </c>
       <c r="G17" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="H17" t="s">
         <v>9</v>
@@ -5379,7 +5379,7 @@
         <v>2009</v>
       </c>
       <c r="G18" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="H18" t="s">
         <v>9</v>
@@ -5414,7 +5414,7 @@
         <v>9</v>
       </c>
       <c r="I19" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J19" t="s">
         <v>128</v>
@@ -5443,7 +5443,7 @@
         <v>9</v>
       </c>
       <c r="I20" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J20" t="s">
         <v>128</v>
@@ -5472,7 +5472,7 @@
         <v>9</v>
       </c>
       <c r="I21" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J21" t="s">
         <v>280</v>
@@ -5617,7 +5617,7 @@
         <v>9</v>
       </c>
       <c r="I26" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="J26" t="s">
         <v>511</v>
@@ -5646,7 +5646,7 @@
         <v>9</v>
       </c>
       <c r="I27" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="J27" t="s">
         <v>513</v>
@@ -5672,10 +5672,10 @@
         <v>480</v>
       </c>
       <c r="H28" t="s">
-        <v>1329</v>
+        <v>1442</v>
       </c>
       <c r="I28" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="J28" t="s">
         <v>512</v>
@@ -5849,7 +5849,7 @@
         <v>9</v>
       </c>
       <c r="I34" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="J34" t="s">
         <v>280</v>
@@ -5910,7 +5910,7 @@
         <v>9</v>
       </c>
       <c r="I36" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J36" t="s">
         <v>128</v>
@@ -5939,7 +5939,7 @@
         <v>9</v>
       </c>
       <c r="I37" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J37" t="s">
         <v>128</v>
@@ -5971,7 +5971,7 @@
         <v>9</v>
       </c>
       <c r="I38" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J38" t="s">
         <v>128</v>
@@ -6000,7 +6000,7 @@
         <v>9</v>
       </c>
       <c r="I39" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J39" t="s">
         <v>277</v>
@@ -6029,7 +6029,7 @@
         <v>9</v>
       </c>
       <c r="I40" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J40" t="s">
         <v>128</v>
@@ -6061,7 +6061,7 @@
         <v>9</v>
       </c>
       <c r="I41" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J41" t="s">
         <v>128</v>
@@ -6090,7 +6090,7 @@
         <v>9</v>
       </c>
       <c r="I42" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J42" t="s">
         <v>128</v>
@@ -6119,7 +6119,7 @@
         <v>9</v>
       </c>
       <c r="I43" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J43" t="s">
         <v>128</v>
@@ -6148,7 +6148,7 @@
         <v>9</v>
       </c>
       <c r="I44" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J44" t="s">
         <v>128</v>
@@ -6177,7 +6177,7 @@
         <v>9</v>
       </c>
       <c r="I45" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J45" t="s">
         <v>128</v>
@@ -6206,7 +6206,7 @@
         <v>9</v>
       </c>
       <c r="I46" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J46" t="s">
         <v>128</v>
@@ -6235,7 +6235,7 @@
         <v>9</v>
       </c>
       <c r="I47" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J47" t="s">
         <v>128</v>
@@ -6264,7 +6264,7 @@
         <v>9</v>
       </c>
       <c r="I48" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J48" t="s">
         <v>277</v>
@@ -6293,7 +6293,7 @@
         <v>9</v>
       </c>
       <c r="I49" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J49" t="s">
         <v>128</v>
@@ -6325,7 +6325,7 @@
         <v>9</v>
       </c>
       <c r="I50" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J50" t="s">
         <v>128</v>
@@ -6354,7 +6354,7 @@
         <v>9</v>
       </c>
       <c r="I51" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J51" t="s">
         <v>128</v>
@@ -6383,7 +6383,7 @@
         <v>9</v>
       </c>
       <c r="I52" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J52" t="s">
         <v>128</v>
@@ -6412,7 +6412,7 @@
         <v>9</v>
       </c>
       <c r="I53" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J53" t="s">
         <v>128</v>
@@ -6444,7 +6444,7 @@
         <v>9</v>
       </c>
       <c r="I54" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J54" t="s">
         <v>277</v>
@@ -6473,7 +6473,7 @@
         <v>9</v>
       </c>
       <c r="I55" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J55" t="s">
         <v>128</v>
@@ -6502,7 +6502,7 @@
         <v>9</v>
       </c>
       <c r="I56" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J56" t="s">
         <v>128</v>
@@ -6531,7 +6531,7 @@
         <v>9</v>
       </c>
       <c r="I57" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J57" t="s">
         <v>128</v>
@@ -6560,7 +6560,7 @@
         <v>9</v>
       </c>
       <c r="I58" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J58" t="s">
         <v>128</v>
@@ -6589,7 +6589,7 @@
         <v>9</v>
       </c>
       <c r="I59" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J59" t="s">
         <v>128</v>
@@ -6618,7 +6618,7 @@
         <v>9</v>
       </c>
       <c r="I60" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J60" t="s">
         <v>128</v>
@@ -6647,7 +6647,7 @@
         <v>9</v>
       </c>
       <c r="I61" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J61" t="s">
         <v>128</v>
@@ -6679,7 +6679,7 @@
         <v>39</v>
       </c>
       <c r="I62" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J62" t="s">
         <v>78</v>
@@ -6708,7 +6708,7 @@
         <v>9</v>
       </c>
       <c r="I63" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="J63" t="s">
         <v>128</v>
@@ -6737,7 +6737,7 @@
         <v>9</v>
       </c>
       <c r="I64" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="J64" t="s">
         <v>128</v>
@@ -6766,7 +6766,7 @@
         <v>9</v>
       </c>
       <c r="I65" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="J65" t="s">
         <v>277</v>
@@ -6798,7 +6798,7 @@
         <v>9</v>
       </c>
       <c r="I66" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J66" t="s">
         <v>277</v>
@@ -6827,7 +6827,7 @@
         <v>9</v>
       </c>
       <c r="I67" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J67" t="s">
         <v>277</v>
@@ -6859,7 +6859,7 @@
         <v>9</v>
       </c>
       <c r="I68" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="J68" t="s">
         <v>128</v>
@@ -7819,7 +7819,7 @@
         <v>9</v>
       </c>
       <c r="I101" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J101" t="s">
         <v>31</v>
@@ -7848,7 +7848,7 @@
         <v>9</v>
       </c>
       <c r="I102" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J102" t="s">
         <v>128</v>
@@ -7877,7 +7877,7 @@
         <v>9</v>
       </c>
       <c r="I103" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J103" t="s">
         <v>280</v>
@@ -7909,7 +7909,7 @@
         <v>9</v>
       </c>
       <c r="I104" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J104" t="s">
         <v>128</v>
@@ -7938,7 +7938,7 @@
         <v>9</v>
       </c>
       <c r="I105" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J105" t="s">
         <v>280</v>
@@ -7967,7 +7967,7 @@
         <v>9</v>
       </c>
       <c r="I106" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J106" t="s">
         <v>280</v>
@@ -7996,7 +7996,7 @@
         <v>9</v>
       </c>
       <c r="I107" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J107" t="s">
         <v>280</v>
@@ -8025,7 +8025,7 @@
         <v>9</v>
       </c>
       <c r="I108" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J108" t="s">
         <v>280</v>
@@ -8054,7 +8054,7 @@
         <v>9</v>
       </c>
       <c r="I109" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="J109" t="s">
         <v>128</v>
@@ -8083,7 +8083,7 @@
         <v>9</v>
       </c>
       <c r="I110" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J110" t="s">
         <v>128</v>
@@ -8112,7 +8112,7 @@
         <v>39</v>
       </c>
       <c r="I111" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J111" t="s">
         <v>280</v>
@@ -8141,7 +8141,7 @@
         <v>9</v>
       </c>
       <c r="I112" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J112" t="s">
         <v>280</v>
@@ -8170,7 +8170,7 @@
         <v>9</v>
       </c>
       <c r="I113" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J113" t="s">
         <v>280</v>
@@ -8199,7 +8199,7 @@
         <v>9</v>
       </c>
       <c r="I114" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J114" t="s">
         <v>277</v>
@@ -8228,7 +8228,7 @@
         <v>9</v>
       </c>
       <c r="I115" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J115" t="s">
         <v>280</v>
@@ -8257,7 +8257,7 @@
         <v>9</v>
       </c>
       <c r="I116" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J116" t="s">
         <v>277</v>
@@ -8286,7 +8286,7 @@
         <v>9</v>
       </c>
       <c r="I117" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J117" t="s">
         <v>277</v>
@@ -8315,7 +8315,7 @@
         <v>9</v>
       </c>
       <c r="I118" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J118" t="s">
         <v>277</v>
@@ -8344,7 +8344,7 @@
         <v>9</v>
       </c>
       <c r="I119" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J119" t="s">
         <v>277</v>
@@ -8373,7 +8373,7 @@
         <v>9</v>
       </c>
       <c r="I120" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J120" t="s">
         <v>280</v>
@@ -8402,7 +8402,7 @@
         <v>9</v>
       </c>
       <c r="I121" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J121" t="s">
         <v>277</v>
@@ -8431,7 +8431,7 @@
         <v>9</v>
       </c>
       <c r="I122" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J122" t="s">
         <v>280</v>
@@ -8460,7 +8460,7 @@
         <v>9</v>
       </c>
       <c r="I123" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J123" t="s">
         <v>277</v>
@@ -8489,7 +8489,7 @@
         <v>9</v>
       </c>
       <c r="I124" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J124" t="s">
         <v>280</v>
@@ -8518,7 +8518,7 @@
         <v>9</v>
       </c>
       <c r="I125" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J125" t="s">
         <v>280</v>
@@ -8547,7 +8547,7 @@
         <v>9</v>
       </c>
       <c r="I126" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J126" t="s">
         <v>277</v>
@@ -8576,7 +8576,7 @@
         <v>9</v>
       </c>
       <c r="I127" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J127" t="s">
         <v>280</v>
@@ -8608,7 +8608,7 @@
         <v>9</v>
       </c>
       <c r="I128" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="J128" t="s">
         <v>31</v>
@@ -8666,7 +8666,7 @@
         <v>9</v>
       </c>
       <c r="I130" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="J130" t="s">
         <v>280</v>
@@ -8695,7 +8695,7 @@
         <v>9</v>
       </c>
       <c r="I131" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="J131" t="s">
         <v>280</v>
@@ -8724,7 +8724,7 @@
         <v>9</v>
       </c>
       <c r="I132" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="J132" t="s">
         <v>280</v>
@@ -8753,7 +8753,7 @@
         <v>9</v>
       </c>
       <c r="I133" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="J133" t="s">
         <v>280</v>
@@ -8782,7 +8782,7 @@
         <v>9</v>
       </c>
       <c r="I134" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="J134" t="s">
         <v>280</v>
@@ -8811,7 +8811,7 @@
         <v>9</v>
       </c>
       <c r="I135" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="J135" t="s">
         <v>280</v>
@@ -8840,7 +8840,7 @@
         <v>9</v>
       </c>
       <c r="I136" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="J136" t="s">
         <v>280</v>
@@ -8869,7 +8869,7 @@
         <v>9</v>
       </c>
       <c r="I137" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="J137" t="s">
         <v>280</v>
@@ -8898,7 +8898,7 @@
         <v>9</v>
       </c>
       <c r="I138" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="J138" t="s">
         <v>280</v>
@@ -8927,7 +8927,7 @@
         <v>9</v>
       </c>
       <c r="I139" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="J139" t="s">
         <v>280</v>
@@ -8956,7 +8956,7 @@
         <v>9</v>
       </c>
       <c r="I140" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="J140" t="s">
         <v>280</v>
@@ -8985,7 +8985,7 @@
         <v>9</v>
       </c>
       <c r="I141" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="J141" t="s">
         <v>280</v>
@@ -9014,7 +9014,7 @@
         <v>9</v>
       </c>
       <c r="I142" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="J142" t="s">
         <v>280</v>
@@ -9043,7 +9043,7 @@
         <v>9</v>
       </c>
       <c r="I143" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="J143" t="s">
         <v>280</v>
@@ -9072,7 +9072,7 @@
         <v>9</v>
       </c>
       <c r="I144" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="J144" t="s">
         <v>280</v>
@@ -9101,7 +9101,7 @@
         <v>9</v>
       </c>
       <c r="I145" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="J145" t="s">
         <v>280</v>
@@ -9130,7 +9130,7 @@
         <v>9</v>
       </c>
       <c r="I146" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="J146" t="s">
         <v>280</v>
@@ -9159,7 +9159,7 @@
         <v>9</v>
       </c>
       <c r="I147" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="J147" t="s">
         <v>280</v>
@@ -9188,7 +9188,7 @@
         <v>9</v>
       </c>
       <c r="I148" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="J148" t="s">
         <v>128</v>
@@ -9217,7 +9217,7 @@
         <v>9</v>
       </c>
       <c r="I149" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="J149" t="s">
         <v>128</v>
@@ -9246,7 +9246,7 @@
         <v>9</v>
       </c>
       <c r="I150" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="J150" t="s">
         <v>128</v>
@@ -9275,7 +9275,7 @@
         <v>9</v>
       </c>
       <c r="I151" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="J151" t="s">
         <v>128</v>
@@ -9304,7 +9304,7 @@
         <v>9</v>
       </c>
       <c r="I152" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="J152" t="s">
         <v>128</v>
@@ -9333,7 +9333,7 @@
         <v>9</v>
       </c>
       <c r="I153" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="J153" t="s">
         <v>128</v>
@@ -9362,7 +9362,7 @@
         <v>9</v>
       </c>
       <c r="I154" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="J154" t="s">
         <v>128</v>
@@ -9391,7 +9391,7 @@
         <v>9</v>
       </c>
       <c r="I155" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="J155" t="s">
         <v>128</v>
@@ -9423,7 +9423,7 @@
         <v>9</v>
       </c>
       <c r="I156" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="J156" t="s">
         <v>10</v>
@@ -9452,7 +9452,7 @@
         <v>1328</v>
       </c>
       <c r="I157" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="J157" t="s">
         <v>10</v>
@@ -9481,13 +9481,13 @@
         <v>1328</v>
       </c>
       <c r="I158" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="J158" t="s">
         <v>10</v>
       </c>
       <c r="M158" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="159" spans="1:13" x14ac:dyDescent="0.2">
@@ -9513,7 +9513,7 @@
         <v>1328</v>
       </c>
       <c r="I159" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="J159" t="s">
         <v>10</v>
@@ -9545,7 +9545,7 @@
         <v>1328</v>
       </c>
       <c r="I160" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="J160" t="s">
         <v>299</v>
@@ -9562,7 +9562,7 @@
         <v>173</v>
       </c>
       <c r="D161" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="E161" t="s">
         <v>172</v>
@@ -9574,10 +9574,10 @@
         <v>449</v>
       </c>
       <c r="H161" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="I161" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="J161" t="s">
         <v>10</v>
@@ -9606,7 +9606,7 @@
         <v>1328</v>
       </c>
       <c r="I162" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="J162" t="s">
         <v>10</v>
@@ -9635,7 +9635,7 @@
         <v>1328</v>
       </c>
       <c r="I163" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="J163" t="s">
         <v>10</v>
@@ -9664,7 +9664,7 @@
         <v>1328</v>
       </c>
       <c r="I164" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="J164" t="s">
         <v>10</v>
@@ -9693,7 +9693,7 @@
         <v>1328</v>
       </c>
       <c r="I165" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="J165" t="s">
         <v>10</v>
@@ -9722,7 +9722,7 @@
         <v>1328</v>
       </c>
       <c r="I166" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="J166" t="s">
         <v>10</v>
@@ -9739,7 +9739,7 @@
         <v>173</v>
       </c>
       <c r="D167" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="E167" t="s">
         <v>172</v>
@@ -9754,7 +9754,7 @@
         <v>9</v>
       </c>
       <c r="I167" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="J167" t="s">
         <v>10</v>
@@ -9783,7 +9783,7 @@
         <v>1328</v>
       </c>
       <c r="I168" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="J168" t="s">
         <v>578</v>
@@ -9800,7 +9800,7 @@
         <v>173</v>
       </c>
       <c r="D169" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="E169" t="s">
         <v>172</v>
@@ -9815,7 +9815,7 @@
         <v>9</v>
       </c>
       <c r="I169" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="J169" t="s">
         <v>10</v>
@@ -9832,7 +9832,7 @@
         <v>173</v>
       </c>
       <c r="D170" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="E170" t="s">
         <v>172</v>
@@ -9847,13 +9847,13 @@
         <v>1328</v>
       </c>
       <c r="I170" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="J170" t="s">
         <v>10</v>
       </c>
       <c r="L170" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.2">
@@ -9879,7 +9879,7 @@
         <v>1328</v>
       </c>
       <c r="I171" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="J171" t="s">
         <v>578</v>
@@ -9908,7 +9908,7 @@
         <v>1328</v>
       </c>
       <c r="I172" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="J172" t="s">
         <v>578</v>
@@ -9937,7 +9937,7 @@
         <v>1328</v>
       </c>
       <c r="I173" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="J173" t="s">
         <v>576</v>
@@ -9966,7 +9966,7 @@
         <v>1328</v>
       </c>
       <c r="I174" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="J174" t="s">
         <v>10</v>
@@ -9995,7 +9995,7 @@
         <v>1328</v>
       </c>
       <c r="I175" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="J175" t="s">
         <v>10</v>
@@ -10027,7 +10027,7 @@
         <v>9</v>
       </c>
       <c r="I176" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J176" t="s">
         <v>10</v>
@@ -10053,13 +10053,13 @@
         <v>2009</v>
       </c>
       <c r="G177" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="H177" t="s">
         <v>9</v>
       </c>
       <c r="I177" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J177" t="s">
         <v>277</v>
@@ -10091,7 +10091,7 @@
         <v>9</v>
       </c>
       <c r="I178" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="J178" t="s">
         <v>128</v>
@@ -10120,7 +10120,7 @@
         <v>1328</v>
       </c>
       <c r="I179" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="J179" t="s">
         <v>128</v>
@@ -10152,7 +10152,7 @@
         <v>9</v>
       </c>
       <c r="I180" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="J180" t="s">
         <v>128</v>
@@ -10184,7 +10184,7 @@
         <v>9</v>
       </c>
       <c r="I181" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="J181" t="s">
         <v>128</v>
@@ -10213,7 +10213,7 @@
         <v>1328</v>
       </c>
       <c r="I182" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="J182" t="s">
         <v>128</v>
@@ -10242,7 +10242,7 @@
         <v>1328</v>
       </c>
       <c r="I183" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="J183" t="s">
         <v>128</v>
@@ -10274,7 +10274,7 @@
         <v>9</v>
       </c>
       <c r="I184" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="J184" t="s">
         <v>128</v>
@@ -10303,7 +10303,7 @@
         <v>1328</v>
       </c>
       <c r="I185" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="J185" t="s">
         <v>128</v>
@@ -10332,7 +10332,7 @@
         <v>1328</v>
       </c>
       <c r="I186" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="J186" t="s">
         <v>128</v>
@@ -10361,7 +10361,7 @@
         <v>1328</v>
       </c>
       <c r="I187" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="J187" t="s">
         <v>128</v>
@@ -10390,7 +10390,7 @@
         <v>1328</v>
       </c>
       <c r="I188" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="J188" t="s">
         <v>128</v>
@@ -10419,7 +10419,7 @@
         <v>9</v>
       </c>
       <c r="I189" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J189" t="s">
         <v>280</v>
@@ -10448,7 +10448,7 @@
         <v>9</v>
       </c>
       <c r="I190" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J190" t="s">
         <v>128</v>
@@ -10477,7 +10477,7 @@
         <v>9</v>
       </c>
       <c r="I191" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J191" t="s">
         <v>128</v>
@@ -10506,7 +10506,7 @@
         <v>9</v>
       </c>
       <c r="I192" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J192" t="s">
         <v>128</v>
@@ -10535,7 +10535,7 @@
         <v>9</v>
       </c>
       <c r="I193" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J193" t="s">
         <v>128</v>
@@ -10564,7 +10564,7 @@
         <v>9</v>
       </c>
       <c r="I194" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J194" t="s">
         <v>128</v>
@@ -10593,7 +10593,7 @@
         <v>9</v>
       </c>
       <c r="I195" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J195" t="s">
         <v>128</v>
@@ -10622,7 +10622,7 @@
         <v>9</v>
       </c>
       <c r="I196" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="J196" t="s">
         <v>280</v>
@@ -10651,7 +10651,7 @@
         <v>9</v>
       </c>
       <c r="I197" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J197" t="s">
         <v>280</v>
@@ -10680,7 +10680,7 @@
         <v>9</v>
       </c>
       <c r="I198" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="J198" t="s">
         <v>280</v>
@@ -10857,7 +10857,7 @@
         <v>9</v>
       </c>
       <c r="I204" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J204" t="s">
         <v>128</v>
@@ -10886,7 +10886,7 @@
         <v>9</v>
       </c>
       <c r="I205" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J205" t="s">
         <v>128</v>
@@ -10915,7 +10915,7 @@
         <v>9</v>
       </c>
       <c r="I206" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J206" t="s">
         <v>609</v>
@@ -10944,7 +10944,7 @@
         <v>9</v>
       </c>
       <c r="I207" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J207" t="s">
         <v>277</v>
@@ -10973,7 +10973,7 @@
         <v>9</v>
       </c>
       <c r="I208" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J208" t="s">
         <v>609</v>
@@ -11002,7 +11002,7 @@
         <v>9</v>
       </c>
       <c r="I209" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J209" t="s">
         <v>128</v>
@@ -11031,7 +11031,7 @@
         <v>9</v>
       </c>
       <c r="I210" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J210" t="s">
         <v>277</v>
@@ -11060,7 +11060,7 @@
         <v>9</v>
       </c>
       <c r="I211" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J211" t="s">
         <v>128</v>
@@ -11089,7 +11089,7 @@
         <v>9</v>
       </c>
       <c r="I212" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J212" t="s">
         <v>128</v>
@@ -11124,7 +11124,7 @@
         <v>277</v>
       </c>
       <c r="P213" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="214" spans="1:16" x14ac:dyDescent="0.2">
@@ -11150,7 +11150,7 @@
         <v>9</v>
       </c>
       <c r="I214" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J214" t="s">
         <v>128</v>
@@ -11179,7 +11179,7 @@
         <v>9</v>
       </c>
       <c r="I215" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J215" t="s">
         <v>609</v>
@@ -11208,7 +11208,7 @@
         <v>9</v>
       </c>
       <c r="I216" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J216" t="s">
         <v>128</v>
@@ -11237,7 +11237,7 @@
         <v>9</v>
       </c>
       <c r="I217" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J217" t="s">
         <v>277</v>
@@ -11266,7 +11266,7 @@
         <v>9</v>
       </c>
       <c r="I218" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J218" t="s">
         <v>277</v>
@@ -11295,7 +11295,7 @@
         <v>9</v>
       </c>
       <c r="I219" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J219" t="s">
         <v>128</v>
@@ -11324,7 +11324,7 @@
         <v>9</v>
       </c>
       <c r="I220" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J220" t="s">
         <v>128</v>
@@ -11353,7 +11353,7 @@
         <v>9</v>
       </c>
       <c r="I221" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J221" t="s">
         <v>128</v>
@@ -11382,7 +11382,7 @@
         <v>9</v>
       </c>
       <c r="I222" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J222" t="s">
         <v>277</v>
@@ -11411,7 +11411,7 @@
         <v>9</v>
       </c>
       <c r="I223" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J223" t="s">
         <v>128</v>
@@ -11440,7 +11440,7 @@
         <v>1328</v>
       </c>
       <c r="I224" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J224" t="s">
         <v>277</v>
@@ -11469,7 +11469,7 @@
         <v>9</v>
       </c>
       <c r="I225" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J225" t="s">
         <v>277</v>
@@ -11498,7 +11498,7 @@
         <v>9</v>
       </c>
       <c r="I226" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J226" t="s">
         <v>128</v>
@@ -11527,7 +11527,7 @@
         <v>9</v>
       </c>
       <c r="I227" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J227" t="s">
         <v>277</v>
@@ -11556,7 +11556,7 @@
         <v>9</v>
       </c>
       <c r="I228" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J228" t="s">
         <v>609</v>
@@ -11585,7 +11585,7 @@
         <v>9</v>
       </c>
       <c r="I229" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J229" t="s">
         <v>128</v>
@@ -11614,7 +11614,7 @@
         <v>9</v>
       </c>
       <c r="I230" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J230" t="s">
         <v>128</v>
@@ -11643,7 +11643,7 @@
         <v>9</v>
       </c>
       <c r="I231" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J231" t="s">
         <v>128</v>
@@ -11672,7 +11672,7 @@
         <v>9</v>
       </c>
       <c r="I232" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J232" t="s">
         <v>609</v>
@@ -11701,7 +11701,7 @@
         <v>9</v>
       </c>
       <c r="I233" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J233" t="s">
         <v>609</v>
@@ -11730,7 +11730,7 @@
         <v>9</v>
       </c>
       <c r="I234" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J234" t="s">
         <v>277</v>
@@ -11759,7 +11759,7 @@
         <v>9</v>
       </c>
       <c r="I235" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J235" t="s">
         <v>128</v>
@@ -11788,7 +11788,7 @@
         <v>9</v>
       </c>
       <c r="I236" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J236" t="s">
         <v>277</v>
@@ -11817,7 +11817,7 @@
         <v>9</v>
       </c>
       <c r="I237" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J237" t="s">
         <v>280</v>
@@ -11846,7 +11846,7 @@
         <v>9</v>
       </c>
       <c r="I238" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J238" t="s">
         <v>277</v>
@@ -11875,7 +11875,7 @@
         <v>9</v>
       </c>
       <c r="I239" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J239" t="s">
         <v>277</v>
@@ -11904,7 +11904,7 @@
         <v>9</v>
       </c>
       <c r="I240" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J240" t="s">
         <v>277</v>
@@ -11933,13 +11933,13 @@
         <v>9</v>
       </c>
       <c r="I241" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J241" t="s">
         <v>277</v>
       </c>
       <c r="P241" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="242" spans="1:16" x14ac:dyDescent="0.2">
@@ -11965,7 +11965,7 @@
         <v>9</v>
       </c>
       <c r="I242" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J242" t="s">
         <v>128</v>
@@ -11994,7 +11994,7 @@
         <v>9</v>
       </c>
       <c r="I243" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J243" t="s">
         <v>128</v>
@@ -12052,7 +12052,7 @@
         <v>9</v>
       </c>
       <c r="I245" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J245" t="s">
         <v>277</v>
@@ -12081,7 +12081,7 @@
         <v>9</v>
       </c>
       <c r="I246" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J246" t="s">
         <v>128</v>
@@ -12110,7 +12110,7 @@
         <v>9</v>
       </c>
       <c r="I247" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J247" t="s">
         <v>128</v>
@@ -12139,7 +12139,7 @@
         <v>9</v>
       </c>
       <c r="I248" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J248" t="s">
         <v>128</v>
@@ -12168,7 +12168,7 @@
         <v>9</v>
       </c>
       <c r="I249" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J249" t="s">
         <v>128</v>
@@ -12197,7 +12197,7 @@
         <v>9</v>
       </c>
       <c r="I250" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J250" t="s">
         <v>277</v>
@@ -12226,7 +12226,7 @@
         <v>9</v>
       </c>
       <c r="I251" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J251" t="s">
         <v>128</v>
@@ -12255,7 +12255,7 @@
         <v>9</v>
       </c>
       <c r="I252" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J252" t="s">
         <v>277</v>
@@ -12287,7 +12287,7 @@
         <v>9</v>
       </c>
       <c r="I253" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J253" t="s">
         <v>128</v>
@@ -12345,7 +12345,7 @@
         <v>9</v>
       </c>
       <c r="I255" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J255" t="s">
         <v>128</v>
@@ -12374,7 +12374,7 @@
         <v>1328</v>
       </c>
       <c r="I256" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J256" t="s">
         <v>128</v>
@@ -12403,7 +12403,7 @@
         <v>9</v>
       </c>
       <c r="I257" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J257" t="s">
         <v>277</v>
@@ -12432,7 +12432,7 @@
         <v>1328</v>
       </c>
       <c r="I258" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J258" t="s">
         <v>277</v>
@@ -12461,7 +12461,7 @@
         <v>1328</v>
       </c>
       <c r="I259" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J259" t="s">
         <v>277</v>
@@ -12490,7 +12490,7 @@
         <v>9</v>
       </c>
       <c r="I260" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J260" t="s">
         <v>277</v>
@@ -12519,7 +12519,7 @@
         <v>9</v>
       </c>
       <c r="I261" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J261" t="s">
         <v>277</v>
@@ -12548,7 +12548,7 @@
         <v>9</v>
       </c>
       <c r="I262" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J262" t="s">
         <v>613</v>
@@ -12577,7 +12577,7 @@
         <v>1328</v>
       </c>
       <c r="I263" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J263" t="s">
         <v>613</v>
@@ -12606,7 +12606,7 @@
         <v>1328</v>
       </c>
       <c r="I264" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J264" t="s">
         <v>613</v>
@@ -12635,7 +12635,7 @@
         <v>9</v>
       </c>
       <c r="I265" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J265" t="s">
         <v>10</v>
@@ -12664,7 +12664,7 @@
         <v>9</v>
       </c>
       <c r="I266" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J266" t="s">
         <v>10</v>
@@ -12693,7 +12693,7 @@
         <v>9</v>
       </c>
       <c r="I267" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J267" t="s">
         <v>280</v>
@@ -12722,7 +12722,7 @@
         <v>9</v>
       </c>
       <c r="I268" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J268" t="s">
         <v>280</v>
@@ -12751,7 +12751,7 @@
         <v>9</v>
       </c>
       <c r="I269" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="J269" t="s">
         <v>280</v>
@@ -12809,7 +12809,7 @@
         <v>9</v>
       </c>
       <c r="I271" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="J271" t="s">
         <v>609</v>
@@ -13099,7 +13099,7 @@
         <v>1328</v>
       </c>
       <c r="I281" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="J281" t="s">
         <v>280</v>
@@ -13128,7 +13128,7 @@
         <v>1328</v>
       </c>
       <c r="I282" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="J282" t="s">
         <v>280</v>
@@ -13157,7 +13157,7 @@
         <v>1328</v>
       </c>
       <c r="I283" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="J283" t="s">
         <v>280</v>
@@ -13186,7 +13186,7 @@
         <v>1328</v>
       </c>
       <c r="I284" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="J284" t="s">
         <v>280</v>
@@ -13215,7 +13215,7 @@
         <v>1328</v>
       </c>
       <c r="I285" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="J285" t="s">
         <v>280</v>
@@ -13223,16 +13223,16 @@
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="B286" s="2">
         <v>0.36736111111111114</v>
       </c>
       <c r="C286" t="s">
+        <v>1338</v>
+      </c>
+      <c r="E286" t="s">
         <v>1339</v>
-      </c>
-      <c r="E286" t="s">
-        <v>1340</v>
       </c>
       <c r="F286">
         <v>2012</v>
@@ -13244,7 +13244,7 @@
         <v>9</v>
       </c>
       <c r="I286" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J286" t="s">
         <v>128</v>
@@ -13252,16 +13252,16 @@
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="B287" s="2">
         <v>0.12222222222222222</v>
       </c>
       <c r="C287" t="s">
+        <v>1338</v>
+      </c>
+      <c r="E287" t="s">
         <v>1339</v>
-      </c>
-      <c r="E287" t="s">
-        <v>1340</v>
       </c>
       <c r="F287">
         <v>2012</v>
@@ -13273,7 +13273,7 @@
         <v>9</v>
       </c>
       <c r="I287" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J287" t="s">
         <v>128</v>
@@ -13302,7 +13302,7 @@
         <v>9</v>
       </c>
       <c r="I288" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J288" t="s">
         <v>280</v>
@@ -13331,7 +13331,7 @@
         <v>9</v>
       </c>
       <c r="I289" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J289" t="s">
         <v>280</v>
@@ -13360,7 +13360,7 @@
         <v>9</v>
       </c>
       <c r="I290" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J290" t="s">
         <v>280</v>
@@ -13389,7 +13389,7 @@
         <v>9</v>
       </c>
       <c r="I291" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J291" t="s">
         <v>280</v>
@@ -13418,7 +13418,7 @@
         <v>9</v>
       </c>
       <c r="I292" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="J292" t="s">
         <v>277</v>
@@ -13447,13 +13447,13 @@
         <v>1328</v>
       </c>
       <c r="I293" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J293" t="s">
         <v>128</v>
       </c>
       <c r="M293" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="294" spans="1:13" x14ac:dyDescent="0.2">
@@ -13479,13 +13479,13 @@
         <v>1328</v>
       </c>
       <c r="I294" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="J294" t="s">
         <v>128</v>
       </c>
       <c r="M294" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="295" spans="1:13" x14ac:dyDescent="0.2">
@@ -13517,7 +13517,7 @@
         <v>496</v>
       </c>
       <c r="M295" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="296" spans="1:13" x14ac:dyDescent="0.2">
@@ -13543,13 +13543,13 @@
         <v>9</v>
       </c>
       <c r="I296" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J296" t="s">
         <v>496</v>
       </c>
       <c r="M296" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="297" spans="1:13" x14ac:dyDescent="0.2">
@@ -13575,7 +13575,7 @@
         <v>9</v>
       </c>
       <c r="I297" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J297" t="s">
         <v>277</v>
@@ -13604,7 +13604,7 @@
         <v>9</v>
       </c>
       <c r="I298" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J298" t="s">
         <v>277</v>
@@ -13662,13 +13662,13 @@
         <v>9</v>
       </c>
       <c r="I300" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="J300" t="s">
         <v>630</v>
       </c>
       <c r="M300" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="301" spans="1:13" x14ac:dyDescent="0.2">
@@ -13694,13 +13694,13 @@
         <v>9</v>
       </c>
       <c r="I301" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="J301" t="s">
         <v>527</v>
       </c>
       <c r="M301" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="302" spans="1:13" x14ac:dyDescent="0.2">
@@ -13726,13 +13726,13 @@
         <v>9</v>
       </c>
       <c r="I302" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="J302" t="s">
         <v>128</v>
       </c>
       <c r="M302" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="303" spans="1:13" x14ac:dyDescent="0.2">
@@ -13758,7 +13758,7 @@
         <v>9</v>
       </c>
       <c r="I303" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="J303" t="s">
         <v>277</v>
@@ -13787,7 +13787,7 @@
         <v>9</v>
       </c>
       <c r="I304" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="J304" t="s">
         <v>277</v>
@@ -13810,13 +13810,13 @@
         <v>1977</v>
       </c>
       <c r="G305" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
       </c>
       <c r="I305" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J305" t="s">
         <v>280</v>
@@ -13845,7 +13845,7 @@
         <v>9</v>
       </c>
       <c r="I306" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J306" t="s">
         <v>277</v>
@@ -13880,7 +13880,7 @@
         <v>277</v>
       </c>
       <c r="M307" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="308" spans="1:1018 1026:2042 2050:3066 3074:4090 4098:5114 5122:6138 6146:7162 7170:8186 8194:9210 9218:10234 10242:11258 11266:12282 12290:13306 13314:14330 14338:15354 15362:16378" x14ac:dyDescent="0.2">
@@ -18433,7 +18433,7 @@
         <v>9</v>
       </c>
       <c r="I323" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J323" t="s">
         <v>128</v>
@@ -18462,7 +18462,7 @@
         <v>9</v>
       </c>
       <c r="I324" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J324" t="s">
         <v>128</v>
@@ -18491,7 +18491,7 @@
         <v>9</v>
       </c>
       <c r="I325" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J325" t="s">
         <v>128</v>
@@ -18520,7 +18520,7 @@
         <v>9</v>
       </c>
       <c r="I326" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J326" t="s">
         <v>128</v>
@@ -18549,7 +18549,7 @@
         <v>9</v>
       </c>
       <c r="I327" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J327" t="s">
         <v>128</v>
@@ -18581,13 +18581,13 @@
         <v>9</v>
       </c>
       <c r="I328" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J328" t="s">
         <v>128</v>
       </c>
       <c r="M328" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="329" spans="1:16" x14ac:dyDescent="0.2">
@@ -18616,7 +18616,7 @@
         <v>9</v>
       </c>
       <c r="I329" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J329" t="s">
         <v>280</v>
@@ -18648,7 +18648,7 @@
         <v>9</v>
       </c>
       <c r="I330" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J330" t="s">
         <v>280</v>
@@ -18677,7 +18677,7 @@
         <v>9</v>
       </c>
       <c r="I331" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J331" t="s">
         <v>280</v>
@@ -18706,7 +18706,7 @@
         <v>9</v>
       </c>
       <c r="I332" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J332" t="s">
         <v>280</v>
@@ -18735,7 +18735,7 @@
         <v>9</v>
       </c>
       <c r="I333" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J333" t="s">
         <v>280</v>
@@ -18764,7 +18764,7 @@
         <v>9</v>
       </c>
       <c r="I334" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J334" t="s">
         <v>280</v>
@@ -18799,7 +18799,7 @@
         <v>9</v>
       </c>
       <c r="I335" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J335" t="s">
         <v>280</v>
@@ -18828,7 +18828,7 @@
         <v>9</v>
       </c>
       <c r="I336" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J336" t="s">
         <v>280</v>
@@ -18857,7 +18857,7 @@
         <v>9</v>
       </c>
       <c r="I337" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J337" t="s">
         <v>280</v>
@@ -18886,7 +18886,7 @@
         <v>9</v>
       </c>
       <c r="I338" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="J338" t="s">
         <v>280</v>
@@ -18915,7 +18915,7 @@
         <v>9</v>
       </c>
       <c r="I339" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J339" t="s">
         <v>280</v>
@@ -18944,7 +18944,7 @@
         <v>9</v>
       </c>
       <c r="I340" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J340" t="s">
         <v>280</v>
@@ -18973,7 +18973,7 @@
         <v>9</v>
       </c>
       <c r="I341" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J341" t="s">
         <v>280</v>
@@ -19002,7 +19002,7 @@
         <v>9</v>
       </c>
       <c r="I342" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J342" t="s">
         <v>280</v>
@@ -19031,7 +19031,7 @@
         <v>9</v>
       </c>
       <c r="I343" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J343" t="s">
         <v>280</v>
@@ -19063,7 +19063,7 @@
         <v>9</v>
       </c>
       <c r="I344" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J344" t="s">
         <v>280</v>
@@ -19092,7 +19092,7 @@
         <v>9</v>
       </c>
       <c r="I345" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J345" t="s">
         <v>128</v>
@@ -19124,7 +19124,7 @@
         <v>9</v>
       </c>
       <c r="I346" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="J346" t="s">
         <v>128</v>
@@ -19182,7 +19182,7 @@
         <v>9</v>
       </c>
       <c r="I348" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J348" t="s">
         <v>128</v>
@@ -19190,16 +19190,16 @@
     </row>
     <row r="349" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="B349" s="2">
         <v>0.1423611111111111</v>
       </c>
       <c r="C349" t="s">
+        <v>1434</v>
+      </c>
+      <c r="E349" t="s">
         <v>1435</v>
-      </c>
-      <c r="E349" t="s">
-        <v>1436</v>
       </c>
       <c r="F349">
         <v>1994</v>
@@ -19211,7 +19211,7 @@
         <v>9</v>
       </c>
       <c r="I349" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J349" t="s">
         <v>128</v>
@@ -19219,16 +19219,16 @@
     </row>
     <row r="350" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="B350" s="2">
         <v>0.125</v>
       </c>
       <c r="C350" t="s">
+        <v>1434</v>
+      </c>
+      <c r="E350" t="s">
         <v>1435</v>
-      </c>
-      <c r="E350" t="s">
-        <v>1436</v>
       </c>
       <c r="F350">
         <v>1994</v>
@@ -19240,7 +19240,7 @@
         <v>9</v>
       </c>
       <c r="I350" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J350" t="s">
         <v>128</v>
@@ -19269,7 +19269,7 @@
         <v>9</v>
       </c>
       <c r="I351" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J351" t="s">
         <v>277</v>
@@ -19298,7 +19298,7 @@
         <v>9</v>
       </c>
       <c r="I352" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J352" t="s">
         <v>128</v>
@@ -19327,7 +19327,7 @@
         <v>9</v>
       </c>
       <c r="I353" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J353" t="s">
         <v>280</v>
@@ -19356,7 +19356,7 @@
         <v>9</v>
       </c>
       <c r="I354" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J354" t="s">
         <v>128</v>
@@ -19385,7 +19385,7 @@
         <v>9</v>
       </c>
       <c r="I355" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J355" t="s">
         <v>128</v>
@@ -19414,7 +19414,7 @@
         <v>1328</v>
       </c>
       <c r="I356" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="J356" t="s">
         <v>522</v>
@@ -19443,7 +19443,7 @@
         <v>1328</v>
       </c>
       <c r="I357" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="J357" t="s">
         <v>522</v>
@@ -19472,7 +19472,7 @@
         <v>1328</v>
       </c>
       <c r="I358" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="J358" t="s">
         <v>522</v>
@@ -19501,7 +19501,7 @@
         <v>1328</v>
       </c>
       <c r="I359" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="J359" t="s">
         <v>522</v>
@@ -19530,7 +19530,7 @@
         <v>1328</v>
       </c>
       <c r="I360" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="J360" t="s">
         <v>522</v>
@@ -19559,7 +19559,7 @@
         <v>1328</v>
       </c>
       <c r="I361" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="J361" t="s">
         <v>522</v>
@@ -19623,7 +19623,7 @@
         <v>128</v>
       </c>
       <c r="M363" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="364" spans="1:16" x14ac:dyDescent="0.2">
@@ -19649,7 +19649,7 @@
         <v>9</v>
       </c>
       <c r="I364" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J364" t="s">
         <v>128</v>
@@ -19678,7 +19678,7 @@
         <v>9</v>
       </c>
       <c r="I365" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J365" t="s">
         <v>54</v>
@@ -19707,13 +19707,13 @@
         <v>9</v>
       </c>
       <c r="I366" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J366" t="s">
         <v>128</v>
       </c>
       <c r="P366" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="367" spans="1:16" x14ac:dyDescent="0.2">
@@ -19739,7 +19739,7 @@
         <v>9</v>
       </c>
       <c r="I367" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J367" t="s">
         <v>54</v>
@@ -19768,13 +19768,13 @@
         <v>9</v>
       </c>
       <c r="I368" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J368" t="s">
         <v>128</v>
       </c>
       <c r="P368" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="369" spans="1:16" x14ac:dyDescent="0.2">
@@ -19858,7 +19858,7 @@
         <v>9</v>
       </c>
       <c r="I371" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J371" t="s">
         <v>128</v>
@@ -19887,7 +19887,7 @@
         <v>9</v>
       </c>
       <c r="I372" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J372" t="s">
         <v>277</v>
@@ -19916,7 +19916,7 @@
         <v>9</v>
       </c>
       <c r="I373" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J373" t="s">
         <v>277</v>
@@ -19945,7 +19945,7 @@
         <v>9</v>
       </c>
       <c r="I374" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J374" t="s">
         <v>277</v>
@@ -19977,7 +19977,7 @@
         <v>9</v>
       </c>
       <c r="I375" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J375" t="s">
         <v>128</v>
@@ -20099,7 +20099,7 @@
         <v>1328</v>
       </c>
       <c r="I379" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="J379" t="s">
         <v>578</v>
@@ -20128,7 +20128,7 @@
         <v>1328</v>
       </c>
       <c r="I380" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="J380" t="s">
         <v>14</v>
@@ -20157,7 +20157,7 @@
         <v>1328</v>
       </c>
       <c r="I381" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="J381" t="s">
         <v>14</v>
@@ -20186,7 +20186,7 @@
         <v>1328</v>
       </c>
       <c r="I382" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="J382" t="s">
         <v>14</v>
@@ -20212,10 +20212,10 @@
         <v>88</v>
       </c>
       <c r="H383" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="I383" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="J383" t="s">
         <v>576</v>
@@ -20244,7 +20244,7 @@
         <v>1328</v>
       </c>
       <c r="I384" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="J384" t="s">
         <v>14</v>
@@ -20273,7 +20273,7 @@
         <v>1328</v>
       </c>
       <c r="I385" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="J385" t="s">
         <v>14</v>
@@ -20302,7 +20302,7 @@
         <v>1328</v>
       </c>
       <c r="I386" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="J386" t="s">
         <v>14</v>
@@ -20331,7 +20331,7 @@
         <v>1328</v>
       </c>
       <c r="I387" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="J387" t="s">
         <v>14</v>
@@ -20360,7 +20360,7 @@
         <v>1328</v>
       </c>
       <c r="I388" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="J388" t="s">
         <v>14</v>
@@ -20389,7 +20389,7 @@
         <v>1328</v>
       </c>
       <c r="I389" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="J389" t="s">
         <v>14</v>
@@ -20418,7 +20418,7 @@
         <v>1328</v>
       </c>
       <c r="I390" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="J390" t="s">
         <v>14</v>
@@ -20447,7 +20447,7 @@
         <v>1328</v>
       </c>
       <c r="I391" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="J391" t="s">
         <v>14</v>
@@ -20476,7 +20476,7 @@
         <v>1328</v>
       </c>
       <c r="I392" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="J392" t="s">
         <v>14</v>
@@ -20505,7 +20505,7 @@
         <v>1328</v>
       </c>
       <c r="I393" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="J393" t="s">
         <v>14</v>
@@ -20534,7 +20534,7 @@
         <v>1328</v>
       </c>
       <c r="I394" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="J394" t="s">
         <v>14</v>
@@ -20952,7 +20952,7 @@
         <v>522</v>
       </c>
       <c r="P408" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="409" spans="1:16" x14ac:dyDescent="0.2">
@@ -20981,7 +20981,7 @@
         <v>9</v>
       </c>
       <c r="I409" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="J409" t="s">
         <v>10</v>
@@ -21013,7 +21013,7 @@
         <v>9</v>
       </c>
       <c r="I410" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="J410" t="s">
         <v>10</v>
@@ -21021,16 +21021,16 @@
     </row>
     <row r="411" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="B411" s="2">
         <v>0.16319444444444445</v>
       </c>
       <c r="C411" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="E411" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="F411">
         <v>1992</v>
@@ -21042,7 +21042,7 @@
         <v>9</v>
       </c>
       <c r="I411" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J411" t="s">
         <v>630</v>
@@ -21071,13 +21071,13 @@
         <v>39</v>
       </c>
       <c r="I412" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="J412" t="s">
         <v>128</v>
       </c>
       <c r="M412" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="413" spans="1:16" x14ac:dyDescent="0.2">
@@ -21103,7 +21103,7 @@
         <v>39</v>
       </c>
       <c r="I413" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="J413" t="s">
         <v>128</v>
@@ -21132,7 +21132,7 @@
         <v>39</v>
       </c>
       <c r="I414" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J414" t="s">
         <v>128</v>
@@ -21161,7 +21161,7 @@
         <v>9</v>
       </c>
       <c r="I415" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J415" t="s">
         <v>10</v>
@@ -21222,13 +21222,13 @@
         <v>9</v>
       </c>
       <c r="I417" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="J417" t="s">
         <v>10</v>
       </c>
       <c r="M417" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="418" spans="1:13" x14ac:dyDescent="0.2">
@@ -21254,7 +21254,7 @@
         <v>9</v>
       </c>
       <c r="I418" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J418" t="s">
         <v>280</v>
@@ -21283,7 +21283,7 @@
         <v>9</v>
       </c>
       <c r="I419" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="J419" t="s">
         <v>277</v>
@@ -21312,7 +21312,7 @@
         <v>9</v>
       </c>
       <c r="I420" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="J420" t="s">
         <v>128</v>
@@ -21341,7 +21341,7 @@
         <v>9</v>
       </c>
       <c r="I421" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J421" t="s">
         <v>128</v>
@@ -21370,7 +21370,7 @@
         <v>9</v>
       </c>
       <c r="I422" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J422" t="s">
         <v>280</v>
@@ -21399,7 +21399,7 @@
         <v>9</v>
       </c>
       <c r="I423" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J423" t="s">
         <v>280</v>
@@ -21428,13 +21428,13 @@
         <v>1328</v>
       </c>
       <c r="I424" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="J424" t="s">
         <v>724</v>
       </c>
       <c r="M424" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="425" spans="1:13" x14ac:dyDescent="0.2">
@@ -21460,7 +21460,7 @@
         <v>9</v>
       </c>
       <c r="I425" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J425" t="s">
         <v>10</v>
@@ -21489,7 +21489,7 @@
         <v>9</v>
       </c>
       <c r="I426" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="J426" t="s">
         <v>128</v>
@@ -21497,16 +21497,16 @@
     </row>
     <row r="427" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="B427" s="2">
         <v>0.18541666666666667</v>
       </c>
       <c r="C427" t="s">
+        <v>1425</v>
+      </c>
+      <c r="E427" t="s">
         <v>1426</v>
-      </c>
-      <c r="E427" t="s">
-        <v>1427</v>
       </c>
       <c r="F427">
         <v>2009</v>
@@ -21526,16 +21526,16 @@
     </row>
     <row r="428" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="B428" s="2">
         <v>0.17847222222222223</v>
       </c>
       <c r="C428" t="s">
+        <v>1425</v>
+      </c>
+      <c r="E428" t="s">
         <v>1426</v>
-      </c>
-      <c r="E428" t="s">
-        <v>1427</v>
       </c>
       <c r="F428">
         <v>2009</v>
@@ -21555,16 +21555,16 @@
     </row>
     <row r="429" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="B429" s="2">
         <v>0.1701388888888889</v>
       </c>
       <c r="C429" t="s">
+        <v>1425</v>
+      </c>
+      <c r="E429" t="s">
         <v>1426</v>
-      </c>
-      <c r="E429" t="s">
-        <v>1427</v>
       </c>
       <c r="F429">
         <v>2009</v>
@@ -21584,16 +21584,16 @@
     </row>
     <row r="430" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="B430" s="2">
         <v>0.16319444444444445</v>
       </c>
       <c r="C430" t="s">
+        <v>1425</v>
+      </c>
+      <c r="E430" t="s">
         <v>1426</v>
-      </c>
-      <c r="E430" t="s">
-        <v>1427</v>
       </c>
       <c r="F430">
         <v>2009</v>
@@ -21634,7 +21634,7 @@
         <v>9</v>
       </c>
       <c r="I431" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J431" t="s">
         <v>10</v>
@@ -21669,7 +21669,7 @@
         <v>259</v>
       </c>
       <c r="M432" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="433" spans="1:10" x14ac:dyDescent="0.2">
@@ -21695,7 +21695,7 @@
         <v>9</v>
       </c>
       <c r="I433" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="J433" t="s">
         <v>128</v>
@@ -21724,7 +21724,7 @@
         <v>9</v>
       </c>
       <c r="I434" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="J434" t="s">
         <v>277</v>
@@ -21753,7 +21753,7 @@
         <v>9</v>
       </c>
       <c r="I435" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J435" t="s">
         <v>10</v>
@@ -21785,7 +21785,7 @@
         <v>9</v>
       </c>
       <c r="I436" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J436" t="s">
         <v>10</v>
@@ -21817,7 +21817,7 @@
         <v>9</v>
       </c>
       <c r="I437" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J437" t="s">
         <v>10</v>
@@ -21846,7 +21846,7 @@
         <v>9</v>
       </c>
       <c r="I438" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J438" t="s">
         <v>10</v>
@@ -21875,7 +21875,7 @@
         <v>9</v>
       </c>
       <c r="I439" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J439" t="s">
         <v>277</v>
@@ -21904,7 +21904,7 @@
         <v>9</v>
       </c>
       <c r="I440" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="J440" t="s">
         <v>277</v>
@@ -21933,7 +21933,7 @@
         <v>9</v>
       </c>
       <c r="I441" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J441" t="s">
         <v>277</v>
@@ -21962,7 +21962,7 @@
         <v>9</v>
       </c>
       <c r="I442" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J442" t="s">
         <v>277</v>
@@ -21991,7 +21991,7 @@
         <v>9</v>
       </c>
       <c r="I443" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J443" t="s">
         <v>277</v>
@@ -22020,7 +22020,7 @@
         <v>9</v>
       </c>
       <c r="I444" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J444" t="s">
         <v>277</v>
@@ -22049,7 +22049,7 @@
         <v>9</v>
       </c>
       <c r="I445" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J445" t="s">
         <v>277</v>
@@ -22078,7 +22078,7 @@
         <v>9</v>
       </c>
       <c r="I446" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J446" t="s">
         <v>277</v>
@@ -22107,7 +22107,7 @@
         <v>9</v>
       </c>
       <c r="I447" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J447" t="s">
         <v>10</v>
@@ -22194,7 +22194,7 @@
         <v>9</v>
       </c>
       <c r="I450" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="J450" t="s">
         <v>630</v>
@@ -22223,7 +22223,7 @@
         <v>9</v>
       </c>
       <c r="I451" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J451" t="s">
         <v>128</v>
@@ -22255,7 +22255,7 @@
         <v>9</v>
       </c>
       <c r="I452" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J452" t="s">
         <v>128</v>
@@ -22284,7 +22284,7 @@
         <v>9</v>
       </c>
       <c r="I453" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="J453" t="s">
         <v>277</v>
@@ -22313,7 +22313,7 @@
         <v>9</v>
       </c>
       <c r="I454" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="J454" t="s">
         <v>277</v>
@@ -22342,7 +22342,7 @@
         <v>9</v>
       </c>
       <c r="I455" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="J455" t="s">
         <v>277</v>
@@ -22371,7 +22371,7 @@
         <v>9</v>
       </c>
       <c r="I456" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="J456" t="s">
         <v>277</v>
@@ -22400,7 +22400,7 @@
         <v>9</v>
       </c>
       <c r="I457" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="J457" t="s">
         <v>277</v>
@@ -22429,7 +22429,7 @@
         <v>9</v>
       </c>
       <c r="I458" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="J458" t="s">
         <v>277</v>
@@ -22458,7 +22458,7 @@
         <v>9</v>
       </c>
       <c r="I459" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="J459" t="s">
         <v>277</v>
@@ -22487,7 +22487,7 @@
         <v>9</v>
       </c>
       <c r="I460" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="J460" t="s">
         <v>277</v>
@@ -22516,7 +22516,7 @@
         <v>9</v>
       </c>
       <c r="I461" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="J461" t="s">
         <v>277</v>
@@ -22545,7 +22545,7 @@
         <v>9</v>
       </c>
       <c r="I462" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="J462" t="s">
         <v>277</v>
@@ -22574,7 +22574,7 @@
         <v>9</v>
       </c>
       <c r="I463" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="J463" t="s">
         <v>277</v>
@@ -22603,7 +22603,7 @@
         <v>9</v>
       </c>
       <c r="I464" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="J464" t="s">
         <v>277</v>
@@ -22632,7 +22632,7 @@
         <v>9</v>
       </c>
       <c r="I465" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="J465" t="s">
         <v>277</v>
@@ -22661,7 +22661,7 @@
         <v>9</v>
       </c>
       <c r="I466" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="J466" t="s">
         <v>277</v>
@@ -22690,7 +22690,7 @@
         <v>9</v>
       </c>
       <c r="I467" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="J467" t="s">
         <v>277</v>
@@ -22719,7 +22719,7 @@
         <v>9</v>
       </c>
       <c r="I468" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="J468" t="s">
         <v>277</v>
@@ -22748,7 +22748,7 @@
         <v>9</v>
       </c>
       <c r="I469" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="J469" t="s">
         <v>277</v>
@@ -23009,7 +23009,7 @@
         <v>9</v>
       </c>
       <c r="I478" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="J478" t="s">
         <v>280</v>
@@ -23154,7 +23154,7 @@
         <v>9</v>
       </c>
       <c r="I483" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="J483" t="s">
         <v>277</v>
@@ -23328,7 +23328,7 @@
         <v>9</v>
       </c>
       <c r="I489" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="J489" t="s">
         <v>128</v>
@@ -23357,7 +23357,7 @@
         <v>9</v>
       </c>
       <c r="I490" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="J490" t="s">
         <v>128</v>
@@ -23386,7 +23386,7 @@
         <v>9</v>
       </c>
       <c r="I491" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J491" t="s">
         <v>522</v>
@@ -23415,7 +23415,7 @@
         <v>9</v>
       </c>
       <c r="I492" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="J492" t="s">
         <v>128</v>
@@ -23444,7 +23444,7 @@
         <v>9</v>
       </c>
       <c r="I493" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J493" t="s">
         <v>128</v>
@@ -23473,7 +23473,7 @@
         <v>9</v>
       </c>
       <c r="I494" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="J494" t="s">
         <v>128</v>
@@ -23502,7 +23502,7 @@
         <v>9</v>
       </c>
       <c r="I495" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="J495" t="s">
         <v>128</v>
@@ -23531,7 +23531,7 @@
         <v>9</v>
       </c>
       <c r="I496" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="J496" t="s">
         <v>128</v>
@@ -23560,7 +23560,7 @@
         <v>9</v>
       </c>
       <c r="I497" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="J497" t="s">
         <v>128</v>
@@ -23589,7 +23589,7 @@
         <v>9</v>
       </c>
       <c r="I498" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="J498" t="s">
         <v>128</v>
@@ -23618,7 +23618,7 @@
         <v>9</v>
       </c>
       <c r="I499" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="J499" t="s">
         <v>128</v>
@@ -23647,7 +23647,7 @@
         <v>9</v>
       </c>
       <c r="I500" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="J500" t="s">
         <v>128</v>
@@ -23676,7 +23676,7 @@
         <v>9</v>
       </c>
       <c r="I501" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="J501" t="s">
         <v>128</v>
@@ -23705,7 +23705,7 @@
         <v>9</v>
       </c>
       <c r="I502" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="J502" t="s">
         <v>128</v>
@@ -23734,7 +23734,7 @@
         <v>9</v>
       </c>
       <c r="I503" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="J503" t="s">
         <v>128</v>
@@ -23763,13 +23763,13 @@
         <v>1328</v>
       </c>
       <c r="I504" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="J504" t="s">
         <v>128</v>
       </c>
       <c r="M504" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="505" spans="1:13" x14ac:dyDescent="0.2">
@@ -23853,7 +23853,7 @@
         <v>9</v>
       </c>
       <c r="I507" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J507" t="s">
         <v>128</v>
@@ -23882,7 +23882,7 @@
         <v>9</v>
       </c>
       <c r="I508" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J508" t="s">
         <v>128</v>
@@ -23911,7 +23911,7 @@
         <v>1328</v>
       </c>
       <c r="I509" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="J509" t="s">
         <v>10</v>
@@ -23940,7 +23940,7 @@
         <v>9</v>
       </c>
       <c r="I510" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J510" t="s">
         <v>277</v>
@@ -23969,7 +23969,7 @@
         <v>9</v>
       </c>
       <c r="I511" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J511" t="s">
         <v>277</v>
@@ -23998,7 +23998,7 @@
         <v>9</v>
       </c>
       <c r="I512" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J512" t="s">
         <v>277</v>
@@ -24027,13 +24027,13 @@
         <v>9</v>
       </c>
       <c r="I513" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J513" t="s">
         <v>277</v>
       </c>
       <c r="P513" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="514" spans="1:16" x14ac:dyDescent="0.2">
@@ -24059,7 +24059,7 @@
         <v>9</v>
       </c>
       <c r="I514" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J514" t="s">
         <v>277</v>
@@ -24088,7 +24088,7 @@
         <v>9</v>
       </c>
       <c r="I515" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J515" t="s">
         <v>128</v>
@@ -24117,7 +24117,7 @@
         <v>9</v>
       </c>
       <c r="I516" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J516" t="s">
         <v>128</v>
@@ -24146,7 +24146,7 @@
         <v>9</v>
       </c>
       <c r="I517" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J517" t="s">
         <v>128</v>
@@ -24175,7 +24175,7 @@
         <v>9</v>
       </c>
       <c r="I518" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J518" t="s">
         <v>128</v>
@@ -24204,7 +24204,7 @@
         <v>9</v>
       </c>
       <c r="I519" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J519" t="s">
         <v>128</v>
@@ -24233,7 +24233,7 @@
         <v>9</v>
       </c>
       <c r="I520" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J520" t="s">
         <v>128</v>
@@ -24262,7 +24262,7 @@
         <v>9</v>
       </c>
       <c r="I521" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J521" t="s">
         <v>128</v>
@@ -24291,7 +24291,7 @@
         <v>9</v>
       </c>
       <c r="I522" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J522" t="s">
         <v>128</v>
@@ -24320,7 +24320,7 @@
         <v>9</v>
       </c>
       <c r="I523" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J523" t="s">
         <v>128</v>
@@ -24349,7 +24349,7 @@
         <v>9</v>
       </c>
       <c r="I524" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J524" t="s">
         <v>128</v>
@@ -24378,7 +24378,7 @@
         <v>1314</v>
       </c>
       <c r="H525" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="I525" t="s">
         <v>10</v>
@@ -24410,7 +24410,7 @@
         <v>9</v>
       </c>
       <c r="I526" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J526" t="s">
         <v>280</v>
@@ -24439,7 +24439,7 @@
         <v>9</v>
       </c>
       <c r="I527" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J527" t="s">
         <v>128</v>
@@ -24468,7 +24468,7 @@
         <v>9</v>
       </c>
       <c r="I528" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J528" t="s">
         <v>128</v>
@@ -24497,7 +24497,7 @@
         <v>9</v>
       </c>
       <c r="I529" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J529" t="s">
         <v>280</v>
@@ -24526,7 +24526,7 @@
         <v>9</v>
       </c>
       <c r="I530" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="J530" t="s">
         <v>280</v>
@@ -24555,7 +24555,7 @@
         <v>9</v>
       </c>
       <c r="I531" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="J531" t="s">
         <v>280</v>
@@ -24584,7 +24584,7 @@
         <v>9</v>
       </c>
       <c r="I532" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="J532" t="s">
         <v>280</v>
@@ -24613,7 +24613,7 @@
         <v>9</v>
       </c>
       <c r="I533" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="J533" t="s">
         <v>280</v>
@@ -24642,7 +24642,7 @@
         <v>9</v>
       </c>
       <c r="I534" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="J534" t="s">
         <v>280</v>
@@ -24671,7 +24671,7 @@
         <v>9</v>
       </c>
       <c r="I535" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="J535" t="s">
         <v>280</v>
@@ -24700,7 +24700,7 @@
         <v>9</v>
       </c>
       <c r="I536" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="J536" t="s">
         <v>280</v>
@@ -24729,7 +24729,7 @@
         <v>9</v>
       </c>
       <c r="I537" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J537" t="s">
         <v>10</v>
@@ -24758,7 +24758,7 @@
         <v>9</v>
       </c>
       <c r="I538" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J538" t="s">
         <v>10</v>
@@ -24787,7 +24787,7 @@
         <v>9</v>
       </c>
       <c r="I539" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J539" t="s">
         <v>10</v>
@@ -24816,7 +24816,7 @@
         <v>9</v>
       </c>
       <c r="I540" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J540" t="s">
         <v>10</v>
@@ -24845,7 +24845,7 @@
         <v>9</v>
       </c>
       <c r="I541" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J541" t="s">
         <v>10</v>
@@ -24874,7 +24874,7 @@
         <v>9</v>
       </c>
       <c r="I542" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J542" t="s">
         <v>10</v>
@@ -24903,7 +24903,7 @@
         <v>9</v>
       </c>
       <c r="I543" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J543" t="s">
         <v>10</v>
@@ -24932,7 +24932,7 @@
         <v>9</v>
       </c>
       <c r="I544" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J544" t="s">
         <v>10</v>
@@ -24961,7 +24961,7 @@
         <v>9</v>
       </c>
       <c r="I545" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J545" t="s">
         <v>10</v>
@@ -24990,7 +24990,7 @@
         <v>9</v>
       </c>
       <c r="I546" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J546" t="s">
         <v>10</v>
@@ -25019,7 +25019,7 @@
         <v>9</v>
       </c>
       <c r="I547" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J547" t="s">
         <v>10</v>
@@ -25048,7 +25048,7 @@
         <v>9</v>
       </c>
       <c r="I548" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J548" t="s">
         <v>10</v>
@@ -25077,7 +25077,7 @@
         <v>9</v>
       </c>
       <c r="I549" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J549" t="s">
         <v>10</v>
@@ -25106,7 +25106,7 @@
         <v>9</v>
       </c>
       <c r="I550" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J550" t="s">
         <v>10</v>
@@ -25251,7 +25251,7 @@
         <v>9</v>
       </c>
       <c r="I555" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J555" t="s">
         <v>128</v>
@@ -25280,7 +25280,7 @@
         <v>9</v>
       </c>
       <c r="I556" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J556" t="s">
         <v>277</v>
@@ -25309,7 +25309,7 @@
         <v>9</v>
       </c>
       <c r="I557" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J557" t="s">
         <v>280</v>
@@ -25338,7 +25338,7 @@
         <v>9</v>
       </c>
       <c r="I558" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J558" t="s">
         <v>280</v>
@@ -25367,7 +25367,7 @@
         <v>9</v>
       </c>
       <c r="I559" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J559" t="s">
         <v>277</v>
@@ -25396,7 +25396,7 @@
         <v>9</v>
       </c>
       <c r="I560" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J560" t="s">
         <v>280</v>
@@ -25425,7 +25425,7 @@
         <v>9</v>
       </c>
       <c r="I561" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J561" t="s">
         <v>277</v>
@@ -25454,7 +25454,7 @@
         <v>9</v>
       </c>
       <c r="I562" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J562" t="s">
         <v>280</v>
@@ -25483,7 +25483,7 @@
         <v>9</v>
       </c>
       <c r="I563" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J563" t="s">
         <v>280</v>
@@ -25512,7 +25512,7 @@
         <v>9</v>
       </c>
       <c r="I564" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J564" t="s">
         <v>280</v>
@@ -25541,7 +25541,7 @@
         <v>9</v>
       </c>
       <c r="I565" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J565" t="s">
         <v>280</v>
@@ -25570,13 +25570,13 @@
         <v>9</v>
       </c>
       <c r="I566" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J566" t="s">
         <v>277</v>
       </c>
       <c r="M566" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="567" spans="1:13" x14ac:dyDescent="0.2">
@@ -25602,13 +25602,13 @@
         <v>9</v>
       </c>
       <c r="I567" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J567" t="s">
         <v>277</v>
       </c>
       <c r="M567" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="568" spans="1:13" x14ac:dyDescent="0.2">
@@ -25634,13 +25634,13 @@
         <v>9</v>
       </c>
       <c r="I568" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J568" t="s">
         <v>277</v>
       </c>
       <c r="M568" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="569" spans="1:13" x14ac:dyDescent="0.2">
@@ -25666,7 +25666,7 @@
         <v>9</v>
       </c>
       <c r="I569" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J569" t="s">
         <v>277</v>
@@ -25695,7 +25695,7 @@
         <v>9</v>
       </c>
       <c r="I570" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J570" t="s">
         <v>128</v>
@@ -25724,7 +25724,7 @@
         <v>9</v>
       </c>
       <c r="I571" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J571" t="s">
         <v>128</v>
@@ -25753,7 +25753,7 @@
         <v>9</v>
       </c>
       <c r="I572" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J572" t="s">
         <v>128</v>
@@ -25782,7 +25782,7 @@
         <v>9</v>
       </c>
       <c r="I573" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="J573" t="s">
         <v>277</v>
@@ -25811,7 +25811,7 @@
         <v>9</v>
       </c>
       <c r="I574" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="J574" t="s">
         <v>277</v>
@@ -25828,7 +25828,7 @@
         <v>955</v>
       </c>
       <c r="D575" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="E575" t="s">
         <v>956</v>
@@ -25846,7 +25846,7 @@
         <v>10</v>
       </c>
       <c r="J575" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="576" spans="1:13" x14ac:dyDescent="0.2">
@@ -25892,7 +25892,7 @@
         <v>955</v>
       </c>
       <c r="D577" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="E577" t="s">
         <v>965</v>
@@ -25907,7 +25907,7 @@
         <v>9</v>
       </c>
       <c r="I577" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="J577" t="s">
         <v>31</v>
@@ -25939,7 +25939,7 @@
         <v>9</v>
       </c>
       <c r="I578" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="J578" t="s">
         <v>10</v>
@@ -25956,7 +25956,7 @@
         <v>955</v>
       </c>
       <c r="D579" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="E579" t="s">
         <v>962</v>
@@ -26003,7 +26003,7 @@
         <v>9</v>
       </c>
       <c r="I580" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="J580" t="s">
         <v>10</v>
@@ -26049,7 +26049,7 @@
         <v>955</v>
       </c>
       <c r="D582" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="E582" t="s">
         <v>965</v>
@@ -26084,7 +26084,7 @@
         <v>955</v>
       </c>
       <c r="D583" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="E583" t="s">
         <v>958</v>
@@ -26131,7 +26131,7 @@
         <v>9</v>
       </c>
       <c r="I584" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J584" t="s">
         <v>10</v>
@@ -26160,7 +26160,7 @@
         <v>9</v>
       </c>
       <c r="I585" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="J585" t="s">
         <v>277</v>
@@ -26189,7 +26189,7 @@
         <v>9</v>
       </c>
       <c r="I586" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="J586" t="s">
         <v>277</v>
@@ -26218,7 +26218,7 @@
         <v>9</v>
       </c>
       <c r="I587" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="J587" t="s">
         <v>10</v>
@@ -26247,7 +26247,7 @@
         <v>9</v>
       </c>
       <c r="I588" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="J588" t="s">
         <v>277</v>
@@ -26276,7 +26276,7 @@
         <v>9</v>
       </c>
       <c r="I589" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="J589" t="s">
         <v>277</v>
@@ -26305,7 +26305,7 @@
         <v>9</v>
       </c>
       <c r="I590" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="J590" t="s">
         <v>277</v>
@@ -26334,7 +26334,7 @@
         <v>9</v>
       </c>
       <c r="I591" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="J591" t="s">
         <v>277</v>
@@ -26363,7 +26363,7 @@
         <v>9</v>
       </c>
       <c r="I592" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="J592" t="s">
         <v>277</v>
@@ -26392,7 +26392,7 @@
         <v>9</v>
       </c>
       <c r="I593" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="J593" t="s">
         <v>277</v>
@@ -26421,7 +26421,7 @@
         <v>9</v>
       </c>
       <c r="I594" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J594" t="s">
         <v>277</v>
@@ -26450,7 +26450,7 @@
         <v>9</v>
       </c>
       <c r="I595" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J595" t="s">
         <v>277</v>
@@ -26479,7 +26479,7 @@
         <v>9</v>
       </c>
       <c r="I596" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J596" t="s">
         <v>277</v>
@@ -26508,7 +26508,7 @@
         <v>9</v>
       </c>
       <c r="I597" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J597" t="s">
         <v>277</v>
@@ -26537,7 +26537,7 @@
         <v>9</v>
       </c>
       <c r="I598" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J598" t="s">
         <v>277</v>
@@ -26566,7 +26566,7 @@
         <v>9</v>
       </c>
       <c r="I599" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J599" t="s">
         <v>277</v>
@@ -26595,7 +26595,7 @@
         <v>9</v>
       </c>
       <c r="I600" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J600" t="s">
         <v>277</v>
@@ -26659,7 +26659,7 @@
         <v>522</v>
       </c>
       <c r="P602" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="603" spans="1:16" x14ac:dyDescent="0.2">
@@ -26714,7 +26714,7 @@
         <v>9</v>
       </c>
       <c r="I604" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J604" t="s">
         <v>280</v>
@@ -26743,7 +26743,7 @@
         <v>9</v>
       </c>
       <c r="I605" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J605" t="s">
         <v>277</v>
@@ -26751,7 +26751,7 @@
     </row>
     <row r="606" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A606" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="B606" s="2">
         <v>0.1875</v>
@@ -26760,7 +26760,7 @@
         <v>1000</v>
       </c>
       <c r="E606" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="F606">
         <v>1982</v>
@@ -26772,7 +26772,7 @@
         <v>9</v>
       </c>
       <c r="I606" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J606" t="s">
         <v>280</v>
@@ -26801,7 +26801,7 @@
         <v>9</v>
       </c>
       <c r="I607" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J607" t="s">
         <v>280</v>
@@ -26809,7 +26809,7 @@
     </row>
     <row r="608" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A608" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="B608" s="2">
         <v>0.1701388888888889</v>
@@ -26830,7 +26830,7 @@
         <v>9</v>
       </c>
       <c r="I608" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J608" t="s">
         <v>280</v>
@@ -26859,7 +26859,7 @@
         <v>9</v>
       </c>
       <c r="I609" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J609" t="s">
         <v>280</v>
@@ -26888,18 +26888,18 @@
         <v>9</v>
       </c>
       <c r="I610" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J610" t="s">
         <v>277</v>
       </c>
       <c r="P610" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="611" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A611" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="B611" s="2">
         <v>0.15902777777777777</v>
@@ -26920,7 +26920,7 @@
         <v>9</v>
       </c>
       <c r="I611" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J611" t="s">
         <v>277</v>
@@ -26949,7 +26949,7 @@
         <v>9</v>
       </c>
       <c r="I612" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J612" t="s">
         <v>280</v>
@@ -26978,7 +26978,7 @@
         <v>9</v>
       </c>
       <c r="I613" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J613" t="s">
         <v>280</v>
@@ -27007,7 +27007,7 @@
         <v>9</v>
       </c>
       <c r="I614" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J614" t="s">
         <v>280</v>
@@ -27036,7 +27036,7 @@
         <v>9</v>
       </c>
       <c r="I615" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J615" t="s">
         <v>280</v>
@@ -27065,7 +27065,7 @@
         <v>9</v>
       </c>
       <c r="I616" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J616" t="s">
         <v>280</v>
@@ -27094,7 +27094,7 @@
         <v>9</v>
       </c>
       <c r="I617" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J617" t="s">
         <v>277</v>
@@ -27123,7 +27123,7 @@
         <v>9</v>
       </c>
       <c r="I618" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J618" t="s">
         <v>277</v>
@@ -27152,7 +27152,7 @@
         <v>9</v>
       </c>
       <c r="I619" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="J619" t="s">
         <v>522</v>
@@ -27184,7 +27184,7 @@
         <v>9</v>
       </c>
       <c r="I620" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="J620" t="s">
         <v>522</v>
@@ -27216,7 +27216,7 @@
         <v>9</v>
       </c>
       <c r="I621" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J621" t="s">
         <v>128</v>
@@ -27248,7 +27248,7 @@
         <v>9</v>
       </c>
       <c r="I622" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J622" t="s">
         <v>128</v>
@@ -27280,7 +27280,7 @@
         <v>9</v>
       </c>
       <c r="I623" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J623" t="s">
         <v>128</v>
@@ -27312,7 +27312,7 @@
         <v>9</v>
       </c>
       <c r="I624" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J624" t="s">
         <v>128</v>
@@ -27344,7 +27344,7 @@
         <v>9</v>
       </c>
       <c r="I625" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J625" t="s">
         <v>128</v>
@@ -27376,7 +27376,7 @@
         <v>9</v>
       </c>
       <c r="I626" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J626" t="s">
         <v>128</v>
@@ -27408,7 +27408,7 @@
         <v>9</v>
       </c>
       <c r="I627" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J627" t="s">
         <v>128</v>
@@ -27440,7 +27440,7 @@
         <v>9</v>
       </c>
       <c r="I628" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J628" t="s">
         <v>128</v>
@@ -27527,7 +27527,7 @@
         <v>9</v>
       </c>
       <c r="I631" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J631" t="s">
         <v>630</v>
@@ -27556,7 +27556,7 @@
         <v>9</v>
       </c>
       <c r="I632" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J632" t="s">
         <v>280</v>
@@ -27585,7 +27585,7 @@
         <v>9</v>
       </c>
       <c r="I633" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="J633" t="s">
         <v>280</v>
@@ -27614,7 +27614,7 @@
         <v>9</v>
       </c>
       <c r="I634" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J634" t="s">
         <v>277</v>
@@ -27643,7 +27643,7 @@
         <v>9</v>
       </c>
       <c r="I635" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J635" t="s">
         <v>128</v>
@@ -27701,7 +27701,7 @@
         <v>9</v>
       </c>
       <c r="I637" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J637" t="s">
         <v>280</v>
@@ -27730,7 +27730,7 @@
         <v>9</v>
       </c>
       <c r="I638" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J638" t="s">
         <v>280</v>
@@ -27759,7 +27759,7 @@
         <v>9</v>
       </c>
       <c r="I639" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J639" t="s">
         <v>280</v>
@@ -27788,7 +27788,7 @@
         <v>9</v>
       </c>
       <c r="I640" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J640" t="s">
         <v>280</v>
@@ -27817,7 +27817,7 @@
         <v>9</v>
       </c>
       <c r="I641" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J641" t="s">
         <v>280</v>
@@ -27878,7 +27878,7 @@
         <v>9</v>
       </c>
       <c r="I643" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="J643" t="s">
         <v>280</v>
@@ -27907,13 +27907,13 @@
         <v>9</v>
       </c>
       <c r="I644" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="J644" t="s">
         <v>277</v>
       </c>
       <c r="P644" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="645" spans="1:16" x14ac:dyDescent="0.2">
@@ -27942,7 +27942,7 @@
         <v>9</v>
       </c>
       <c r="I645" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J645" t="s">
         <v>522</v>
@@ -27971,7 +27971,7 @@
         <v>9</v>
       </c>
       <c r="I646" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J646" t="s">
         <v>527</v>
@@ -28000,13 +28000,13 @@
         <v>9</v>
       </c>
       <c r="I647" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J647" t="s">
         <v>10</v>
       </c>
       <c r="P647" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="648" spans="1:16" x14ac:dyDescent="0.2">
@@ -28090,7 +28090,7 @@
         <v>9</v>
       </c>
       <c r="I650" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J650" t="s">
         <v>277</v>
@@ -28119,7 +28119,7 @@
         <v>9</v>
       </c>
       <c r="I651" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J651" t="s">
         <v>277</v>
@@ -28148,7 +28148,7 @@
         <v>9</v>
       </c>
       <c r="I652" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J652" t="s">
         <v>128</v>
@@ -28177,13 +28177,13 @@
         <v>9</v>
       </c>
       <c r="I653" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="J653" t="s">
         <v>128</v>
       </c>
       <c r="M653" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="654" spans="1:16" x14ac:dyDescent="0.2">
@@ -28209,7 +28209,7 @@
         <v>9</v>
       </c>
       <c r="I654" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J654" t="s">
         <v>128</v>
@@ -28238,7 +28238,7 @@
         <v>9</v>
       </c>
       <c r="I655" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J655" t="s">
         <v>128</v>
@@ -28267,7 +28267,7 @@
         <v>9</v>
       </c>
       <c r="I656" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J656" t="s">
         <v>128</v>
@@ -28296,7 +28296,7 @@
         <v>9</v>
       </c>
       <c r="I657" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J657" t="s">
         <v>128</v>
@@ -28325,7 +28325,7 @@
         <v>9</v>
       </c>
       <c r="I658" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J658" t="s">
         <v>128</v>
@@ -28354,7 +28354,7 @@
         <v>9</v>
       </c>
       <c r="I659" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J659" t="s">
         <v>128</v>
@@ -28383,7 +28383,7 @@
         <v>9</v>
       </c>
       <c r="I660" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J660" t="s">
         <v>128</v>
@@ -28412,7 +28412,7 @@
         <v>9</v>
       </c>
       <c r="I661" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J661" t="s">
         <v>128</v>
@@ -28441,7 +28441,7 @@
         <v>9</v>
       </c>
       <c r="I662" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J662" t="s">
         <v>128</v>
@@ -28470,7 +28470,7 @@
         <v>9</v>
       </c>
       <c r="I663" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J663" t="s">
         <v>280</v>
@@ -28528,7 +28528,7 @@
         <v>9</v>
       </c>
       <c r="I665" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="J665" t="s">
         <v>277</v>
@@ -28560,7 +28560,7 @@
         <v>9</v>
       </c>
       <c r="I666" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J666" t="s">
         <v>128</v>
@@ -28850,7 +28850,7 @@
         <v>9</v>
       </c>
       <c r="I676" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="J676" t="s">
         <v>128</v>
@@ -28908,7 +28908,7 @@
         <v>9</v>
       </c>
       <c r="I678" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J678" t="s">
         <v>280</v>
@@ -28966,7 +28966,7 @@
         <v>9</v>
       </c>
       <c r="I680" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J680" t="s">
         <v>128</v>
@@ -29024,7 +29024,7 @@
         <v>9</v>
       </c>
       <c r="I682" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J682" t="s">
         <v>280</v>
@@ -29111,7 +29111,7 @@
         <v>9</v>
       </c>
       <c r="I685" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J685" t="s">
         <v>280</v>
@@ -29140,7 +29140,7 @@
         <v>9</v>
       </c>
       <c r="I686" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J686" t="s">
         <v>280</v>
@@ -29169,7 +29169,7 @@
         <v>9</v>
       </c>
       <c r="I687" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J687" t="s">
         <v>280</v>
@@ -29198,7 +29198,7 @@
         <v>9</v>
       </c>
       <c r="I688" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J688" t="s">
         <v>280</v>
@@ -29227,7 +29227,7 @@
         <v>9</v>
       </c>
       <c r="I689" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J689" t="s">
         <v>280</v>
@@ -29256,7 +29256,7 @@
         <v>9</v>
       </c>
       <c r="I690" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J690" t="s">
         <v>280</v>
@@ -29285,7 +29285,7 @@
         <v>9</v>
       </c>
       <c r="I691" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J691" t="s">
         <v>280</v>
@@ -29314,7 +29314,7 @@
         <v>9</v>
       </c>
       <c r="I692" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J692" t="s">
         <v>277</v>
@@ -29343,7 +29343,7 @@
         <v>9</v>
       </c>
       <c r="I693" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J693" t="s">
         <v>277</v>
@@ -29372,7 +29372,7 @@
         <v>9</v>
       </c>
       <c r="I694" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J694" t="s">
         <v>277</v>
@@ -29401,7 +29401,7 @@
         <v>9</v>
       </c>
       <c r="I695" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J695" t="s">
         <v>277</v>
@@ -29430,7 +29430,7 @@
         <v>9</v>
       </c>
       <c r="I696" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J696" t="s">
         <v>280</v>
@@ -29459,7 +29459,7 @@
         <v>9</v>
       </c>
       <c r="I697" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J697" t="s">
         <v>280</v>
@@ -29488,7 +29488,7 @@
         <v>9</v>
       </c>
       <c r="I698" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J698" t="s">
         <v>277</v>
@@ -29517,7 +29517,7 @@
         <v>9</v>
       </c>
       <c r="I699" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J699" t="s">
         <v>280</v>
@@ -29546,7 +29546,7 @@
         <v>9</v>
       </c>
       <c r="I700" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J700" t="s">
         <v>280</v>
@@ -29575,7 +29575,7 @@
         <v>9</v>
       </c>
       <c r="I701" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J701" t="s">
         <v>280</v>
@@ -29583,16 +29583,16 @@
     </row>
     <row r="702" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A702" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B702" s="2">
         <v>0.14166666666666666</v>
       </c>
       <c r="C702" t="s">
+        <v>1438</v>
+      </c>
+      <c r="E702" t="s">
         <v>1439</v>
-      </c>
-      <c r="E702" t="s">
-        <v>1440</v>
       </c>
       <c r="F702">
         <v>1986</v>
@@ -29604,7 +29604,7 @@
         <v>9</v>
       </c>
       <c r="I702" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J702" t="s">
         <v>280</v>
@@ -29633,7 +29633,7 @@
         <v>9</v>
       </c>
       <c r="I703" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="J703" t="s">
         <v>128</v>
@@ -29662,7 +29662,7 @@
         <v>9</v>
       </c>
       <c r="I704" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="J704" t="s">
         <v>280</v>
@@ -29691,7 +29691,7 @@
         <v>9</v>
       </c>
       <c r="I705" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J705" t="s">
         <v>277</v>
@@ -29720,7 +29720,7 @@
         <v>9</v>
       </c>
       <c r="I706" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J706" t="s">
         <v>277</v>
@@ -29749,7 +29749,7 @@
         <v>9</v>
       </c>
       <c r="I707" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J707" t="s">
         <v>280</v>
@@ -29807,7 +29807,7 @@
         <v>9</v>
       </c>
       <c r="I709" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J709" t="s">
         <v>280</v>
@@ -29836,7 +29836,7 @@
         <v>9</v>
       </c>
       <c r="I710" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J710" t="s">
         <v>128</v>
@@ -29865,7 +29865,7 @@
         <v>9</v>
       </c>
       <c r="I711" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J711" t="s">
         <v>128</v>
@@ -29894,7 +29894,7 @@
         <v>9</v>
       </c>
       <c r="I712" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J712" t="s">
         <v>128</v>
@@ -29923,7 +29923,7 @@
         <v>9</v>
       </c>
       <c r="I713" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J713" t="s">
         <v>128</v>
@@ -29952,7 +29952,7 @@
         <v>9</v>
       </c>
       <c r="I714" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J714" t="s">
         <v>128</v>
@@ -29981,7 +29981,7 @@
         <v>9</v>
       </c>
       <c r="I715" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J715" t="s">
         <v>128</v>
@@ -30010,7 +30010,7 @@
         <v>9</v>
       </c>
       <c r="I716" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J716" t="s">
         <v>128</v>
@@ -30042,7 +30042,7 @@
         <v>9</v>
       </c>
       <c r="I717" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J717" t="s">
         <v>10</v>
@@ -30071,7 +30071,7 @@
         <v>9</v>
       </c>
       <c r="I718" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J718" t="s">
         <v>277</v>
@@ -30100,7 +30100,7 @@
         <v>9</v>
       </c>
       <c r="I719" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J719" t="s">
         <v>277</v>
@@ -30129,7 +30129,7 @@
         <v>9</v>
       </c>
       <c r="I720" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="J720" t="s">
         <v>280</v>
@@ -30158,7 +30158,7 @@
         <v>9</v>
       </c>
       <c r="I721" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="J721" t="s">
         <v>31</v>
@@ -30245,7 +30245,7 @@
         <v>9</v>
       </c>
       <c r="I724" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="J724" t="s">
         <v>10</v>
@@ -30274,7 +30274,7 @@
         <v>9</v>
       </c>
       <c r="I725" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="J725" t="s">
         <v>10</v>
@@ -30303,7 +30303,7 @@
         <v>9</v>
       </c>
       <c r="I726" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="J726" t="s">
         <v>10</v>
@@ -30332,7 +30332,7 @@
         <v>9</v>
       </c>
       <c r="I727" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="J727" t="s">
         <v>10</v>
@@ -30364,7 +30364,7 @@
         <v>9</v>
       </c>
       <c r="I728" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J728" t="s">
         <v>280</v>
@@ -30393,7 +30393,7 @@
         <v>9</v>
       </c>
       <c r="I729" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="J729" t="s">
         <v>128</v>
@@ -30428,7 +30428,7 @@
         <v>578</v>
       </c>
       <c r="M730" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="731" spans="1:13" x14ac:dyDescent="0.2">
@@ -30547,7 +30547,7 @@
         <v>9</v>
       </c>
       <c r="I734" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J734" t="s">
         <v>10</v>
@@ -30573,13 +30573,13 @@
         <v>2004</v>
       </c>
       <c r="G735" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
       </c>
       <c r="I735" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J735" t="s">
         <v>10</v>
@@ -30611,7 +30611,7 @@
         <v>9</v>
       </c>
       <c r="I736" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J736" t="s">
         <v>10</v>
@@ -30643,7 +30643,7 @@
         <v>9</v>
       </c>
       <c r="I737" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J737" t="s">
         <v>277</v>
@@ -30675,7 +30675,7 @@
         <v>9</v>
       </c>
       <c r="I738" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J738" t="s">
         <v>10</v>
@@ -30707,7 +30707,7 @@
         <v>9</v>
       </c>
       <c r="I739" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J739" t="s">
         <v>10</v>
@@ -30736,7 +30736,7 @@
         <v>1328</v>
       </c>
       <c r="I740" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J740" t="s">
         <v>10</v>
@@ -30762,13 +30762,13 @@
         <v>2004</v>
       </c>
       <c r="G741" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
       </c>
       <c r="I741" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J741" t="s">
         <v>10</v>
@@ -30800,7 +30800,7 @@
         <v>9</v>
       </c>
       <c r="I742" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J742" t="s">
         <v>277</v>
@@ -30832,7 +30832,7 @@
         <v>9</v>
       </c>
       <c r="I743" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J743" t="s">
         <v>10</v>
@@ -30864,7 +30864,7 @@
         <v>9</v>
       </c>
       <c r="I744" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J744" t="s">
         <v>277</v>
@@ -30896,7 +30896,7 @@
         <v>9</v>
       </c>
       <c r="I745" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J745" t="s">
         <v>277</v>
@@ -30928,7 +30928,7 @@
         <v>9</v>
       </c>
       <c r="I746" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J746" t="s">
         <v>277</v>
@@ -30960,7 +30960,7 @@
         <v>9</v>
       </c>
       <c r="I747" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J747" t="s">
         <v>277</v>
@@ -30992,7 +30992,7 @@
         <v>9</v>
       </c>
       <c r="I748" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J748" t="s">
         <v>10</v>
@@ -31024,7 +31024,7 @@
         <v>9</v>
       </c>
       <c r="I749" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J749" t="s">
         <v>277</v>
@@ -31056,7 +31056,7 @@
         <v>9</v>
       </c>
       <c r="I750" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J750" t="s">
         <v>277</v>
@@ -31088,7 +31088,7 @@
         <v>9</v>
       </c>
       <c r="I751" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J751" t="s">
         <v>277</v>

--- a/data/music.xlsx
+++ b/data/music.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lindanakasone/Documents/GitHub/sound-and-vision/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE600016-6B5D-A647-AAD4-74D91B076F0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8294ACCB-83B9-8D42-AA9C-265872481EB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1380" yWindow="5640" windowWidth="33440" windowHeight="19800" xr2:uid="{D9D4D37D-4BCE-774B-89FD-6B702A9EB150}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5389" uniqueCount="1442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5389" uniqueCount="1441">
   <si>
     <t>Song</t>
   </si>
@@ -3882,9 +3882,6 @@
   </si>
   <si>
     <t>US - California</t>
-  </si>
-  <si>
-    <t>Italy; Ireland</t>
   </si>
   <si>
     <t>US - Illinois</t>
@@ -4841,7 +4838,7 @@
         <v>1269</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>1</v>
@@ -4853,22 +4850,22 @@
         <v>183</v>
       </c>
       <c r="L1" s="3" t="s">
+        <v>1321</v>
+      </c>
+      <c r="M1" s="3" t="s">
         <v>1322</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>1323</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="P1" s="3" t="s">
         <v>124</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.2">
@@ -5039,7 +5036,7 @@
         <v>9</v>
       </c>
       <c r="I7" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="J7" t="s">
         <v>277</v>
@@ -5065,10 +5062,10 @@
         <v>38</v>
       </c>
       <c r="H8" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I8" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J8" t="s">
         <v>10</v>
@@ -5094,10 +5091,10 @@
         <v>38</v>
       </c>
       <c r="H9" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I9" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J9" t="s">
         <v>299</v>
@@ -5129,7 +5126,7 @@
         <v>9</v>
       </c>
       <c r="I10" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J10" t="s">
         <v>10</v>
@@ -5161,7 +5158,7 @@
         <v>9</v>
       </c>
       <c r="I11" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J11" t="s">
         <v>10</v>
@@ -5251,7 +5248,7 @@
         <v>2009</v>
       </c>
       <c r="G14" t="s">
-        <v>1275</v>
+        <v>1439</v>
       </c>
       <c r="H14" t="s">
         <v>9</v>
@@ -5315,7 +5312,7 @@
         <v>150</v>
       </c>
       <c r="H16" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I16" t="s">
         <v>259</v>
@@ -5344,7 +5341,7 @@
         <v>2009</v>
       </c>
       <c r="G17" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="H17" t="s">
         <v>9</v>
@@ -5376,7 +5373,7 @@
         <v>2009</v>
       </c>
       <c r="G18" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="H18" t="s">
         <v>9</v>
@@ -5405,13 +5402,13 @@
         <v>2005</v>
       </c>
       <c r="G19" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="H19" t="s">
         <v>9</v>
       </c>
       <c r="I19" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J19" t="s">
         <v>128</v>
@@ -5434,13 +5431,13 @@
         <v>2005</v>
       </c>
       <c r="G20" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="H20" t="s">
         <v>9</v>
       </c>
       <c r="I20" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J20" t="s">
         <v>128</v>
@@ -5469,7 +5466,7 @@
         <v>9</v>
       </c>
       <c r="I21" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J21" t="s">
         <v>280</v>
@@ -5608,13 +5605,13 @@
         <v>1968</v>
       </c>
       <c r="G26" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="H26" t="s">
         <v>9</v>
       </c>
       <c r="I26" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="J26" t="s">
         <v>511</v>
@@ -5643,7 +5640,7 @@
         <v>9</v>
       </c>
       <c r="I27" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="J27" t="s">
         <v>513</v>
@@ -5669,10 +5666,10 @@
         <v>480</v>
       </c>
       <c r="H28" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="I28" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="J28" t="s">
         <v>512</v>
@@ -5840,13 +5837,13 @@
         <v>2003</v>
       </c>
       <c r="G34" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="H34" t="s">
         <v>9</v>
       </c>
       <c r="I34" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J34" t="s">
         <v>280</v>
@@ -5872,7 +5869,7 @@
         <v>2006</v>
       </c>
       <c r="G35" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="H35" t="s">
         <v>9</v>
@@ -5907,7 +5904,7 @@
         <v>9</v>
       </c>
       <c r="I36" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="J36" t="s">
         <v>128</v>
@@ -5936,7 +5933,7 @@
         <v>9</v>
       </c>
       <c r="I37" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="J37" t="s">
         <v>128</v>
@@ -5968,7 +5965,7 @@
         <v>9</v>
       </c>
       <c r="I38" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J38" t="s">
         <v>128</v>
@@ -5997,7 +5994,7 @@
         <v>9</v>
       </c>
       <c r="I39" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J39" t="s">
         <v>277</v>
@@ -6026,7 +6023,7 @@
         <v>9</v>
       </c>
       <c r="I40" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J40" t="s">
         <v>128</v>
@@ -6058,7 +6055,7 @@
         <v>9</v>
       </c>
       <c r="I41" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J41" t="s">
         <v>128</v>
@@ -6087,7 +6084,7 @@
         <v>9</v>
       </c>
       <c r="I42" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J42" t="s">
         <v>128</v>
@@ -6116,7 +6113,7 @@
         <v>9</v>
       </c>
       <c r="I43" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J43" t="s">
         <v>128</v>
@@ -6145,7 +6142,7 @@
         <v>9</v>
       </c>
       <c r="I44" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J44" t="s">
         <v>128</v>
@@ -6174,7 +6171,7 @@
         <v>9</v>
       </c>
       <c r="I45" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J45" t="s">
         <v>128</v>
@@ -6203,7 +6200,7 @@
         <v>9</v>
       </c>
       <c r="I46" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J46" t="s">
         <v>128</v>
@@ -6232,7 +6229,7 @@
         <v>9</v>
       </c>
       <c r="I47" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J47" t="s">
         <v>128</v>
@@ -6261,7 +6258,7 @@
         <v>9</v>
       </c>
       <c r="I48" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J48" t="s">
         <v>277</v>
@@ -6290,7 +6287,7 @@
         <v>9</v>
       </c>
       <c r="I49" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J49" t="s">
         <v>128</v>
@@ -6322,7 +6319,7 @@
         <v>9</v>
       </c>
       <c r="I50" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J50" t="s">
         <v>128</v>
@@ -6351,7 +6348,7 @@
         <v>9</v>
       </c>
       <c r="I51" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J51" t="s">
         <v>128</v>
@@ -6380,7 +6377,7 @@
         <v>9</v>
       </c>
       <c r="I52" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J52" t="s">
         <v>128</v>
@@ -6409,7 +6406,7 @@
         <v>9</v>
       </c>
       <c r="I53" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J53" t="s">
         <v>128</v>
@@ -6441,7 +6438,7 @@
         <v>9</v>
       </c>
       <c r="I54" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J54" t="s">
         <v>277</v>
@@ -6470,7 +6467,7 @@
         <v>9</v>
       </c>
       <c r="I55" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J55" t="s">
         <v>128</v>
@@ -6499,7 +6496,7 @@
         <v>9</v>
       </c>
       <c r="I56" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J56" t="s">
         <v>128</v>
@@ -6528,7 +6525,7 @@
         <v>9</v>
       </c>
       <c r="I57" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J57" t="s">
         <v>128</v>
@@ -6557,7 +6554,7 @@
         <v>9</v>
       </c>
       <c r="I58" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J58" t="s">
         <v>128</v>
@@ -6586,7 +6583,7 @@
         <v>9</v>
       </c>
       <c r="I59" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J59" t="s">
         <v>128</v>
@@ -6615,7 +6612,7 @@
         <v>9</v>
       </c>
       <c r="I60" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J60" t="s">
         <v>128</v>
@@ -6644,7 +6641,7 @@
         <v>9</v>
       </c>
       <c r="I61" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J61" t="s">
         <v>128</v>
@@ -6670,13 +6667,13 @@
         <v>2014</v>
       </c>
       <c r="G62" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="H62" t="s">
         <v>39</v>
       </c>
       <c r="I62" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J62" t="s">
         <v>78</v>
@@ -6699,13 +6696,13 @@
         <v>2006</v>
       </c>
       <c r="G63" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="H63" t="s">
         <v>9</v>
       </c>
       <c r="I63" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J63" t="s">
         <v>128</v>
@@ -6734,7 +6731,7 @@
         <v>9</v>
       </c>
       <c r="I64" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="J64" t="s">
         <v>128</v>
@@ -6757,13 +6754,13 @@
         <v>1977</v>
       </c>
       <c r="G65" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H65" t="s">
         <v>9</v>
       </c>
       <c r="I65" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="J65" t="s">
         <v>277</v>
@@ -6789,13 +6786,13 @@
         <v>2004</v>
       </c>
       <c r="G66" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="H66" t="s">
         <v>9</v>
       </c>
       <c r="I66" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J66" t="s">
         <v>277</v>
@@ -6824,7 +6821,7 @@
         <v>9</v>
       </c>
       <c r="I67" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J67" t="s">
         <v>277</v>
@@ -6850,13 +6847,13 @@
         <v>2004</v>
       </c>
       <c r="G68" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="H68" t="s">
         <v>9</v>
       </c>
       <c r="I68" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J68" t="s">
         <v>128</v>
@@ -7816,7 +7813,7 @@
         <v>9</v>
       </c>
       <c r="I101" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J101" t="s">
         <v>31</v>
@@ -7845,7 +7842,7 @@
         <v>9</v>
       </c>
       <c r="I102" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J102" t="s">
         <v>128</v>
@@ -7874,7 +7871,7 @@
         <v>9</v>
       </c>
       <c r="I103" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J103" t="s">
         <v>280</v>
@@ -7906,7 +7903,7 @@
         <v>9</v>
       </c>
       <c r="I104" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J104" t="s">
         <v>128</v>
@@ -7935,7 +7932,7 @@
         <v>9</v>
       </c>
       <c r="I105" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J105" t="s">
         <v>280</v>
@@ -7964,7 +7961,7 @@
         <v>9</v>
       </c>
       <c r="I106" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J106" t="s">
         <v>280</v>
@@ -7993,7 +7990,7 @@
         <v>9</v>
       </c>
       <c r="I107" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J107" t="s">
         <v>280</v>
@@ -8022,7 +8019,7 @@
         <v>9</v>
       </c>
       <c r="I108" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J108" t="s">
         <v>280</v>
@@ -8045,13 +8042,13 @@
         <v>2021</v>
       </c>
       <c r="G109" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="H109" t="s">
         <v>9</v>
       </c>
       <c r="I109" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="J109" t="s">
         <v>128</v>
@@ -8080,7 +8077,7 @@
         <v>9</v>
       </c>
       <c r="I110" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J110" t="s">
         <v>128</v>
@@ -8097,7 +8094,7 @@
         <v>134</v>
       </c>
       <c r="E111" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="F111">
         <v>1990</v>
@@ -8109,7 +8106,7 @@
         <v>39</v>
       </c>
       <c r="I111" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J111" t="s">
         <v>280</v>
@@ -8126,7 +8123,7 @@
         <v>134</v>
       </c>
       <c r="E112" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="F112">
         <v>1990</v>
@@ -8138,7 +8135,7 @@
         <v>9</v>
       </c>
       <c r="I112" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J112" t="s">
         <v>280</v>
@@ -8155,7 +8152,7 @@
         <v>134</v>
       </c>
       <c r="E113" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="F113">
         <v>1990</v>
@@ -8167,7 +8164,7 @@
         <v>9</v>
       </c>
       <c r="I113" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J113" t="s">
         <v>280</v>
@@ -8196,7 +8193,7 @@
         <v>9</v>
       </c>
       <c r="I114" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J114" t="s">
         <v>277</v>
@@ -8213,7 +8210,7 @@
         <v>134</v>
       </c>
       <c r="E115" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="F115">
         <v>1990</v>
@@ -8225,7 +8222,7 @@
         <v>9</v>
       </c>
       <c r="I115" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J115" t="s">
         <v>280</v>
@@ -8254,7 +8251,7 @@
         <v>9</v>
       </c>
       <c r="I116" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J116" t="s">
         <v>277</v>
@@ -8283,7 +8280,7 @@
         <v>9</v>
       </c>
       <c r="I117" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J117" t="s">
         <v>277</v>
@@ -8312,7 +8309,7 @@
         <v>9</v>
       </c>
       <c r="I118" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J118" t="s">
         <v>277</v>
@@ -8341,7 +8338,7 @@
         <v>9</v>
       </c>
       <c r="I119" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J119" t="s">
         <v>277</v>
@@ -8358,7 +8355,7 @@
         <v>134</v>
       </c>
       <c r="E120" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="F120">
         <v>1990</v>
@@ -8370,7 +8367,7 @@
         <v>9</v>
       </c>
       <c r="I120" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J120" t="s">
         <v>280</v>
@@ -8399,7 +8396,7 @@
         <v>9</v>
       </c>
       <c r="I121" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J121" t="s">
         <v>277</v>
@@ -8416,7 +8413,7 @@
         <v>134</v>
       </c>
       <c r="E122" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="F122">
         <v>1990</v>
@@ -8428,7 +8425,7 @@
         <v>9</v>
       </c>
       <c r="I122" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J122" t="s">
         <v>280</v>
@@ -8457,7 +8454,7 @@
         <v>9</v>
       </c>
       <c r="I123" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J123" t="s">
         <v>277</v>
@@ -8474,7 +8471,7 @@
         <v>134</v>
       </c>
       <c r="E124" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="F124">
         <v>1990</v>
@@ -8486,7 +8483,7 @@
         <v>9</v>
       </c>
       <c r="I124" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J124" t="s">
         <v>280</v>
@@ -8503,7 +8500,7 @@
         <v>134</v>
       </c>
       <c r="E125" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="F125">
         <v>1990</v>
@@ -8515,7 +8512,7 @@
         <v>9</v>
       </c>
       <c r="I125" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J125" t="s">
         <v>280</v>
@@ -8544,7 +8541,7 @@
         <v>9</v>
       </c>
       <c r="I126" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J126" t="s">
         <v>277</v>
@@ -8561,7 +8558,7 @@
         <v>134</v>
       </c>
       <c r="E127" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="F127">
         <v>1990</v>
@@ -8573,7 +8570,7 @@
         <v>9</v>
       </c>
       <c r="I127" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J127" t="s">
         <v>280</v>
@@ -8590,7 +8587,7 @@
         <v>148</v>
       </c>
       <c r="D128" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="E128" t="s">
         <v>149</v>
@@ -8599,13 +8596,13 @@
         <v>2016</v>
       </c>
       <c r="G128" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="H128" t="s">
         <v>9</v>
       </c>
       <c r="I128" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="J128" t="s">
         <v>31</v>
@@ -8663,7 +8660,7 @@
         <v>9</v>
       </c>
       <c r="I130" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J130" t="s">
         <v>280</v>
@@ -8692,7 +8689,7 @@
         <v>9</v>
       </c>
       <c r="I131" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J131" t="s">
         <v>280</v>
@@ -8721,7 +8718,7 @@
         <v>9</v>
       </c>
       <c r="I132" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J132" t="s">
         <v>280</v>
@@ -8750,7 +8747,7 @@
         <v>9</v>
       </c>
       <c r="I133" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J133" t="s">
         <v>280</v>
@@ -8779,7 +8776,7 @@
         <v>9</v>
       </c>
       <c r="I134" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J134" t="s">
         <v>280</v>
@@ -8808,7 +8805,7 @@
         <v>9</v>
       </c>
       <c r="I135" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J135" t="s">
         <v>280</v>
@@ -8837,7 +8834,7 @@
         <v>9</v>
       </c>
       <c r="I136" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J136" t="s">
         <v>280</v>
@@ -8866,7 +8863,7 @@
         <v>9</v>
       </c>
       <c r="I137" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J137" t="s">
         <v>280</v>
@@ -8895,7 +8892,7 @@
         <v>9</v>
       </c>
       <c r="I138" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J138" t="s">
         <v>280</v>
@@ -8924,7 +8921,7 @@
         <v>9</v>
       </c>
       <c r="I139" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J139" t="s">
         <v>280</v>
@@ -8953,7 +8950,7 @@
         <v>9</v>
       </c>
       <c r="I140" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J140" t="s">
         <v>280</v>
@@ -8982,7 +8979,7 @@
         <v>9</v>
       </c>
       <c r="I141" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J141" t="s">
         <v>280</v>
@@ -9011,7 +9008,7 @@
         <v>9</v>
       </c>
       <c r="I142" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J142" t="s">
         <v>280</v>
@@ -9040,7 +9037,7 @@
         <v>9</v>
       </c>
       <c r="I143" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J143" t="s">
         <v>280</v>
@@ -9069,7 +9066,7 @@
         <v>9</v>
       </c>
       <c r="I144" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J144" t="s">
         <v>280</v>
@@ -9098,7 +9095,7 @@
         <v>9</v>
       </c>
       <c r="I145" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J145" t="s">
         <v>280</v>
@@ -9127,7 +9124,7 @@
         <v>9</v>
       </c>
       <c r="I146" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J146" t="s">
         <v>280</v>
@@ -9156,7 +9153,7 @@
         <v>9</v>
       </c>
       <c r="I147" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="J147" t="s">
         <v>280</v>
@@ -9185,7 +9182,7 @@
         <v>9</v>
       </c>
       <c r="I148" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="J148" t="s">
         <v>128</v>
@@ -9214,7 +9211,7 @@
         <v>9</v>
       </c>
       <c r="I149" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="J149" t="s">
         <v>128</v>
@@ -9243,7 +9240,7 @@
         <v>9</v>
       </c>
       <c r="I150" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="J150" t="s">
         <v>128</v>
@@ -9272,7 +9269,7 @@
         <v>9</v>
       </c>
       <c r="I151" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="J151" t="s">
         <v>128</v>
@@ -9301,7 +9298,7 @@
         <v>9</v>
       </c>
       <c r="I152" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="J152" t="s">
         <v>128</v>
@@ -9330,7 +9327,7 @@
         <v>9</v>
       </c>
       <c r="I153" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="J153" t="s">
         <v>128</v>
@@ -9359,7 +9356,7 @@
         <v>9</v>
       </c>
       <c r="I154" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="J154" t="s">
         <v>128</v>
@@ -9388,7 +9385,7 @@
         <v>9</v>
       </c>
       <c r="I155" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="J155" t="s">
         <v>128</v>
@@ -9420,7 +9417,7 @@
         <v>9</v>
       </c>
       <c r="I156" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="J156" t="s">
         <v>10</v>
@@ -9446,10 +9443,10 @@
         <v>449</v>
       </c>
       <c r="H157" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I157" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="J157" t="s">
         <v>10</v>
@@ -9475,16 +9472,16 @@
         <v>449</v>
       </c>
       <c r="H158" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I158" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="J158" t="s">
         <v>10</v>
       </c>
       <c r="M158" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="159" spans="1:13" x14ac:dyDescent="0.2">
@@ -9507,10 +9504,10 @@
         <v>449</v>
       </c>
       <c r="H159" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I159" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="J159" t="s">
         <v>10</v>
@@ -9539,10 +9536,10 @@
         <v>449</v>
       </c>
       <c r="H160" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I160" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="J160" t="s">
         <v>299</v>
@@ -9559,7 +9556,7 @@
         <v>173</v>
       </c>
       <c r="D161" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="E161" t="s">
         <v>172</v>
@@ -9571,10 +9568,10 @@
         <v>449</v>
       </c>
       <c r="H161" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="I161" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="J161" t="s">
         <v>10</v>
@@ -9600,10 +9597,10 @@
         <v>449</v>
       </c>
       <c r="H162" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I162" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="J162" t="s">
         <v>10</v>
@@ -9629,10 +9626,10 @@
         <v>449</v>
       </c>
       <c r="H163" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I163" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="J163" t="s">
         <v>10</v>
@@ -9658,10 +9655,10 @@
         <v>449</v>
       </c>
       <c r="H164" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I164" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="J164" t="s">
         <v>10</v>
@@ -9687,10 +9684,10 @@
         <v>449</v>
       </c>
       <c r="H165" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I165" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="J165" t="s">
         <v>10</v>
@@ -9716,10 +9713,10 @@
         <v>449</v>
       </c>
       <c r="H166" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I166" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="J166" t="s">
         <v>10</v>
@@ -9736,7 +9733,7 @@
         <v>173</v>
       </c>
       <c r="D167" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="E167" t="s">
         <v>172</v>
@@ -9751,7 +9748,7 @@
         <v>9</v>
       </c>
       <c r="I167" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="J167" t="s">
         <v>10</v>
@@ -9777,10 +9774,10 @@
         <v>449</v>
       </c>
       <c r="H168" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I168" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="J168" t="s">
         <v>578</v>
@@ -9797,7 +9794,7 @@
         <v>173</v>
       </c>
       <c r="D169" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="E169" t="s">
         <v>172</v>
@@ -9812,7 +9809,7 @@
         <v>9</v>
       </c>
       <c r="I169" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="J169" t="s">
         <v>10</v>
@@ -9829,7 +9826,7 @@
         <v>173</v>
       </c>
       <c r="D170" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="E170" t="s">
         <v>172</v>
@@ -9841,16 +9838,16 @@
         <v>449</v>
       </c>
       <c r="H170" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I170" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="J170" t="s">
         <v>10</v>
       </c>
       <c r="L170" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.2">
@@ -9873,10 +9870,10 @@
         <v>449</v>
       </c>
       <c r="H171" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I171" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="J171" t="s">
         <v>578</v>
@@ -9902,10 +9899,10 @@
         <v>449</v>
       </c>
       <c r="H172" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I172" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="J172" t="s">
         <v>578</v>
@@ -9931,10 +9928,10 @@
         <v>449</v>
       </c>
       <c r="H173" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I173" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="J173" t="s">
         <v>576</v>
@@ -9960,10 +9957,10 @@
         <v>449</v>
       </c>
       <c r="H174" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I174" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="J174" t="s">
         <v>10</v>
@@ -9989,10 +9986,10 @@
         <v>449</v>
       </c>
       <c r="H175" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I175" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="J175" t="s">
         <v>10</v>
@@ -10018,13 +10015,13 @@
         <v>2010</v>
       </c>
       <c r="G176" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="H176" t="s">
         <v>9</v>
       </c>
       <c r="I176" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J176" t="s">
         <v>10</v>
@@ -10050,13 +10047,13 @@
         <v>2009</v>
       </c>
       <c r="G177" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="H177" t="s">
         <v>9</v>
       </c>
       <c r="I177" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J177" t="s">
         <v>277</v>
@@ -10082,13 +10079,13 @@
         <v>2011</v>
       </c>
       <c r="G178" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="H178" t="s">
         <v>9</v>
       </c>
       <c r="I178" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="J178" t="s">
         <v>128</v>
@@ -10111,13 +10108,13 @@
         <v>2011</v>
       </c>
       <c r="G179" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="H179" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I179" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="J179" t="s">
         <v>128</v>
@@ -10143,13 +10140,13 @@
         <v>2011</v>
       </c>
       <c r="G180" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="H180" t="s">
         <v>9</v>
       </c>
       <c r="I180" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="J180" t="s">
         <v>128</v>
@@ -10175,13 +10172,13 @@
         <v>2011</v>
       </c>
       <c r="G181" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="H181" t="s">
         <v>9</v>
       </c>
       <c r="I181" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="J181" t="s">
         <v>128</v>
@@ -10204,13 +10201,13 @@
         <v>2011</v>
       </c>
       <c r="G182" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="H182" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I182" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="J182" t="s">
         <v>128</v>
@@ -10233,13 +10230,13 @@
         <v>2011</v>
       </c>
       <c r="G183" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="H183" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I183" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="J183" t="s">
         <v>128</v>
@@ -10265,13 +10262,13 @@
         <v>2011</v>
       </c>
       <c r="G184" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="H184" t="s">
         <v>9</v>
       </c>
       <c r="I184" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="J184" t="s">
         <v>128</v>
@@ -10294,13 +10291,13 @@
         <v>2011</v>
       </c>
       <c r="G185" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="H185" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I185" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="J185" t="s">
         <v>128</v>
@@ -10323,13 +10320,13 @@
         <v>2011</v>
       </c>
       <c r="G186" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="H186" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I186" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="J186" t="s">
         <v>128</v>
@@ -10352,13 +10349,13 @@
         <v>2011</v>
       </c>
       <c r="G187" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="H187" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I187" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="J187" t="s">
         <v>128</v>
@@ -10381,13 +10378,13 @@
         <v>2011</v>
       </c>
       <c r="G188" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="H188" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I188" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="J188" t="s">
         <v>128</v>
@@ -10416,7 +10413,7 @@
         <v>9</v>
       </c>
       <c r="I189" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J189" t="s">
         <v>280</v>
@@ -10445,7 +10442,7 @@
         <v>9</v>
       </c>
       <c r="I190" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J190" t="s">
         <v>128</v>
@@ -10474,7 +10471,7 @@
         <v>9</v>
       </c>
       <c r="I191" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J191" t="s">
         <v>128</v>
@@ -10503,7 +10500,7 @@
         <v>9</v>
       </c>
       <c r="I192" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J192" t="s">
         <v>128</v>
@@ -10532,7 +10529,7 @@
         <v>9</v>
       </c>
       <c r="I193" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J193" t="s">
         <v>128</v>
@@ -10561,7 +10558,7 @@
         <v>9</v>
       </c>
       <c r="I194" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J194" t="s">
         <v>128</v>
@@ -10590,7 +10587,7 @@
         <v>9</v>
       </c>
       <c r="I195" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J195" t="s">
         <v>128</v>
@@ -10619,7 +10616,7 @@
         <v>9</v>
       </c>
       <c r="I196" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="J196" t="s">
         <v>280</v>
@@ -10648,7 +10645,7 @@
         <v>9</v>
       </c>
       <c r="I197" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="J197" t="s">
         <v>280</v>
@@ -10677,7 +10674,7 @@
         <v>9</v>
       </c>
       <c r="I198" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="J198" t="s">
         <v>280</v>
@@ -10703,7 +10700,7 @@
         <v>2008</v>
       </c>
       <c r="G199" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="H199" t="s">
         <v>9</v>
@@ -10732,7 +10729,7 @@
         <v>2008</v>
       </c>
       <c r="G200" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="H200" t="s">
         <v>9</v>
@@ -10761,7 +10758,7 @@
         <v>2005</v>
       </c>
       <c r="G201" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="H201" t="s">
         <v>9</v>
@@ -10854,7 +10851,7 @@
         <v>9</v>
       </c>
       <c r="I204" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J204" t="s">
         <v>128</v>
@@ -10883,7 +10880,7 @@
         <v>9</v>
       </c>
       <c r="I205" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J205" t="s">
         <v>128</v>
@@ -10912,7 +10909,7 @@
         <v>9</v>
       </c>
       <c r="I206" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J206" t="s">
         <v>609</v>
@@ -10941,7 +10938,7 @@
         <v>9</v>
       </c>
       <c r="I207" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J207" t="s">
         <v>277</v>
@@ -10970,7 +10967,7 @@
         <v>9</v>
       </c>
       <c r="I208" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J208" t="s">
         <v>609</v>
@@ -10999,7 +10996,7 @@
         <v>9</v>
       </c>
       <c r="I209" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J209" t="s">
         <v>128</v>
@@ -11028,7 +11025,7 @@
         <v>9</v>
       </c>
       <c r="I210" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J210" t="s">
         <v>277</v>
@@ -11057,7 +11054,7 @@
         <v>9</v>
       </c>
       <c r="I211" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J211" t="s">
         <v>128</v>
@@ -11086,7 +11083,7 @@
         <v>9</v>
       </c>
       <c r="I212" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J212" t="s">
         <v>128</v>
@@ -11112,7 +11109,7 @@
         <v>1271</v>
       </c>
       <c r="H213" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I213" t="s">
         <v>578</v>
@@ -11121,7 +11118,7 @@
         <v>277</v>
       </c>
       <c r="P213" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="214" spans="1:16" x14ac:dyDescent="0.2">
@@ -11147,7 +11144,7 @@
         <v>9</v>
       </c>
       <c r="I214" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J214" t="s">
         <v>128</v>
@@ -11176,7 +11173,7 @@
         <v>9</v>
       </c>
       <c r="I215" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J215" t="s">
         <v>609</v>
@@ -11205,7 +11202,7 @@
         <v>9</v>
       </c>
       <c r="I216" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J216" t="s">
         <v>128</v>
@@ -11234,7 +11231,7 @@
         <v>9</v>
       </c>
       <c r="I217" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J217" t="s">
         <v>277</v>
@@ -11263,7 +11260,7 @@
         <v>9</v>
       </c>
       <c r="I218" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J218" t="s">
         <v>277</v>
@@ -11292,7 +11289,7 @@
         <v>9</v>
       </c>
       <c r="I219" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J219" t="s">
         <v>128</v>
@@ -11321,7 +11318,7 @@
         <v>9</v>
       </c>
       <c r="I220" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J220" t="s">
         <v>128</v>
@@ -11350,7 +11347,7 @@
         <v>9</v>
       </c>
       <c r="I221" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J221" t="s">
         <v>128</v>
@@ -11379,7 +11376,7 @@
         <v>9</v>
       </c>
       <c r="I222" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J222" t="s">
         <v>277</v>
@@ -11408,7 +11405,7 @@
         <v>9</v>
       </c>
       <c r="I223" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J223" t="s">
         <v>128</v>
@@ -11434,10 +11431,10 @@
         <v>1271</v>
       </c>
       <c r="H224" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I224" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J224" t="s">
         <v>277</v>
@@ -11466,7 +11463,7 @@
         <v>9</v>
       </c>
       <c r="I225" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J225" t="s">
         <v>277</v>
@@ -11495,7 +11492,7 @@
         <v>9</v>
       </c>
       <c r="I226" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J226" t="s">
         <v>128</v>
@@ -11524,7 +11521,7 @@
         <v>9</v>
       </c>
       <c r="I227" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J227" t="s">
         <v>277</v>
@@ -11553,7 +11550,7 @@
         <v>9</v>
       </c>
       <c r="I228" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J228" t="s">
         <v>609</v>
@@ -11582,7 +11579,7 @@
         <v>9</v>
       </c>
       <c r="I229" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J229" t="s">
         <v>128</v>
@@ -11611,7 +11608,7 @@
         <v>9</v>
       </c>
       <c r="I230" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J230" t="s">
         <v>128</v>
@@ -11640,7 +11637,7 @@
         <v>9</v>
       </c>
       <c r="I231" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J231" t="s">
         <v>128</v>
@@ -11669,7 +11666,7 @@
         <v>9</v>
       </c>
       <c r="I232" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J232" t="s">
         <v>609</v>
@@ -11698,7 +11695,7 @@
         <v>9</v>
       </c>
       <c r="I233" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J233" t="s">
         <v>609</v>
@@ -11727,7 +11724,7 @@
         <v>9</v>
       </c>
       <c r="I234" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J234" t="s">
         <v>277</v>
@@ -11756,7 +11753,7 @@
         <v>9</v>
       </c>
       <c r="I235" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J235" t="s">
         <v>128</v>
@@ -11785,7 +11782,7 @@
         <v>9</v>
       </c>
       <c r="I236" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J236" t="s">
         <v>277</v>
@@ -11814,7 +11811,7 @@
         <v>9</v>
       </c>
       <c r="I237" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J237" t="s">
         <v>280</v>
@@ -11843,7 +11840,7 @@
         <v>9</v>
       </c>
       <c r="I238" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J238" t="s">
         <v>277</v>
@@ -11872,7 +11869,7 @@
         <v>9</v>
       </c>
       <c r="I239" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J239" t="s">
         <v>277</v>
@@ -11901,7 +11898,7 @@
         <v>9</v>
       </c>
       <c r="I240" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J240" t="s">
         <v>277</v>
@@ -11930,13 +11927,13 @@
         <v>9</v>
       </c>
       <c r="I241" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J241" t="s">
         <v>277</v>
       </c>
       <c r="P241" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="242" spans="1:16" x14ac:dyDescent="0.2">
@@ -11962,7 +11959,7 @@
         <v>9</v>
       </c>
       <c r="I242" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J242" t="s">
         <v>128</v>
@@ -11991,7 +11988,7 @@
         <v>9</v>
       </c>
       <c r="I243" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J243" t="s">
         <v>128</v>
@@ -12017,7 +12014,7 @@
         <v>1271</v>
       </c>
       <c r="H244" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I244" t="s">
         <v>10</v>
@@ -12049,7 +12046,7 @@
         <v>9</v>
       </c>
       <c r="I245" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J245" t="s">
         <v>277</v>
@@ -12078,7 +12075,7 @@
         <v>9</v>
       </c>
       <c r="I246" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J246" t="s">
         <v>128</v>
@@ -12107,7 +12104,7 @@
         <v>9</v>
       </c>
       <c r="I247" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J247" t="s">
         <v>128</v>
@@ -12136,7 +12133,7 @@
         <v>9</v>
       </c>
       <c r="I248" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J248" t="s">
         <v>128</v>
@@ -12165,7 +12162,7 @@
         <v>9</v>
       </c>
       <c r="I249" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J249" t="s">
         <v>128</v>
@@ -12194,7 +12191,7 @@
         <v>9</v>
       </c>
       <c r="I250" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J250" t="s">
         <v>277</v>
@@ -12223,7 +12220,7 @@
         <v>9</v>
       </c>
       <c r="I251" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J251" t="s">
         <v>128</v>
@@ -12252,7 +12249,7 @@
         <v>9</v>
       </c>
       <c r="I252" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J252" t="s">
         <v>277</v>
@@ -12284,7 +12281,7 @@
         <v>9</v>
       </c>
       <c r="I253" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J253" t="s">
         <v>128</v>
@@ -12310,7 +12307,7 @@
         <v>1271</v>
       </c>
       <c r="H254" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I254" t="s">
         <v>10</v>
@@ -12342,7 +12339,7 @@
         <v>9</v>
       </c>
       <c r="I255" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J255" t="s">
         <v>128</v>
@@ -12368,10 +12365,10 @@
         <v>1271</v>
       </c>
       <c r="H256" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I256" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J256" t="s">
         <v>128</v>
@@ -12400,7 +12397,7 @@
         <v>9</v>
       </c>
       <c r="I257" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J257" t="s">
         <v>277</v>
@@ -12426,10 +12423,10 @@
         <v>1271</v>
       </c>
       <c r="H258" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I258" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J258" t="s">
         <v>277</v>
@@ -12455,10 +12452,10 @@
         <v>1271</v>
       </c>
       <c r="H259" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I259" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J259" t="s">
         <v>277</v>
@@ -12487,7 +12484,7 @@
         <v>9</v>
       </c>
       <c r="I260" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J260" t="s">
         <v>277</v>
@@ -12516,7 +12513,7 @@
         <v>9</v>
       </c>
       <c r="I261" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J261" t="s">
         <v>277</v>
@@ -12545,7 +12542,7 @@
         <v>9</v>
       </c>
       <c r="I262" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J262" t="s">
         <v>613</v>
@@ -12571,10 +12568,10 @@
         <v>1274</v>
       </c>
       <c r="H263" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I263" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J263" t="s">
         <v>613</v>
@@ -12600,10 +12597,10 @@
         <v>1274</v>
       </c>
       <c r="H264" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I264" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J264" t="s">
         <v>613</v>
@@ -12632,7 +12629,7 @@
         <v>9</v>
       </c>
       <c r="I265" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J265" t="s">
         <v>10</v>
@@ -12661,7 +12658,7 @@
         <v>9</v>
       </c>
       <c r="I266" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J266" t="s">
         <v>10</v>
@@ -12684,13 +12681,13 @@
         <v>1985</v>
       </c>
       <c r="G267" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
       </c>
       <c r="I267" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J267" t="s">
         <v>280</v>
@@ -12713,13 +12710,13 @@
         <v>1985</v>
       </c>
       <c r="G268" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
       </c>
       <c r="I268" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J268" t="s">
         <v>280</v>
@@ -12748,7 +12745,7 @@
         <v>9</v>
       </c>
       <c r="I269" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J269" t="s">
         <v>280</v>
@@ -12806,7 +12803,7 @@
         <v>9</v>
       </c>
       <c r="I271" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="J271" t="s">
         <v>609</v>
@@ -12832,7 +12829,7 @@
         <v>1271</v>
       </c>
       <c r="H272" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I272" t="s">
         <v>609</v>
@@ -13090,13 +13087,13 @@
         <v>2016</v>
       </c>
       <c r="G281" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="H281" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I281" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="J281" t="s">
         <v>280</v>
@@ -13119,13 +13116,13 @@
         <v>2016</v>
       </c>
       <c r="G282" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="H282" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I282" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="J282" t="s">
         <v>280</v>
@@ -13148,13 +13145,13 @@
         <v>2016</v>
       </c>
       <c r="G283" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="H283" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I283" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="J283" t="s">
         <v>280</v>
@@ -13177,13 +13174,13 @@
         <v>2016</v>
       </c>
       <c r="G284" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="H284" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I284" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="J284" t="s">
         <v>280</v>
@@ -13206,13 +13203,13 @@
         <v>2016</v>
       </c>
       <c r="G285" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="H285" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I285" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="J285" t="s">
         <v>280</v>
@@ -13220,16 +13217,16 @@
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="B286" s="2">
         <v>0.36736111111111114</v>
       </c>
       <c r="C286" t="s">
+        <v>1336</v>
+      </c>
+      <c r="E286" t="s">
         <v>1337</v>
-      </c>
-      <c r="E286" t="s">
-        <v>1338</v>
       </c>
       <c r="F286">
         <v>2012</v>
@@ -13241,7 +13238,7 @@
         <v>9</v>
       </c>
       <c r="I286" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J286" t="s">
         <v>128</v>
@@ -13249,16 +13246,16 @@
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="B287" s="2">
         <v>0.12222222222222222</v>
       </c>
       <c r="C287" t="s">
+        <v>1336</v>
+      </c>
+      <c r="E287" t="s">
         <v>1337</v>
-      </c>
-      <c r="E287" t="s">
-        <v>1338</v>
       </c>
       <c r="F287">
         <v>2012</v>
@@ -13270,7 +13267,7 @@
         <v>9</v>
       </c>
       <c r="I287" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J287" t="s">
         <v>128</v>
@@ -13299,7 +13296,7 @@
         <v>9</v>
       </c>
       <c r="I288" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J288" t="s">
         <v>280</v>
@@ -13328,7 +13325,7 @@
         <v>9</v>
       </c>
       <c r="I289" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J289" t="s">
         <v>280</v>
@@ -13357,7 +13354,7 @@
         <v>9</v>
       </c>
       <c r="I290" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J290" t="s">
         <v>280</v>
@@ -13386,7 +13383,7 @@
         <v>9</v>
       </c>
       <c r="I291" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J291" t="s">
         <v>280</v>
@@ -13409,13 +13406,13 @@
         <v>2011</v>
       </c>
       <c r="G292" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
       </c>
       <c r="I292" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="J292" t="s">
         <v>277</v>
@@ -13438,19 +13435,19 @@
         <v>2000</v>
       </c>
       <c r="G293" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="H293" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I293" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J293" t="s">
         <v>128</v>
       </c>
       <c r="M293" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="294" spans="1:13" x14ac:dyDescent="0.2">
@@ -13473,16 +13470,16 @@
         <v>38</v>
       </c>
       <c r="H294" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I294" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="J294" t="s">
         <v>128</v>
       </c>
       <c r="M294" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="295" spans="1:13" x14ac:dyDescent="0.2">
@@ -13514,7 +13511,7 @@
         <v>496</v>
       </c>
       <c r="M295" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="296" spans="1:13" x14ac:dyDescent="0.2">
@@ -13540,13 +13537,13 @@
         <v>9</v>
       </c>
       <c r="I296" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J296" t="s">
         <v>496</v>
       </c>
       <c r="M296" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="297" spans="1:13" x14ac:dyDescent="0.2">
@@ -13572,7 +13569,7 @@
         <v>9</v>
       </c>
       <c r="I297" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J297" t="s">
         <v>277</v>
@@ -13601,7 +13598,7 @@
         <v>9</v>
       </c>
       <c r="I298" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J298" t="s">
         <v>277</v>
@@ -13659,13 +13656,13 @@
         <v>9</v>
       </c>
       <c r="I300" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="J300" t="s">
         <v>630</v>
       </c>
       <c r="M300" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="301" spans="1:13" x14ac:dyDescent="0.2">
@@ -13691,13 +13688,13 @@
         <v>9</v>
       </c>
       <c r="I301" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="J301" t="s">
         <v>527</v>
       </c>
       <c r="M301" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="302" spans="1:13" x14ac:dyDescent="0.2">
@@ -13723,13 +13720,13 @@
         <v>9</v>
       </c>
       <c r="I302" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="J302" t="s">
         <v>128</v>
       </c>
       <c r="M302" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="303" spans="1:13" x14ac:dyDescent="0.2">
@@ -13755,7 +13752,7 @@
         <v>9</v>
       </c>
       <c r="I303" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="J303" t="s">
         <v>277</v>
@@ -13784,7 +13781,7 @@
         <v>9</v>
       </c>
       <c r="I304" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="J304" t="s">
         <v>277</v>
@@ -13807,13 +13804,13 @@
         <v>1977</v>
       </c>
       <c r="G305" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
       </c>
       <c r="I305" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="J305" t="s">
         <v>280</v>
@@ -13842,7 +13839,7 @@
         <v>9</v>
       </c>
       <c r="I306" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J306" t="s">
         <v>277</v>
@@ -13877,7 +13874,7 @@
         <v>277</v>
       </c>
       <c r="M307" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="308" spans="1:1018 1026:2042 2050:3066 3074:4090 4098:5114 5122:6138 6146:7162 7170:8186 8194:9210 9218:10234 10242:11258 11266:12282 12290:13306 13314:14330 14338:15354 15362:16378" x14ac:dyDescent="0.2">
@@ -18424,13 +18421,13 @@
         <v>1997</v>
       </c>
       <c r="G323" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
       </c>
       <c r="I323" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J323" t="s">
         <v>128</v>
@@ -18453,13 +18450,13 @@
         <v>1997</v>
       </c>
       <c r="G324" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
       </c>
       <c r="I324" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J324" t="s">
         <v>128</v>
@@ -18482,13 +18479,13 @@
         <v>1997</v>
       </c>
       <c r="G325" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
       </c>
       <c r="I325" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J325" t="s">
         <v>128</v>
@@ -18511,13 +18508,13 @@
         <v>1997</v>
       </c>
       <c r="G326" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
       </c>
       <c r="I326" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J326" t="s">
         <v>128</v>
@@ -18540,13 +18537,13 @@
         <v>1997</v>
       </c>
       <c r="G327" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
       </c>
       <c r="I327" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J327" t="s">
         <v>128</v>
@@ -18572,19 +18569,19 @@
         <v>2018</v>
       </c>
       <c r="G328" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
       </c>
       <c r="I328" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J328" t="s">
         <v>128</v>
       </c>
       <c r="M328" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="329" spans="1:16" x14ac:dyDescent="0.2">
@@ -18607,13 +18604,13 @@
         <v>2021</v>
       </c>
       <c r="G329" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
       </c>
       <c r="I329" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J329" t="s">
         <v>280</v>
@@ -18639,13 +18636,13 @@
         <v>1995</v>
       </c>
       <c r="G330" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
       </c>
       <c r="I330" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J330" t="s">
         <v>280</v>
@@ -18668,13 +18665,13 @@
         <v>1998</v>
       </c>
       <c r="G331" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
       </c>
       <c r="I331" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J331" t="s">
         <v>280</v>
@@ -18697,13 +18694,13 @@
         <v>1995</v>
       </c>
       <c r="G332" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
       </c>
       <c r="I332" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J332" t="s">
         <v>280</v>
@@ -18726,13 +18723,13 @@
         <v>1995</v>
       </c>
       <c r="G333" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
       </c>
       <c r="I333" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J333" t="s">
         <v>280</v>
@@ -18755,13 +18752,13 @@
         <v>2023</v>
       </c>
       <c r="G334" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
       </c>
       <c r="I334" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J334" t="s">
         <v>280</v>
@@ -18790,13 +18787,13 @@
         <v>2021</v>
       </c>
       <c r="G335" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
       </c>
       <c r="I335" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J335" t="s">
         <v>280</v>
@@ -18819,13 +18816,13 @@
         <v>1998</v>
       </c>
       <c r="G336" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
       </c>
       <c r="I336" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J336" t="s">
         <v>280</v>
@@ -18848,13 +18845,13 @@
         <v>1998</v>
       </c>
       <c r="G337" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
       </c>
       <c r="I337" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J337" t="s">
         <v>280</v>
@@ -18877,13 +18874,13 @@
         <v>1999</v>
       </c>
       <c r="G338" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
       </c>
       <c r="I338" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="J338" t="s">
         <v>280</v>
@@ -18906,13 +18903,13 @@
         <v>1995</v>
       </c>
       <c r="G339" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
       </c>
       <c r="I339" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J339" t="s">
         <v>280</v>
@@ -18935,13 +18932,13 @@
         <v>1995</v>
       </c>
       <c r="G340" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
       </c>
       <c r="I340" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J340" t="s">
         <v>280</v>
@@ -18964,13 +18961,13 @@
         <v>1995</v>
       </c>
       <c r="G341" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
       </c>
       <c r="I341" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J341" t="s">
         <v>280</v>
@@ -18993,13 +18990,13 @@
         <v>1998</v>
       </c>
       <c r="G342" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
       </c>
       <c r="I342" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J342" t="s">
         <v>280</v>
@@ -19022,13 +19019,13 @@
         <v>1998</v>
       </c>
       <c r="G343" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
       </c>
       <c r="I343" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J343" t="s">
         <v>280</v>
@@ -19054,13 +19051,13 @@
         <v>2021</v>
       </c>
       <c r="G344" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
       </c>
       <c r="I344" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J344" t="s">
         <v>280</v>
@@ -19083,13 +19080,13 @@
         <v>2005</v>
       </c>
       <c r="G345" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
       </c>
       <c r="I345" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J345" t="s">
         <v>128</v>
@@ -19121,7 +19118,7 @@
         <v>9</v>
       </c>
       <c r="I346" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="J346" t="s">
         <v>128</v>
@@ -19179,7 +19176,7 @@
         <v>9</v>
       </c>
       <c r="I348" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J348" t="s">
         <v>128</v>
@@ -19187,16 +19184,16 @@
     </row>
     <row r="349" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="B349" s="2">
         <v>0.1423611111111111</v>
       </c>
       <c r="C349" t="s">
+        <v>1432</v>
+      </c>
+      <c r="E349" t="s">
         <v>1433</v>
-      </c>
-      <c r="E349" t="s">
-        <v>1434</v>
       </c>
       <c r="F349">
         <v>1994</v>
@@ -19208,7 +19205,7 @@
         <v>9</v>
       </c>
       <c r="I349" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J349" t="s">
         <v>128</v>
@@ -19216,16 +19213,16 @@
     </row>
     <row r="350" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B350" s="2">
         <v>0.125</v>
       </c>
       <c r="C350" t="s">
+        <v>1432</v>
+      </c>
+      <c r="E350" t="s">
         <v>1433</v>
-      </c>
-      <c r="E350" t="s">
-        <v>1434</v>
       </c>
       <c r="F350">
         <v>1994</v>
@@ -19237,7 +19234,7 @@
         <v>9</v>
       </c>
       <c r="I350" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J350" t="s">
         <v>128</v>
@@ -19266,7 +19263,7 @@
         <v>9</v>
       </c>
       <c r="I351" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J351" t="s">
         <v>277</v>
@@ -19295,7 +19292,7 @@
         <v>9</v>
       </c>
       <c r="I352" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J352" t="s">
         <v>128</v>
@@ -19324,7 +19321,7 @@
         <v>9</v>
       </c>
       <c r="I353" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J353" t="s">
         <v>280</v>
@@ -19353,7 +19350,7 @@
         <v>9</v>
       </c>
       <c r="I354" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J354" t="s">
         <v>128</v>
@@ -19376,13 +19373,13 @@
         <v>2014</v>
       </c>
       <c r="G355" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
       </c>
       <c r="I355" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J355" t="s">
         <v>128</v>
@@ -19405,13 +19402,13 @@
         <v>1991</v>
       </c>
       <c r="G356" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="H356" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I356" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="J356" t="s">
         <v>522</v>
@@ -19434,13 +19431,13 @@
         <v>1991</v>
       </c>
       <c r="G357" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="H357" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I357" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="J357" t="s">
         <v>522</v>
@@ -19463,13 +19460,13 @@
         <v>1991</v>
       </c>
       <c r="G358" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="H358" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I358" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="J358" t="s">
         <v>522</v>
@@ -19492,13 +19489,13 @@
         <v>1991</v>
       </c>
       <c r="G359" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="H359" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I359" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="J359" t="s">
         <v>522</v>
@@ -19521,13 +19518,13 @@
         <v>1991</v>
       </c>
       <c r="G360" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="H360" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I360" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="J360" t="s">
         <v>522</v>
@@ -19550,13 +19547,13 @@
         <v>1991</v>
       </c>
       <c r="G361" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="H361" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I361" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="J361" t="s">
         <v>522</v>
@@ -19570,7 +19567,7 @@
         <v>0.12291666666666666</v>
       </c>
       <c r="C362" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="E362" t="s">
         <v>642</v>
@@ -19579,7 +19576,7 @@
         <v>2010</v>
       </c>
       <c r="G362" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -19620,7 +19617,7 @@
         <v>128</v>
       </c>
       <c r="M363" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="364" spans="1:16" x14ac:dyDescent="0.2">
@@ -19646,7 +19643,7 @@
         <v>9</v>
       </c>
       <c r="I364" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J364" t="s">
         <v>128</v>
@@ -19669,13 +19666,13 @@
         <v>1997</v>
       </c>
       <c r="G365" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
       </c>
       <c r="I365" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J365" t="s">
         <v>54</v>
@@ -19698,19 +19695,19 @@
         <v>2000</v>
       </c>
       <c r="G366" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
       </c>
       <c r="I366" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J366" t="s">
         <v>128</v>
       </c>
       <c r="P366" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="367" spans="1:16" x14ac:dyDescent="0.2">
@@ -19730,13 +19727,13 @@
         <v>1997</v>
       </c>
       <c r="G367" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
       </c>
       <c r="I367" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J367" t="s">
         <v>54</v>
@@ -19759,19 +19756,19 @@
         <v>2002</v>
       </c>
       <c r="G368" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
       </c>
       <c r="I368" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J368" t="s">
         <v>128</v>
       </c>
       <c r="P368" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="369" spans="1:16" x14ac:dyDescent="0.2">
@@ -19855,7 +19852,7 @@
         <v>9</v>
       </c>
       <c r="I371" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J371" t="s">
         <v>128</v>
@@ -19878,13 +19875,13 @@
         <v>2004</v>
       </c>
       <c r="G372" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
       </c>
       <c r="I372" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J372" t="s">
         <v>277</v>
@@ -19907,13 +19904,13 @@
         <v>2004</v>
       </c>
       <c r="G373" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
       </c>
       <c r="I373" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J373" t="s">
         <v>277</v>
@@ -19936,13 +19933,13 @@
         <v>2004</v>
       </c>
       <c r="G374" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
       </c>
       <c r="I374" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J374" t="s">
         <v>277</v>
@@ -19968,13 +19965,13 @@
         <v>2021</v>
       </c>
       <c r="G375" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
       </c>
       <c r="I375" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J375" t="s">
         <v>128</v>
@@ -20093,10 +20090,10 @@
         <v>88</v>
       </c>
       <c r="H379" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I379" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="J379" t="s">
         <v>578</v>
@@ -20122,10 +20119,10 @@
         <v>88</v>
       </c>
       <c r="H380" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I380" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J380" t="s">
         <v>14</v>
@@ -20151,10 +20148,10 @@
         <v>88</v>
       </c>
       <c r="H381" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I381" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J381" t="s">
         <v>14</v>
@@ -20180,10 +20177,10 @@
         <v>88</v>
       </c>
       <c r="H382" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I382" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J382" t="s">
         <v>14</v>
@@ -20209,10 +20206,10 @@
         <v>88</v>
       </c>
       <c r="H383" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="I383" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="J383" t="s">
         <v>576</v>
@@ -20238,10 +20235,10 @@
         <v>88</v>
       </c>
       <c r="H384" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I384" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J384" t="s">
         <v>14</v>
@@ -20267,10 +20264,10 @@
         <v>88</v>
       </c>
       <c r="H385" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I385" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J385" t="s">
         <v>14</v>
@@ -20296,10 +20293,10 @@
         <v>88</v>
       </c>
       <c r="H386" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I386" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J386" t="s">
         <v>14</v>
@@ -20325,10 +20322,10 @@
         <v>88</v>
       </c>
       <c r="H387" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I387" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J387" t="s">
         <v>14</v>
@@ -20354,10 +20351,10 @@
         <v>88</v>
       </c>
       <c r="H388" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I388" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J388" t="s">
         <v>14</v>
@@ -20383,10 +20380,10 @@
         <v>88</v>
       </c>
       <c r="H389" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I389" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J389" t="s">
         <v>14</v>
@@ -20412,10 +20409,10 @@
         <v>88</v>
       </c>
       <c r="H390" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I390" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J390" t="s">
         <v>14</v>
@@ -20441,10 +20438,10 @@
         <v>88</v>
       </c>
       <c r="H391" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I391" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J391" t="s">
         <v>14</v>
@@ -20470,10 +20467,10 @@
         <v>88</v>
       </c>
       <c r="H392" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I392" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J392" t="s">
         <v>14</v>
@@ -20499,10 +20496,10 @@
         <v>88</v>
       </c>
       <c r="H393" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I393" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J393" t="s">
         <v>14</v>
@@ -20528,10 +20525,10 @@
         <v>88</v>
       </c>
       <c r="H394" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I394" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J394" t="s">
         <v>14</v>
@@ -20644,7 +20641,7 @@
         <v>2018</v>
       </c>
       <c r="G398" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -20656,7 +20653,7 @@
         <v>128</v>
       </c>
       <c r="L398" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="399" spans="1:12" x14ac:dyDescent="0.2">
@@ -20676,7 +20673,7 @@
         <v>2018</v>
       </c>
       <c r="G399" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -20705,7 +20702,7 @@
         <v>2019</v>
       </c>
       <c r="G400" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -20734,7 +20731,7 @@
         <v>2019</v>
       </c>
       <c r="G401" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -20763,7 +20760,7 @@
         <v>2019</v>
       </c>
       <c r="G402" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -20792,7 +20789,7 @@
         <v>2019</v>
       </c>
       <c r="G403" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -20821,7 +20818,7 @@
         <v>2019</v>
       </c>
       <c r="G404" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -20850,7 +20847,7 @@
         <v>2019</v>
       </c>
       <c r="G405" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -20879,7 +20876,7 @@
         <v>2019</v>
       </c>
       <c r="G406" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -20908,7 +20905,7 @@
         <v>2019</v>
       </c>
       <c r="G407" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -20937,7 +20934,7 @@
         <v>2011</v>
       </c>
       <c r="G408" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -20949,7 +20946,7 @@
         <v>522</v>
       </c>
       <c r="P408" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="409" spans="1:16" x14ac:dyDescent="0.2">
@@ -20972,13 +20969,13 @@
         <v>2006</v>
       </c>
       <c r="G409" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
       </c>
       <c r="I409" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="J409" t="s">
         <v>10</v>
@@ -21004,13 +21001,13 @@
         <v>2006</v>
       </c>
       <c r="G410" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
       </c>
       <c r="I410" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="J410" t="s">
         <v>10</v>
@@ -21018,16 +21015,16 @@
     </row>
     <row r="411" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="B411" s="2">
         <v>0.16319444444444445</v>
       </c>
       <c r="C411" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="E411" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="F411">
         <v>1992</v>
@@ -21039,7 +21036,7 @@
         <v>9</v>
       </c>
       <c r="I411" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J411" t="s">
         <v>630</v>
@@ -21068,13 +21065,13 @@
         <v>39</v>
       </c>
       <c r="I412" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="J412" t="s">
         <v>128</v>
       </c>
       <c r="M412" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="413" spans="1:16" x14ac:dyDescent="0.2">
@@ -21100,7 +21097,7 @@
         <v>39</v>
       </c>
       <c r="I413" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="J413" t="s">
         <v>128</v>
@@ -21129,7 +21126,7 @@
         <v>39</v>
       </c>
       <c r="I414" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J414" t="s">
         <v>128</v>
@@ -21158,7 +21155,7 @@
         <v>9</v>
       </c>
       <c r="I415" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J415" t="s">
         <v>10</v>
@@ -21181,7 +21178,7 @@
         <v>2013</v>
       </c>
       <c r="G416" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -21219,13 +21216,13 @@
         <v>9</v>
       </c>
       <c r="I417" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="J417" t="s">
         <v>10</v>
       </c>
       <c r="M417" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="418" spans="1:13" x14ac:dyDescent="0.2">
@@ -21251,7 +21248,7 @@
         <v>9</v>
       </c>
       <c r="I418" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J418" t="s">
         <v>280</v>
@@ -21274,13 +21271,13 @@
         <v>1972</v>
       </c>
       <c r="G419" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
       </c>
       <c r="I419" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="J419" t="s">
         <v>277</v>
@@ -21309,7 +21306,7 @@
         <v>9</v>
       </c>
       <c r="I420" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J420" t="s">
         <v>128</v>
@@ -21338,7 +21335,7 @@
         <v>9</v>
       </c>
       <c r="I421" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J421" t="s">
         <v>128</v>
@@ -21367,7 +21364,7 @@
         <v>9</v>
       </c>
       <c r="I422" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J422" t="s">
         <v>280</v>
@@ -21396,7 +21393,7 @@
         <v>9</v>
       </c>
       <c r="I423" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J423" t="s">
         <v>280</v>
@@ -21419,19 +21416,19 @@
         <v>1964</v>
       </c>
       <c r="G424" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="H424" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I424" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="J424" t="s">
         <v>724</v>
       </c>
       <c r="M424" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="425" spans="1:13" x14ac:dyDescent="0.2">
@@ -21457,7 +21454,7 @@
         <v>9</v>
       </c>
       <c r="I425" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J425" t="s">
         <v>10</v>
@@ -21486,7 +21483,7 @@
         <v>9</v>
       </c>
       <c r="I426" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J426" t="s">
         <v>128</v>
@@ -21494,16 +21491,16 @@
     </row>
     <row r="427" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="B427" s="2">
         <v>0.18541666666666667</v>
       </c>
       <c r="C427" t="s">
+        <v>1423</v>
+      </c>
+      <c r="E427" t="s">
         <v>1424</v>
-      </c>
-      <c r="E427" t="s">
-        <v>1425</v>
       </c>
       <c r="F427">
         <v>2009</v>
@@ -21523,16 +21520,16 @@
     </row>
     <row r="428" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="B428" s="2">
         <v>0.17847222222222223</v>
       </c>
       <c r="C428" t="s">
+        <v>1423</v>
+      </c>
+      <c r="E428" t="s">
         <v>1424</v>
-      </c>
-      <c r="E428" t="s">
-        <v>1425</v>
       </c>
       <c r="F428">
         <v>2009</v>
@@ -21552,16 +21549,16 @@
     </row>
     <row r="429" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="B429" s="2">
         <v>0.1701388888888889</v>
       </c>
       <c r="C429" t="s">
+        <v>1423</v>
+      </c>
+      <c r="E429" t="s">
         <v>1424</v>
-      </c>
-      <c r="E429" t="s">
-        <v>1425</v>
       </c>
       <c r="F429">
         <v>2009</v>
@@ -21581,16 +21578,16 @@
     </row>
     <row r="430" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="B430" s="2">
         <v>0.16319444444444445</v>
       </c>
       <c r="C430" t="s">
+        <v>1423</v>
+      </c>
+      <c r="E430" t="s">
         <v>1424</v>
-      </c>
-      <c r="E430" t="s">
-        <v>1425</v>
       </c>
       <c r="F430">
         <v>2009</v>
@@ -21631,7 +21628,7 @@
         <v>9</v>
       </c>
       <c r="I431" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J431" t="s">
         <v>10</v>
@@ -21654,10 +21651,10 @@
         <v>1967</v>
       </c>
       <c r="G432" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="H432" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I432" t="s">
         <v>259</v>
@@ -21666,7 +21663,7 @@
         <v>259</v>
       </c>
       <c r="M432" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="433" spans="1:10" x14ac:dyDescent="0.2">
@@ -21686,13 +21683,13 @@
         <v>2021</v>
       </c>
       <c r="G433" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
       </c>
       <c r="I433" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J433" t="s">
         <v>128</v>
@@ -21715,13 +21712,13 @@
         <v>2023</v>
       </c>
       <c r="G434" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
       </c>
       <c r="I434" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="J434" t="s">
         <v>277</v>
@@ -21744,13 +21741,13 @@
         <v>1995</v>
       </c>
       <c r="G435" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
       </c>
       <c r="I435" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J435" t="s">
         <v>10</v>
@@ -21776,13 +21773,13 @@
         <v>2013</v>
       </c>
       <c r="G436" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
       </c>
       <c r="I436" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J436" t="s">
         <v>10</v>
@@ -21808,13 +21805,13 @@
         <v>2013</v>
       </c>
       <c r="G437" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
       </c>
       <c r="I437" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J437" t="s">
         <v>10</v>
@@ -21837,13 +21834,13 @@
         <v>1996</v>
       </c>
       <c r="G438" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
       </c>
       <c r="I438" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J438" t="s">
         <v>10</v>
@@ -21866,13 +21863,13 @@
         <v>2014</v>
       </c>
       <c r="G439" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
       </c>
       <c r="I439" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J439" t="s">
         <v>277</v>
@@ -21901,7 +21898,7 @@
         <v>9</v>
       </c>
       <c r="I440" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="J440" t="s">
         <v>277</v>
@@ -21930,7 +21927,7 @@
         <v>9</v>
       </c>
       <c r="I441" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J441" t="s">
         <v>277</v>
@@ -21959,7 +21956,7 @@
         <v>9</v>
       </c>
       <c r="I442" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J442" t="s">
         <v>277</v>
@@ -21988,7 +21985,7 @@
         <v>9</v>
       </c>
       <c r="I443" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J443" t="s">
         <v>277</v>
@@ -22017,7 +22014,7 @@
         <v>9</v>
       </c>
       <c r="I444" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J444" t="s">
         <v>277</v>
@@ -22046,7 +22043,7 @@
         <v>9</v>
       </c>
       <c r="I445" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J445" t="s">
         <v>277</v>
@@ -22075,7 +22072,7 @@
         <v>9</v>
       </c>
       <c r="I446" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J446" t="s">
         <v>277</v>
@@ -22104,7 +22101,7 @@
         <v>9</v>
       </c>
       <c r="I447" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J447" t="s">
         <v>10</v>
@@ -22127,10 +22124,10 @@
         <v>1969</v>
       </c>
       <c r="G448" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H448" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I448" t="s">
         <v>259</v>
@@ -22191,7 +22188,7 @@
         <v>9</v>
       </c>
       <c r="I450" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="J450" t="s">
         <v>630</v>
@@ -22220,7 +22217,7 @@
         <v>9</v>
       </c>
       <c r="I451" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J451" t="s">
         <v>128</v>
@@ -22246,13 +22243,13 @@
         <v>2011</v>
       </c>
       <c r="G452" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
       </c>
       <c r="I452" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J452" t="s">
         <v>128</v>
@@ -22275,13 +22272,13 @@
         <v>2003</v>
       </c>
       <c r="G453" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
       </c>
       <c r="I453" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="J453" t="s">
         <v>277</v>
@@ -22304,13 +22301,13 @@
         <v>2003</v>
       </c>
       <c r="G454" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
       </c>
       <c r="I454" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="J454" t="s">
         <v>277</v>
@@ -22333,13 +22330,13 @@
         <v>2003</v>
       </c>
       <c r="G455" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
       </c>
       <c r="I455" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="J455" t="s">
         <v>277</v>
@@ -22362,13 +22359,13 @@
         <v>2005</v>
       </c>
       <c r="G456" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
       </c>
       <c r="I456" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="J456" t="s">
         <v>277</v>
@@ -22391,13 +22388,13 @@
         <v>2003</v>
       </c>
       <c r="G457" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
       </c>
       <c r="I457" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="J457" t="s">
         <v>277</v>
@@ -22420,13 +22417,13 @@
         <v>2003</v>
       </c>
       <c r="G458" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
       </c>
       <c r="I458" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="J458" t="s">
         <v>277</v>
@@ -22449,13 +22446,13 @@
         <v>2005</v>
       </c>
       <c r="G459" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
       </c>
       <c r="I459" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="J459" t="s">
         <v>277</v>
@@ -22478,13 +22475,13 @@
         <v>2003</v>
       </c>
       <c r="G460" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
       </c>
       <c r="I460" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="J460" t="s">
         <v>277</v>
@@ -22507,13 +22504,13 @@
         <v>2003</v>
       </c>
       <c r="G461" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
       </c>
       <c r="I461" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="J461" t="s">
         <v>277</v>
@@ -22536,13 +22533,13 @@
         <v>2003</v>
       </c>
       <c r="G462" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
       </c>
       <c r="I462" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="J462" t="s">
         <v>277</v>
@@ -22565,13 +22562,13 @@
         <v>2003</v>
       </c>
       <c r="G463" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
       </c>
       <c r="I463" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="J463" t="s">
         <v>277</v>
@@ -22594,13 +22591,13 @@
         <v>2003</v>
       </c>
       <c r="G464" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
       </c>
       <c r="I464" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="J464" t="s">
         <v>277</v>
@@ -22623,13 +22620,13 @@
         <v>2003</v>
       </c>
       <c r="G465" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
       </c>
       <c r="I465" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="J465" t="s">
         <v>277</v>
@@ -22652,13 +22649,13 @@
         <v>2003</v>
       </c>
       <c r="G466" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
       </c>
       <c r="I466" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="J466" t="s">
         <v>277</v>
@@ -22681,13 +22678,13 @@
         <v>2003</v>
       </c>
       <c r="G467" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
       </c>
       <c r="I467" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="J467" t="s">
         <v>277</v>
@@ -22710,13 +22707,13 @@
         <v>2005</v>
       </c>
       <c r="G468" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
       </c>
       <c r="I468" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="J468" t="s">
         <v>277</v>
@@ -22739,13 +22736,13 @@
         <v>2005</v>
       </c>
       <c r="G469" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
       </c>
       <c r="I469" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="J469" t="s">
         <v>277</v>
@@ -23006,7 +23003,7 @@
         <v>9</v>
       </c>
       <c r="I478" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="J478" t="s">
         <v>280</v>
@@ -23061,7 +23058,7 @@
         <v>1271</v>
       </c>
       <c r="H480" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I480" t="s">
         <v>609</v>
@@ -23151,7 +23148,7 @@
         <v>9</v>
       </c>
       <c r="I483" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="J483" t="s">
         <v>277</v>
@@ -23174,7 +23171,7 @@
         <v>1965</v>
       </c>
       <c r="G484" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -23203,7 +23200,7 @@
         <v>1951</v>
       </c>
       <c r="G485" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="H485" t="s">
         <v>39</v>
@@ -23232,7 +23229,7 @@
         <v>1951</v>
       </c>
       <c r="G486" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -23261,7 +23258,7 @@
         <v>1965</v>
       </c>
       <c r="G487" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -23290,7 +23287,7 @@
         <v>1965</v>
       </c>
       <c r="G488" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -23319,13 +23316,13 @@
         <v>1994</v>
       </c>
       <c r="G489" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
       </c>
       <c r="I489" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="J489" t="s">
         <v>128</v>
@@ -23348,13 +23345,13 @@
         <v>1994</v>
       </c>
       <c r="G490" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
       </c>
       <c r="I490" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="J490" t="s">
         <v>128</v>
@@ -23377,13 +23374,13 @@
         <v>1997</v>
       </c>
       <c r="G491" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
       </c>
       <c r="I491" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J491" t="s">
         <v>522</v>
@@ -23406,13 +23403,13 @@
         <v>2005</v>
       </c>
       <c r="G492" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
       </c>
       <c r="I492" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="J492" t="s">
         <v>128</v>
@@ -23435,13 +23432,13 @@
         <v>2005</v>
       </c>
       <c r="G493" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
       </c>
       <c r="I493" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J493" t="s">
         <v>128</v>
@@ -23464,13 +23461,13 @@
         <v>1989</v>
       </c>
       <c r="G494" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
       </c>
       <c r="I494" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="J494" t="s">
         <v>128</v>
@@ -23493,13 +23490,13 @@
         <v>2005</v>
       </c>
       <c r="G495" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
       </c>
       <c r="I495" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="J495" t="s">
         <v>128</v>
@@ -23522,13 +23519,13 @@
         <v>1994</v>
       </c>
       <c r="G496" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
       </c>
       <c r="I496" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="J496" t="s">
         <v>128</v>
@@ -23551,13 +23548,13 @@
         <v>1989</v>
       </c>
       <c r="G497" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
       </c>
       <c r="I497" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="J497" t="s">
         <v>128</v>
@@ -23580,13 +23577,13 @@
         <v>2005</v>
       </c>
       <c r="G498" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
       </c>
       <c r="I498" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="J498" t="s">
         <v>128</v>
@@ -23609,13 +23606,13 @@
         <v>1992</v>
       </c>
       <c r="G499" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
       </c>
       <c r="I499" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="J499" t="s">
         <v>128</v>
@@ -23638,13 +23635,13 @@
         <v>1989</v>
       </c>
       <c r="G500" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
       </c>
       <c r="I500" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="J500" t="s">
         <v>128</v>
@@ -23667,13 +23664,13 @@
         <v>2005</v>
       </c>
       <c r="G501" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
       </c>
       <c r="I501" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="J501" t="s">
         <v>128</v>
@@ -23696,13 +23693,13 @@
         <v>2017</v>
       </c>
       <c r="G502" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
       </c>
       <c r="I502" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="J502" t="s">
         <v>128</v>
@@ -23725,13 +23722,13 @@
         <v>1994</v>
       </c>
       <c r="G503" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
       </c>
       <c r="I503" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="J503" t="s">
         <v>128</v>
@@ -23754,19 +23751,19 @@
         <v>1999</v>
       </c>
       <c r="G504" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H504" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I504" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="J504" t="s">
         <v>128</v>
       </c>
       <c r="M504" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="505" spans="1:13" x14ac:dyDescent="0.2">
@@ -23844,13 +23841,13 @@
         <v>1991</v>
       </c>
       <c r="G507" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
       </c>
       <c r="I507" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J507" t="s">
         <v>128</v>
@@ -23873,13 +23870,13 @@
         <v>1993</v>
       </c>
       <c r="G508" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
       </c>
       <c r="I508" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J508" t="s">
         <v>128</v>
@@ -23902,13 +23899,13 @@
         <v>2013</v>
       </c>
       <c r="G509" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="H509" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I509" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="J509" t="s">
         <v>10</v>
@@ -23937,7 +23934,7 @@
         <v>9</v>
       </c>
       <c r="I510" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J510" t="s">
         <v>277</v>
@@ -23966,7 +23963,7 @@
         <v>9</v>
       </c>
       <c r="I511" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J511" t="s">
         <v>277</v>
@@ -23995,7 +23992,7 @@
         <v>9</v>
       </c>
       <c r="I512" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J512" t="s">
         <v>277</v>
@@ -24024,13 +24021,13 @@
         <v>9</v>
       </c>
       <c r="I513" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J513" t="s">
         <v>277</v>
       </c>
       <c r="P513" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="514" spans="1:16" x14ac:dyDescent="0.2">
@@ -24056,7 +24053,7 @@
         <v>9</v>
       </c>
       <c r="I514" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J514" t="s">
         <v>277</v>
@@ -24085,7 +24082,7 @@
         <v>9</v>
       </c>
       <c r="I515" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J515" t="s">
         <v>128</v>
@@ -24114,7 +24111,7 @@
         <v>9</v>
       </c>
       <c r="I516" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J516" t="s">
         <v>128</v>
@@ -24143,7 +24140,7 @@
         <v>9</v>
       </c>
       <c r="I517" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J517" t="s">
         <v>128</v>
@@ -24172,7 +24169,7 @@
         <v>9</v>
       </c>
       <c r="I518" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J518" t="s">
         <v>128</v>
@@ -24201,7 +24198,7 @@
         <v>9</v>
       </c>
       <c r="I519" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J519" t="s">
         <v>128</v>
@@ -24230,7 +24227,7 @@
         <v>9</v>
       </c>
       <c r="I520" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J520" t="s">
         <v>128</v>
@@ -24259,7 +24256,7 @@
         <v>9</v>
       </c>
       <c r="I521" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J521" t="s">
         <v>128</v>
@@ -24288,7 +24285,7 @@
         <v>9</v>
       </c>
       <c r="I522" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J522" t="s">
         <v>128</v>
@@ -24317,7 +24314,7 @@
         <v>9</v>
       </c>
       <c r="I523" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J523" t="s">
         <v>128</v>
@@ -24346,7 +24343,7 @@
         <v>9</v>
       </c>
       <c r="I524" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J524" t="s">
         <v>128</v>
@@ -24372,10 +24369,10 @@
         <v>2012</v>
       </c>
       <c r="G525" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="H525" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="I525" t="s">
         <v>10</v>
@@ -24407,7 +24404,7 @@
         <v>9</v>
       </c>
       <c r="I526" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J526" t="s">
         <v>280</v>
@@ -24436,7 +24433,7 @@
         <v>9</v>
       </c>
       <c r="I527" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J527" t="s">
         <v>128</v>
@@ -24465,7 +24462,7 @@
         <v>9</v>
       </c>
       <c r="I528" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J528" t="s">
         <v>128</v>
@@ -24494,7 +24491,7 @@
         <v>9</v>
       </c>
       <c r="I529" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J529" t="s">
         <v>280</v>
@@ -24523,7 +24520,7 @@
         <v>9</v>
       </c>
       <c r="I530" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="J530" t="s">
         <v>280</v>
@@ -24552,7 +24549,7 @@
         <v>9</v>
       </c>
       <c r="I531" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="J531" t="s">
         <v>280</v>
@@ -24581,7 +24578,7 @@
         <v>9</v>
       </c>
       <c r="I532" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="J532" t="s">
         <v>280</v>
@@ -24610,7 +24607,7 @@
         <v>9</v>
       </c>
       <c r="I533" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="J533" t="s">
         <v>280</v>
@@ -24639,7 +24636,7 @@
         <v>9</v>
       </c>
       <c r="I534" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="J534" t="s">
         <v>280</v>
@@ -24668,7 +24665,7 @@
         <v>9</v>
       </c>
       <c r="I535" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="J535" t="s">
         <v>280</v>
@@ -24697,7 +24694,7 @@
         <v>9</v>
       </c>
       <c r="I536" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="J536" t="s">
         <v>280</v>
@@ -24726,7 +24723,7 @@
         <v>9</v>
       </c>
       <c r="I537" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J537" t="s">
         <v>10</v>
@@ -24755,7 +24752,7 @@
         <v>9</v>
       </c>
       <c r="I538" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J538" t="s">
         <v>10</v>
@@ -24784,7 +24781,7 @@
         <v>9</v>
       </c>
       <c r="I539" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J539" t="s">
         <v>10</v>
@@ -24813,7 +24810,7 @@
         <v>9</v>
       </c>
       <c r="I540" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J540" t="s">
         <v>10</v>
@@ -24842,7 +24839,7 @@
         <v>9</v>
       </c>
       <c r="I541" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J541" t="s">
         <v>10</v>
@@ -24871,7 +24868,7 @@
         <v>9</v>
       </c>
       <c r="I542" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J542" t="s">
         <v>10</v>
@@ -24900,7 +24897,7 @@
         <v>9</v>
       </c>
       <c r="I543" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J543" t="s">
         <v>10</v>
@@ -24929,7 +24926,7 @@
         <v>9</v>
       </c>
       <c r="I544" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J544" t="s">
         <v>10</v>
@@ -24958,7 +24955,7 @@
         <v>9</v>
       </c>
       <c r="I545" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J545" t="s">
         <v>10</v>
@@ -24987,7 +24984,7 @@
         <v>9</v>
       </c>
       <c r="I546" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J546" t="s">
         <v>10</v>
@@ -25016,7 +25013,7 @@
         <v>9</v>
       </c>
       <c r="I547" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J547" t="s">
         <v>10</v>
@@ -25045,7 +25042,7 @@
         <v>9</v>
       </c>
       <c r="I548" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J548" t="s">
         <v>10</v>
@@ -25074,7 +25071,7 @@
         <v>9</v>
       </c>
       <c r="I549" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J549" t="s">
         <v>10</v>
@@ -25103,7 +25100,7 @@
         <v>9</v>
       </c>
       <c r="I550" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J550" t="s">
         <v>10</v>
@@ -25242,13 +25239,13 @@
         <v>1991</v>
       </c>
       <c r="G555" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
       </c>
       <c r="I555" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J555" t="s">
         <v>128</v>
@@ -25271,13 +25268,13 @@
         <v>1983</v>
       </c>
       <c r="G556" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
       </c>
       <c r="I556" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J556" t="s">
         <v>277</v>
@@ -25300,13 +25297,13 @@
         <v>1988</v>
       </c>
       <c r="G557" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
       </c>
       <c r="I557" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J557" t="s">
         <v>280</v>
@@ -25329,13 +25326,13 @@
         <v>1981</v>
       </c>
       <c r="G558" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
       </c>
       <c r="I558" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J558" t="s">
         <v>280</v>
@@ -25358,13 +25355,13 @@
         <v>1983</v>
       </c>
       <c r="G559" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
       </c>
       <c r="I559" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J559" t="s">
         <v>277</v>
@@ -25387,13 +25384,13 @@
         <v>1985</v>
       </c>
       <c r="G560" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
       </c>
       <c r="I560" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J560" t="s">
         <v>280</v>
@@ -25416,13 +25413,13 @@
         <v>1983</v>
       </c>
       <c r="G561" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
       </c>
       <c r="I561" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J561" t="s">
         <v>277</v>
@@ -25445,13 +25442,13 @@
         <v>1983</v>
       </c>
       <c r="G562" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
       </c>
       <c r="I562" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J562" t="s">
         <v>280</v>
@@ -25474,13 +25471,13 @@
         <v>1987</v>
       </c>
       <c r="G563" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
       </c>
       <c r="I563" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J563" t="s">
         <v>280</v>
@@ -25503,13 +25500,13 @@
         <v>1984</v>
       </c>
       <c r="G564" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
       </c>
       <c r="I564" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J564" t="s">
         <v>280</v>
@@ -25532,13 +25529,13 @@
         <v>1986</v>
       </c>
       <c r="G565" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
       </c>
       <c r="I565" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J565" t="s">
         <v>280</v>
@@ -25561,19 +25558,19 @@
         <v>2008</v>
       </c>
       <c r="G566" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
       </c>
       <c r="I566" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J566" t="s">
         <v>277</v>
       </c>
       <c r="M566" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="567" spans="1:13" x14ac:dyDescent="0.2">
@@ -25593,19 +25590,19 @@
         <v>2008</v>
       </c>
       <c r="G567" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
       </c>
       <c r="I567" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J567" t="s">
         <v>277</v>
       </c>
       <c r="M567" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="568" spans="1:13" x14ac:dyDescent="0.2">
@@ -25625,19 +25622,19 @@
         <v>2008</v>
       </c>
       <c r="G568" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
       </c>
       <c r="I568" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J568" t="s">
         <v>277</v>
       </c>
       <c r="M568" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="569" spans="1:13" x14ac:dyDescent="0.2">
@@ -25663,7 +25660,7 @@
         <v>9</v>
       </c>
       <c r="I569" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J569" t="s">
         <v>277</v>
@@ -25692,7 +25689,7 @@
         <v>9</v>
       </c>
       <c r="I570" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J570" t="s">
         <v>128</v>
@@ -25721,7 +25718,7 @@
         <v>9</v>
       </c>
       <c r="I571" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J571" t="s">
         <v>128</v>
@@ -25750,7 +25747,7 @@
         <v>9</v>
       </c>
       <c r="I572" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J572" t="s">
         <v>128</v>
@@ -25773,13 +25770,13 @@
         <v>1973</v>
       </c>
       <c r="G573" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
       </c>
       <c r="I573" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="J573" t="s">
         <v>277</v>
@@ -25802,13 +25799,13 @@
         <v>1982</v>
       </c>
       <c r="G574" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
       </c>
       <c r="I574" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="J574" t="s">
         <v>277</v>
@@ -25825,7 +25822,7 @@
         <v>954</v>
       </c>
       <c r="D575" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="E575" t="s">
         <v>955</v>
@@ -25843,7 +25840,7 @@
         <v>10</v>
       </c>
       <c r="J575" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="576" spans="1:13" x14ac:dyDescent="0.2">
@@ -25889,7 +25886,7 @@
         <v>954</v>
       </c>
       <c r="D577" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="E577" t="s">
         <v>964</v>
@@ -25904,7 +25901,7 @@
         <v>9</v>
       </c>
       <c r="I577" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="J577" t="s">
         <v>31</v>
@@ -25936,7 +25933,7 @@
         <v>9</v>
       </c>
       <c r="I578" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="J578" t="s">
         <v>10</v>
@@ -25953,7 +25950,7 @@
         <v>954</v>
       </c>
       <c r="D579" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="E579" t="s">
         <v>961</v>
@@ -26000,7 +25997,7 @@
         <v>9</v>
       </c>
       <c r="I580" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="J580" t="s">
         <v>10</v>
@@ -26026,7 +26023,7 @@
         <v>8</v>
       </c>
       <c r="H581" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I581" t="s">
         <v>10</v>
@@ -26046,7 +26043,7 @@
         <v>954</v>
       </c>
       <c r="D582" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="E582" t="s">
         <v>964</v>
@@ -26067,7 +26064,7 @@
         <v>31</v>
       </c>
       <c r="L582" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="583" spans="1:12" x14ac:dyDescent="0.2">
@@ -26081,7 +26078,7 @@
         <v>954</v>
       </c>
       <c r="D583" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="E583" t="s">
         <v>957</v>
@@ -26122,13 +26119,13 @@
         <v>2013</v>
       </c>
       <c r="G584" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
       </c>
       <c r="I584" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J584" t="s">
         <v>10</v>
@@ -26157,7 +26154,7 @@
         <v>9</v>
       </c>
       <c r="I585" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="J585" t="s">
         <v>277</v>
@@ -26186,7 +26183,7 @@
         <v>9</v>
       </c>
       <c r="I586" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="J586" t="s">
         <v>277</v>
@@ -26215,7 +26212,7 @@
         <v>9</v>
       </c>
       <c r="I587" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="J587" t="s">
         <v>10</v>
@@ -26244,7 +26241,7 @@
         <v>9</v>
       </c>
       <c r="I588" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="J588" t="s">
         <v>277</v>
@@ -26273,7 +26270,7 @@
         <v>9</v>
       </c>
       <c r="I589" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="J589" t="s">
         <v>277</v>
@@ -26302,7 +26299,7 @@
         <v>9</v>
       </c>
       <c r="I590" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="J590" t="s">
         <v>277</v>
@@ -26331,7 +26328,7 @@
         <v>9</v>
       </c>
       <c r="I591" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="J591" t="s">
         <v>277</v>
@@ -26360,7 +26357,7 @@
         <v>9</v>
       </c>
       <c r="I592" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="J592" t="s">
         <v>277</v>
@@ -26389,7 +26386,7 @@
         <v>9</v>
       </c>
       <c r="I593" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="J593" t="s">
         <v>277</v>
@@ -26418,7 +26415,7 @@
         <v>9</v>
       </c>
       <c r="I594" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J594" t="s">
         <v>277</v>
@@ -26447,7 +26444,7 @@
         <v>9</v>
       </c>
       <c r="I595" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J595" t="s">
         <v>277</v>
@@ -26476,7 +26473,7 @@
         <v>9</v>
       </c>
       <c r="I596" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J596" t="s">
         <v>277</v>
@@ -26505,7 +26502,7 @@
         <v>9</v>
       </c>
       <c r="I597" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J597" t="s">
         <v>277</v>
@@ -26534,7 +26531,7 @@
         <v>9</v>
       </c>
       <c r="I598" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J598" t="s">
         <v>277</v>
@@ -26563,7 +26560,7 @@
         <v>9</v>
       </c>
       <c r="I599" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J599" t="s">
         <v>277</v>
@@ -26592,7 +26589,7 @@
         <v>9</v>
       </c>
       <c r="I600" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J600" t="s">
         <v>277</v>
@@ -26656,7 +26653,7 @@
         <v>522</v>
       </c>
       <c r="P602" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="603" spans="1:16" x14ac:dyDescent="0.2">
@@ -26711,7 +26708,7 @@
         <v>9</v>
       </c>
       <c r="I604" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J604" t="s">
         <v>280</v>
@@ -26740,7 +26737,7 @@
         <v>9</v>
       </c>
       <c r="I605" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="J605" t="s">
         <v>277</v>
@@ -26748,7 +26745,7 @@
     </row>
     <row r="606" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A606" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="B606" s="2">
         <v>0.1875</v>
@@ -26757,7 +26754,7 @@
         <v>999</v>
       </c>
       <c r="E606" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="F606">
         <v>1982</v>
@@ -26769,7 +26766,7 @@
         <v>9</v>
       </c>
       <c r="I606" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="J606" t="s">
         <v>280</v>
@@ -26798,7 +26795,7 @@
         <v>9</v>
       </c>
       <c r="I607" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="J607" t="s">
         <v>280</v>
@@ -26806,7 +26803,7 @@
     </row>
     <row r="608" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A608" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="B608" s="2">
         <v>0.1701388888888889</v>
@@ -26827,7 +26824,7 @@
         <v>9</v>
       </c>
       <c r="I608" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="J608" t="s">
         <v>280</v>
@@ -26856,7 +26853,7 @@
         <v>9</v>
       </c>
       <c r="I609" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="J609" t="s">
         <v>280</v>
@@ -26885,18 +26882,18 @@
         <v>9</v>
       </c>
       <c r="I610" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="J610" t="s">
         <v>277</v>
       </c>
       <c r="P610" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="611" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A611" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="B611" s="2">
         <v>0.15902777777777777</v>
@@ -26917,7 +26914,7 @@
         <v>9</v>
       </c>
       <c r="I611" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="J611" t="s">
         <v>277</v>
@@ -26946,7 +26943,7 @@
         <v>9</v>
       </c>
       <c r="I612" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="J612" t="s">
         <v>280</v>
@@ -26975,7 +26972,7 @@
         <v>9</v>
       </c>
       <c r="I613" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="J613" t="s">
         <v>280</v>
@@ -27004,7 +27001,7 @@
         <v>9</v>
       </c>
       <c r="I614" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J614" t="s">
         <v>280</v>
@@ -27033,7 +27030,7 @@
         <v>9</v>
       </c>
       <c r="I615" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J615" t="s">
         <v>280</v>
@@ -27062,7 +27059,7 @@
         <v>9</v>
       </c>
       <c r="I616" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J616" t="s">
         <v>280</v>
@@ -27091,7 +27088,7 @@
         <v>9</v>
       </c>
       <c r="I617" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J617" t="s">
         <v>277</v>
@@ -27120,7 +27117,7 @@
         <v>9</v>
       </c>
       <c r="I618" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J618" t="s">
         <v>277</v>
@@ -27149,7 +27146,7 @@
         <v>9</v>
       </c>
       <c r="I619" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="J619" t="s">
         <v>522</v>
@@ -27181,7 +27178,7 @@
         <v>9</v>
       </c>
       <c r="I620" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="J620" t="s">
         <v>522</v>
@@ -27213,7 +27210,7 @@
         <v>9</v>
       </c>
       <c r="I621" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J621" t="s">
         <v>128</v>
@@ -27245,7 +27242,7 @@
         <v>9</v>
       </c>
       <c r="I622" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J622" t="s">
         <v>128</v>
@@ -27277,7 +27274,7 @@
         <v>9</v>
       </c>
       <c r="I623" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J623" t="s">
         <v>128</v>
@@ -27309,7 +27306,7 @@
         <v>9</v>
       </c>
       <c r="I624" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J624" t="s">
         <v>128</v>
@@ -27341,7 +27338,7 @@
         <v>9</v>
       </c>
       <c r="I625" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J625" t="s">
         <v>128</v>
@@ -27373,7 +27370,7 @@
         <v>9</v>
       </c>
       <c r="I626" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J626" t="s">
         <v>128</v>
@@ -27405,7 +27402,7 @@
         <v>9</v>
       </c>
       <c r="I627" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J627" t="s">
         <v>128</v>
@@ -27437,7 +27434,7 @@
         <v>9</v>
       </c>
       <c r="I628" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J628" t="s">
         <v>128</v>
@@ -27463,7 +27460,7 @@
         <v>1271</v>
       </c>
       <c r="H629" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I629" t="s">
         <v>14</v>
@@ -27492,7 +27489,7 @@
         <v>1271</v>
       </c>
       <c r="H630" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I630" t="s">
         <v>14</v>
@@ -27524,7 +27521,7 @@
         <v>9</v>
       </c>
       <c r="I631" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J631" t="s">
         <v>630</v>
@@ -27553,7 +27550,7 @@
         <v>9</v>
       </c>
       <c r="I632" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J632" t="s">
         <v>280</v>
@@ -27576,13 +27573,13 @@
         <v>1986</v>
       </c>
       <c r="G633" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
       </c>
       <c r="I633" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="J633" t="s">
         <v>280</v>
@@ -27611,7 +27608,7 @@
         <v>9</v>
       </c>
       <c r="I634" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J634" t="s">
         <v>277</v>
@@ -27640,7 +27637,7 @@
         <v>9</v>
       </c>
       <c r="I635" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J635" t="s">
         <v>128</v>
@@ -27698,7 +27695,7 @@
         <v>9</v>
       </c>
       <c r="I637" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J637" t="s">
         <v>280</v>
@@ -27727,7 +27724,7 @@
         <v>9</v>
       </c>
       <c r="I638" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J638" t="s">
         <v>280</v>
@@ -27756,7 +27753,7 @@
         <v>9</v>
       </c>
       <c r="I639" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J639" t="s">
         <v>280</v>
@@ -27785,7 +27782,7 @@
         <v>9</v>
       </c>
       <c r="I640" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J640" t="s">
         <v>280</v>
@@ -27814,7 +27811,7 @@
         <v>9</v>
       </c>
       <c r="I641" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="J641" t="s">
         <v>280</v>
@@ -27875,7 +27872,7 @@
         <v>9</v>
       </c>
       <c r="I643" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="J643" t="s">
         <v>280</v>
@@ -27904,13 +27901,13 @@
         <v>9</v>
       </c>
       <c r="I644" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="J644" t="s">
         <v>277</v>
       </c>
       <c r="P644" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="645" spans="1:16" x14ac:dyDescent="0.2">
@@ -27933,13 +27930,13 @@
         <v>2014</v>
       </c>
       <c r="G645" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
       </c>
       <c r="I645" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J645" t="s">
         <v>522</v>
@@ -27968,7 +27965,7 @@
         <v>9</v>
       </c>
       <c r="I646" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J646" t="s">
         <v>527</v>
@@ -27997,13 +27994,13 @@
         <v>9</v>
       </c>
       <c r="I647" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J647" t="s">
         <v>10</v>
       </c>
       <c r="P647" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="648" spans="1:16" x14ac:dyDescent="0.2">
@@ -28023,7 +28020,7 @@
         <v>2005</v>
       </c>
       <c r="G648" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -28052,7 +28049,7 @@
         <v>2009</v>
       </c>
       <c r="G649" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -28081,13 +28078,13 @@
         <v>1998</v>
       </c>
       <c r="G650" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
       </c>
       <c r="I650" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J650" t="s">
         <v>277</v>
@@ -28110,13 +28107,13 @@
         <v>1998</v>
       </c>
       <c r="G651" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
       </c>
       <c r="I651" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J651" t="s">
         <v>277</v>
@@ -28145,7 +28142,7 @@
         <v>9</v>
       </c>
       <c r="I652" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="J652" t="s">
         <v>128</v>
@@ -28174,13 +28171,13 @@
         <v>9</v>
       </c>
       <c r="I653" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="J653" t="s">
         <v>128</v>
       </c>
       <c r="M653" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="654" spans="1:16" x14ac:dyDescent="0.2">
@@ -28206,7 +28203,7 @@
         <v>9</v>
       </c>
       <c r="I654" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="J654" t="s">
         <v>128</v>
@@ -28235,7 +28232,7 @@
         <v>9</v>
       </c>
       <c r="I655" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="J655" t="s">
         <v>128</v>
@@ -28264,7 +28261,7 @@
         <v>9</v>
       </c>
       <c r="I656" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="J656" t="s">
         <v>128</v>
@@ -28293,7 +28290,7 @@
         <v>9</v>
       </c>
       <c r="I657" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="J657" t="s">
         <v>128</v>
@@ -28322,7 +28319,7 @@
         <v>9</v>
       </c>
       <c r="I658" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="J658" t="s">
         <v>128</v>
@@ -28351,7 +28348,7 @@
         <v>9</v>
       </c>
       <c r="I659" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="J659" t="s">
         <v>128</v>
@@ -28380,7 +28377,7 @@
         <v>9</v>
       </c>
       <c r="I660" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="J660" t="s">
         <v>128</v>
@@ -28409,7 +28406,7 @@
         <v>9</v>
       </c>
       <c r="I661" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="J661" t="s">
         <v>128</v>
@@ -28438,7 +28435,7 @@
         <v>9</v>
       </c>
       <c r="I662" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="J662" t="s">
         <v>128</v>
@@ -28467,7 +28464,7 @@
         <v>9</v>
       </c>
       <c r="I663" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="J663" t="s">
         <v>280</v>
@@ -28493,7 +28490,7 @@
         <v>8</v>
       </c>
       <c r="H664" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I664" t="s">
         <v>10</v>
@@ -28525,7 +28522,7 @@
         <v>9</v>
       </c>
       <c r="I665" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="J665" t="s">
         <v>277</v>
@@ -28551,13 +28548,13 @@
         <v>2023</v>
       </c>
       <c r="G666" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
       </c>
       <c r="I666" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J666" t="s">
         <v>128</v>
@@ -28580,7 +28577,7 @@
         <v>2011</v>
       </c>
       <c r="G667" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -28609,7 +28606,7 @@
         <v>2011</v>
       </c>
       <c r="G668" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -28638,7 +28635,7 @@
         <v>2016</v>
       </c>
       <c r="G669" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -28667,7 +28664,7 @@
         <v>2011</v>
       </c>
       <c r="G670" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -28696,7 +28693,7 @@
         <v>2016</v>
       </c>
       <c r="G671" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -28725,7 +28722,7 @@
         <v>2008</v>
       </c>
       <c r="G672" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -28754,7 +28751,7 @@
         <v>2011</v>
       </c>
       <c r="G673" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -28783,7 +28780,7 @@
         <v>2016</v>
       </c>
       <c r="G674" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -28812,7 +28809,7 @@
         <v>2008</v>
       </c>
       <c r="G675" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -28847,7 +28844,7 @@
         <v>9</v>
       </c>
       <c r="I676" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="J676" t="s">
         <v>128</v>
@@ -28870,7 +28867,7 @@
         <v>2010</v>
       </c>
       <c r="G677" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -28905,7 +28902,7 @@
         <v>9</v>
       </c>
       <c r="I678" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J678" t="s">
         <v>280</v>
@@ -28963,7 +28960,7 @@
         <v>9</v>
       </c>
       <c r="I680" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J680" t="s">
         <v>128</v>
@@ -29021,7 +29018,7 @@
         <v>9</v>
       </c>
       <c r="I682" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J682" t="s">
         <v>280</v>
@@ -29044,7 +29041,7 @@
         <v>2012</v>
       </c>
       <c r="G683" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -29073,7 +29070,7 @@
         <v>2001</v>
       </c>
       <c r="G684" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -29108,7 +29105,7 @@
         <v>9</v>
       </c>
       <c r="I685" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="J685" t="s">
         <v>280</v>
@@ -29137,7 +29134,7 @@
         <v>9</v>
       </c>
       <c r="I686" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="J686" t="s">
         <v>280</v>
@@ -29166,7 +29163,7 @@
         <v>9</v>
       </c>
       <c r="I687" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="J687" t="s">
         <v>280</v>
@@ -29195,7 +29192,7 @@
         <v>9</v>
       </c>
       <c r="I688" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="J688" t="s">
         <v>280</v>
@@ -29224,7 +29221,7 @@
         <v>9</v>
       </c>
       <c r="I689" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="J689" t="s">
         <v>280</v>
@@ -29253,7 +29250,7 @@
         <v>9</v>
       </c>
       <c r="I690" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="J690" t="s">
         <v>280</v>
@@ -29282,7 +29279,7 @@
         <v>9</v>
       </c>
       <c r="I691" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="J691" t="s">
         <v>280</v>
@@ -29311,7 +29308,7 @@
         <v>9</v>
       </c>
       <c r="I692" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="J692" t="s">
         <v>277</v>
@@ -29340,7 +29337,7 @@
         <v>9</v>
       </c>
       <c r="I693" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="J693" t="s">
         <v>277</v>
@@ -29369,7 +29366,7 @@
         <v>9</v>
       </c>
       <c r="I694" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="J694" t="s">
         <v>277</v>
@@ -29398,7 +29395,7 @@
         <v>9</v>
       </c>
       <c r="I695" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="J695" t="s">
         <v>277</v>
@@ -29427,7 +29424,7 @@
         <v>9</v>
       </c>
       <c r="I696" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="J696" t="s">
         <v>280</v>
@@ -29456,7 +29453,7 @@
         <v>9</v>
       </c>
       <c r="I697" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="J697" t="s">
         <v>280</v>
@@ -29485,7 +29482,7 @@
         <v>9</v>
       </c>
       <c r="I698" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="J698" t="s">
         <v>277</v>
@@ -29514,7 +29511,7 @@
         <v>9</v>
       </c>
       <c r="I699" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="J699" t="s">
         <v>280</v>
@@ -29543,7 +29540,7 @@
         <v>9</v>
       </c>
       <c r="I700" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="J700" t="s">
         <v>280</v>
@@ -29572,7 +29569,7 @@
         <v>9</v>
       </c>
       <c r="I701" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="J701" t="s">
         <v>280</v>
@@ -29580,28 +29577,28 @@
     </row>
     <row r="702" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A702" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="B702" s="2">
         <v>0.14166666666666666</v>
       </c>
       <c r="C702" t="s">
+        <v>1436</v>
+      </c>
+      <c r="E702" t="s">
         <v>1437</v>
-      </c>
-      <c r="E702" t="s">
-        <v>1438</v>
       </c>
       <c r="F702">
         <v>1986</v>
       </c>
       <c r="G702" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
       </c>
       <c r="I702" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J702" t="s">
         <v>280</v>
@@ -29630,7 +29627,7 @@
         <v>9</v>
       </c>
       <c r="I703" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="J703" t="s">
         <v>128</v>
@@ -29659,7 +29656,7 @@
         <v>9</v>
       </c>
       <c r="I704" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="J704" t="s">
         <v>280</v>
@@ -29688,7 +29685,7 @@
         <v>9</v>
       </c>
       <c r="I705" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J705" t="s">
         <v>277</v>
@@ -29717,7 +29714,7 @@
         <v>9</v>
       </c>
       <c r="I706" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J706" t="s">
         <v>277</v>
@@ -29746,7 +29743,7 @@
         <v>9</v>
       </c>
       <c r="I707" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J707" t="s">
         <v>280</v>
@@ -29798,13 +29795,13 @@
         <v>2003</v>
       </c>
       <c r="G709" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
       </c>
       <c r="I709" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J709" t="s">
         <v>280</v>
@@ -29833,7 +29830,7 @@
         <v>9</v>
       </c>
       <c r="I710" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J710" t="s">
         <v>128</v>
@@ -29862,7 +29859,7 @@
         <v>9</v>
       </c>
       <c r="I711" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J711" t="s">
         <v>128</v>
@@ -29891,7 +29888,7 @@
         <v>9</v>
       </c>
       <c r="I712" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J712" t="s">
         <v>128</v>
@@ -29914,13 +29911,13 @@
         <v>1990</v>
       </c>
       <c r="G713" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
       </c>
       <c r="I713" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J713" t="s">
         <v>128</v>
@@ -29943,13 +29940,13 @@
         <v>2007</v>
       </c>
       <c r="G714" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
       </c>
       <c r="I714" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J714" t="s">
         <v>128</v>
@@ -29972,13 +29969,13 @@
         <v>2007</v>
       </c>
       <c r="G715" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
       </c>
       <c r="I715" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J715" t="s">
         <v>128</v>
@@ -30001,13 +29998,13 @@
         <v>2007</v>
       </c>
       <c r="G716" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
       </c>
       <c r="I716" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J716" t="s">
         <v>128</v>
@@ -30033,13 +30030,13 @@
         <v>2014</v>
       </c>
       <c r="G717" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
       </c>
       <c r="I717" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J717" t="s">
         <v>10</v>
@@ -30068,7 +30065,7 @@
         <v>9</v>
       </c>
       <c r="I718" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J718" t="s">
         <v>277</v>
@@ -30097,7 +30094,7 @@
         <v>9</v>
       </c>
       <c r="I719" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="J719" t="s">
         <v>277</v>
@@ -30126,7 +30123,7 @@
         <v>9</v>
       </c>
       <c r="I720" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="J720" t="s">
         <v>280</v>
@@ -30155,7 +30152,7 @@
         <v>9</v>
       </c>
       <c r="I721" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="J721" t="s">
         <v>31</v>
@@ -30242,7 +30239,7 @@
         <v>9</v>
       </c>
       <c r="I724" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="J724" t="s">
         <v>10</v>
@@ -30271,7 +30268,7 @@
         <v>9</v>
       </c>
       <c r="I725" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="J725" t="s">
         <v>10</v>
@@ -30300,7 +30297,7 @@
         <v>9</v>
       </c>
       <c r="I726" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="J726" t="s">
         <v>10</v>
@@ -30329,7 +30326,7 @@
         <v>9</v>
       </c>
       <c r="I727" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="J727" t="s">
         <v>10</v>
@@ -30361,7 +30358,7 @@
         <v>9</v>
       </c>
       <c r="I728" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="J728" t="s">
         <v>280</v>
@@ -30384,13 +30381,13 @@
         <v>2024</v>
       </c>
       <c r="G729" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
       </c>
       <c r="I729" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J729" t="s">
         <v>128</v>
@@ -30413,10 +30410,10 @@
         <v>1964</v>
       </c>
       <c r="G730" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="H730" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I730" t="s">
         <v>578</v>
@@ -30425,7 +30422,7 @@
         <v>578</v>
       </c>
       <c r="M730" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="731" spans="1:13" x14ac:dyDescent="0.2">
@@ -30544,7 +30541,7 @@
         <v>9</v>
       </c>
       <c r="I734" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J734" t="s">
         <v>10</v>
@@ -30570,13 +30567,13 @@
         <v>2004</v>
       </c>
       <c r="G735" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
       </c>
       <c r="I735" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J735" t="s">
         <v>10</v>
@@ -30608,7 +30605,7 @@
         <v>9</v>
       </c>
       <c r="I736" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J736" t="s">
         <v>10</v>
@@ -30640,7 +30637,7 @@
         <v>9</v>
       </c>
       <c r="I737" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J737" t="s">
         <v>277</v>
@@ -30672,7 +30669,7 @@
         <v>9</v>
       </c>
       <c r="I738" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J738" t="s">
         <v>10</v>
@@ -30704,7 +30701,7 @@
         <v>9</v>
       </c>
       <c r="I739" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J739" t="s">
         <v>10</v>
@@ -30730,10 +30727,10 @@
         <v>1271</v>
       </c>
       <c r="H740" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I740" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J740" t="s">
         <v>10</v>
@@ -30759,13 +30756,13 @@
         <v>2004</v>
       </c>
       <c r="G741" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
       </c>
       <c r="I741" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J741" t="s">
         <v>10</v>
@@ -30797,7 +30794,7 @@
         <v>9</v>
       </c>
       <c r="I742" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J742" t="s">
         <v>277</v>
@@ -30829,7 +30826,7 @@
         <v>9</v>
       </c>
       <c r="I743" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J743" t="s">
         <v>10</v>
@@ -30861,7 +30858,7 @@
         <v>9</v>
       </c>
       <c r="I744" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J744" t="s">
         <v>277</v>
@@ -30893,7 +30890,7 @@
         <v>9</v>
       </c>
       <c r="I745" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J745" t="s">
         <v>277</v>
@@ -30925,7 +30922,7 @@
         <v>9</v>
       </c>
       <c r="I746" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J746" t="s">
         <v>277</v>
@@ -30957,7 +30954,7 @@
         <v>9</v>
       </c>
       <c r="I747" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J747" t="s">
         <v>277</v>
@@ -30989,7 +30986,7 @@
         <v>9</v>
       </c>
       <c r="I748" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J748" t="s">
         <v>10</v>
@@ -31021,7 +31018,7 @@
         <v>9</v>
       </c>
       <c r="I749" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J749" t="s">
         <v>277</v>
@@ -31053,7 +31050,7 @@
         <v>9</v>
       </c>
       <c r="I750" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J750" t="s">
         <v>277</v>
@@ -31085,7 +31082,7 @@
         <v>9</v>
       </c>
       <c r="I751" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="J751" t="s">
         <v>277</v>

--- a/data/music.xlsx
+++ b/data/music.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lindanakasone/Documents/GitHub/sound-and-vision/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8A43501-697F-9043-B58B-DCA334D1B22D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5BE433F-7779-2C4E-84BF-D3F754DB7AD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2100" yWindow="6100" windowWidth="33440" windowHeight="21500" xr2:uid="{D9D4D37D-4BCE-774B-89FD-6B702A9EB150}"/>
+    <workbookView xWindow="2300" yWindow="920" windowWidth="33440" windowHeight="21500" xr2:uid="{D9D4D37D-4BCE-774B-89FD-6B702A9EB150}"/>
   </bookViews>
   <sheets>
     <sheet name="750 songs" sheetId="5" r:id="rId1"/>

--- a/data/music.xlsx
+++ b/data/music.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lindanakasone/Documents/GitHub/sound-and-vision/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5BE433F-7779-2C4E-84BF-D3F754DB7AD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3715AC32-DFA8-C143-9063-2877ABD0D87F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2300" yWindow="920" windowWidth="33440" windowHeight="21500" xr2:uid="{D9D4D37D-4BCE-774B-89FD-6B702A9EB150}"/>
+    <workbookView xWindow="19040" yWindow="9240" windowWidth="33440" windowHeight="21500" xr2:uid="{D9D4D37D-4BCE-774B-89FD-6B702A9EB150}"/>
   </bookViews>
   <sheets>
     <sheet name="750 songs" sheetId="5" r:id="rId1"/>
